--- a/public/Amritsar_South_2022_2024_2026_Three_Column_Comparison.xlsx
+++ b/public/Amritsar_South_2022_2024_2026_Three_Column_Comparison.xlsx
@@ -116,14 +116,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-        <bgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -230,25 +230,25 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -849,12 +849,12 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Booth 1 - Amritsar South</t>
+          <t>Amrit Senior Secondary School - Chowk Chira, Gate Hakima, Amritsar</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 1 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਅੰਮ੍ਰਿਤ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ - ਚੌਂਕ ਚਿੜਾ, ਗੇਟ ਹਕੀਮਾਂ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D4" s="21" t="n">
@@ -932,31 +932,31 @@
         <v>27</v>
       </c>
       <c r="Z4" s="21" t="n">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="AA4" s="24" t="inlineStr">
         <is>
-          <t>TIED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB4" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(4.35%) | INC:0(0.0%) | BJP:0 | SAD:1</t>
+          <t>AAP:16(18.6%) | INC:26(30.23%) | BJP:9 | SAD:6</t>
         </is>
       </c>
       <c r="AC4" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD4" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → TIED</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE4" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → TIED)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>Booth 2 - Amritsar South</t>
+          <t>Amrit Senior Secondary School - Chowk Chira, Gate Hakima, Amritsar</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 2 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਅੰਮ੍ਰਿਤ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ - ਚੌਂਕ ਚਿੜਾ, ਗੇਟ ਹਕੀਮਾਂ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D5" s="27" t="n">
@@ -1035,7 +1035,7 @@
       <c r="V5" s="27" t="n">
         <v>32</v>
       </c>
-      <c r="W5" s="28" t="inlineStr">
+      <c r="W5" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -1049,16 +1049,16 @@
         <v>15</v>
       </c>
       <c r="Z5" s="27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA5" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>100</v>
+      </c>
+      <c r="AA5" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB5" s="26" t="inlineStr">
         <is>
-          <t>AAP:7(17.5%) | INC:2(5.0%) | BJP:1 | SAD:0</t>
+          <t>AAP:9(9.0%) | INC:51(51.0%) | BJP:4 | SAD:2</t>
         </is>
       </c>
       <c r="AC5" s="26" t="inlineStr">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="AD5" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → AAP</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE5" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (AAP → INC → AAP)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Booth 3 - Amritsar South</t>
+          <t>Amrit Sr. Sec. School - Chowk Chira, Gate Hakima, Amritsar</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 3 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਅੰਮ੍ਰਿਤ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ - ਚੌਂਕ ਚਿੜਾ, ਗੇਟ ਹਕੀਮਾਂ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D6" s="21" t="n">
@@ -1166,31 +1166,31 @@
         <v>109</v>
       </c>
       <c r="Z6" s="21" t="n">
-        <v>63</v>
-      </c>
-      <c r="AA6" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>72</v>
+      </c>
+      <c r="AA6" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB6" s="20" t="inlineStr">
         <is>
-          <t>AAP:8(12.7%) | INC:1(1.59%) | BJP:0 | SAD:0</t>
+          <t>AAP:11(15.28%) | INC:28(38.89%) | BJP:6 | SAD:3</t>
         </is>
       </c>
       <c r="AC6" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD6" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE6" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>Booth 4 - Amritsar South</t>
+          <t>Amrit Senior Secondary School - Chowk Chira, Gate Hakima, Amritsar</t>
         </is>
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 4 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਅੰਮ੍ਰਿਤ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਚੌਂਕ ਚਿੜਾ, ਗੇਟ ਹਕੀਮਾਂ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D7" s="27" t="n">
@@ -1283,16 +1283,16 @@
         <v>110</v>
       </c>
       <c r="Z7" s="27" t="n">
-        <v>59</v>
-      </c>
-      <c r="AA7" s="28" t="inlineStr">
+        <v>90</v>
+      </c>
+      <c r="AA7" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
       </c>
       <c r="AB7" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(1.69%) | INC:8(13.56%) | BJP:1 | SAD:0</t>
+          <t>AAP:20(22.22%) | INC:25(27.78%) | BJP:7 | SAD:7</t>
         </is>
       </c>
       <c r="AC7" s="26" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Booth 5 - Amritsar South</t>
+          <t>Swaran Senior Secondary School - Sant Nagar, Amritsar</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 5 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਵਰਨ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ - ਸੰਤ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D8" s="21" t="n">
@@ -1400,31 +1400,31 @@
         <v>85</v>
       </c>
       <c r="Z8" s="21" t="n">
-        <v>77</v>
-      </c>
-      <c r="AA8" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>103</v>
+      </c>
+      <c r="AA8" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB8" s="20" t="inlineStr">
         <is>
-          <t>AAP:6(7.79%) | INC:2(2.6%) | BJP:0 | SAD:0</t>
+          <t>AAP:17(16.5%) | INC:32(31.07%) | BJP:13 | SAD:4</t>
         </is>
       </c>
       <c r="AC8" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD8" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE8" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>Booth 6 - Amritsar South</t>
+          <t>Swaran Senior Secondary School - Sant Nagar, Amritsar</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 6 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਵਰਨ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਸੰਤ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D9" s="27" t="n">
@@ -1517,21 +1517,21 @@
         <v>124</v>
       </c>
       <c r="Z9" s="27" t="n">
-        <v>82</v>
-      </c>
-      <c r="AA9" s="28" t="inlineStr">
+        <v>96</v>
+      </c>
+      <c r="AA9" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
       </c>
       <c r="AB9" s="26" t="inlineStr">
         <is>
-          <t>AAP:3(3.66%) | INC:4(4.88%) | BJP:1 | SAD:0</t>
+          <t>AAP:12(12.5%) | INC:33(34.38%) | BJP:10 | SAD:7</t>
         </is>
       </c>
       <c r="AC9" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD9" s="26" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Booth 7 - Amritsar South</t>
+          <t>Swaran Senior Secondary School - Sant Nagar, Amritsar</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 7 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਵਰਨ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ - ਸੰਤ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D10" s="21" t="n">
@@ -1634,7 +1634,7 @@
         <v>21</v>
       </c>
       <c r="Z10" s="21" t="n">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="AA10" s="22" t="inlineStr">
         <is>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="AB10" s="20" t="inlineStr">
         <is>
-          <t>AAP:7(10.45%) | INC:4(5.97%) | BJP:0 | SAD:0</t>
+          <t>AAP:27(25.71%) | INC:26(24.76%) | BJP:8 | SAD:7</t>
         </is>
       </c>
       <c r="AC10" s="20" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD10" s="20" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>Bhagtanwala Gali No. 4, Nagar Nigam Amritsar, Ward No. 49 + Bazar Munshian Wala, Nagar Nigam Amritsar, Ward No. 49 + Gali Mansood Choudhary, Nagar Nigam Amritsar, Ward No. 49 + Bazar Ghumiyaran Wala, Nagar Nigam Amritsar, Ward No. 49 + Gali Munshian Wali, Nagar Nigam Amritsar, Ward No. 49 + Katra Karam Singh, Nagar Nigam Amritsar, Ward No. 49</t>
+          <t>Swaran Senior Secondary School - Sant Nagar, Amritsar</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>ਭਗਤਾਂਵਾਲਾ ਗਲੀ ਨੰ.4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਬਜ਼ਾਰ ਮੁਨਸ਼ੀਆ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਮਨਸੂਦ ਚੌਧਰੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਬਜ਼ਾਰ ਘੁਮਿਆਰਾਂ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਮੁਨਸ਼ੀਆ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਕਟੜਾ ਕਰਮ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49</t>
+          <t>ਸਵਰਨ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਸੰਤ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
@@ -1751,16 +1751,16 @@
         <v>104</v>
       </c>
       <c r="Z11" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA11" s="29" t="inlineStr">
-        <is>
-          <t>TIED</t>
+        <v>112</v>
+      </c>
+      <c r="AA11" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB11" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:1(33.33%) | BJP:0 | SAD:0</t>
+          <t>AAP:19(16.96%) | INC:30(26.79%) | BJP:16 | SAD:8</t>
         </is>
       </c>
       <c r="AC11" s="26" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="AD11" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → TIED</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE11" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → TIED)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Gali Hatam Bhai Andrun Gate Hakima, Nagar Nigam Amritsar, Ward No. 54</t>
+          <t>Govt. Middle School, Gali Mochian, Amritsar</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਹਾਤਮ ਭਾਈ ਅੰਦਰੁਨ ਗੇਟ ਹਕੀਮਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 54</t>
+          <t>ਸਰਕਾਰੀ ਮਿਡਲ ਸਕੂਲ, ਗਾਲੀ ਮੋਚੀਆਂ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D12" s="21" t="n">
@@ -1868,31 +1868,31 @@
         <v>128</v>
       </c>
       <c r="Z12" s="21" t="n">
-        <v>74</v>
-      </c>
-      <c r="AA12" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>117</v>
+      </c>
+      <c r="AA12" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB12" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:32(27.35%) | INC:21(17.95%) | BJP:20 | SAD:3</t>
         </is>
       </c>
       <c r="AC12" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD12" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → UNDECIDED</t>
+          <t>AAP → BJP → AAP</t>
         </is>
       </c>
       <c r="AE12" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → UNDECIDED)</t>
+          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>Gali Khoiyan No. 1, Nagar Nigam Amritsar, Ward No. 54 + Gali Khoiyan No. 2, Nagar Nigam Amritsar, Ward No. 54 + Gali Hatam Bhai Baharla Pasa, Nagar Nigam Amritsar, Ward No. 54 + Gate Khazana Saja Pasa, Nagar Nigam Amritsar, Ward No. 54 + Circular Road Khazana Gate, Nagar Nigam Amritsar, Ward No. 54</t>
+          <t>Govt. Middle School - Gali Mochian, Amritsar</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਖੋਈਆਂ ਨੰ. 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 54 + ਗਲੀ ਖੋਈਆਂ ਨੰ. 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 54 + ਗਲੀ ਹਾਤਮ ਭਾਈ ਬਾਹਰਲਾ ਪਾਸਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 54 + ਗੇਟ ਖਜ਼ਾਨਾ ਸੱਜਾ ਪਾਸਾ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 54 + ਸਰਕੁਲਰ ਰੋਡ ਖਜ਼ਾਨਾ ਗੇਟ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 54</t>
+          <t>ਸਰਕਾਰੀ ਮਿਡਲ ਸਕੂਲ - ਗਾਲੀ ਮੋਛੀਆਂ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D13" s="27" t="n">
@@ -1985,31 +1985,31 @@
         <v>67</v>
       </c>
       <c r="Z13" s="27" t="n">
-        <v>33</v>
-      </c>
-      <c r="AA13" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>91</v>
+      </c>
+      <c r="AA13" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB13" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:2(6.06%) | BJP:0 | SAD:0</t>
+          <t>AAP:24(26.37%) | INC:22(24.18%) | BJP:6 | SAD:6</t>
         </is>
       </c>
       <c r="AC13" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD13" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → INC</t>
+          <t>AAP → BJP → AAP</t>
         </is>
       </c>
       <c r="AE13" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → BJP → INC)</t>
+          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Booth 11 - Amritsar South</t>
+          <t>Government Middle School - Gali Mochian, Amritsar</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 11 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਮਿਡਲ ਸਕੂਲ - ਗਾਲੀ ਮੋਚੀਆਂ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D14" s="21" t="n">
@@ -2102,16 +2102,16 @@
         <v>94</v>
       </c>
       <c r="Z14" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="28" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="AA14" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
       </c>
       <c r="AB14" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(20.0%) | INC:4(80.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:8(9.64%) | INC:30(36.14%) | BJP:13 | SAD:3</t>
         </is>
       </c>
       <c r="AC14" s="20" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>Booth 12 - Amritsar South</t>
+          <t>Sweet Model School - Near Khazana Gate, Amritsar</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 12 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਵੀਟ ਮਾਡਲ ਸਕੂਲ - ਨੇੜੇ ਖਜ਼ਾਨਾ ਗੇਟ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
@@ -2219,31 +2219,31 @@
         <v>120</v>
       </c>
       <c r="Z15" s="27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA15" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>104</v>
+      </c>
+      <c r="AA15" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB15" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:26(25.0%) | INC:25(24.04%) | BJP:15 | SAD:1</t>
         </is>
       </c>
       <c r="AC15" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD15" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → UNDECIDED</t>
+          <t>AAP → BJP → AAP</t>
         </is>
       </c>
       <c r="AE15" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → UNDECIDED)</t>
+          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Booth 13 - Amritsar South</t>
+          <t>Govt. Elementary School, Gali Mochian, Gate Khazana Amritsar</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 13 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਗਲੀ ਮੋਚੀਆਂ, ਗੇਟ ਖਜ਼ਾਨਾ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D16" s="21" t="n">
@@ -2336,31 +2336,31 @@
         <v>85</v>
       </c>
       <c r="Z16" s="21" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="AA16" s="24" t="inlineStr">
         <is>
-          <t>UNDECIDED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB16" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:12(16.9%) | INC:21(29.58%) | BJP:11 | SAD:2</t>
         </is>
       </c>
       <c r="AC16" s="20" t="inlineStr">
         <is>
-          <t>Harjinder Singh Thekedar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD16" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → UNDECIDED</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE16" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>Booth 14 - Amritsar South</t>
+          <t>Govt. Elementary School - Gali Mochian, Gate Khazana Amritsar</t>
         </is>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 14 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਗਾਲੀ ਮੋਛੀਆਂ, ਗੇਟ ਖਜ਼ਾਨਾ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D17" s="27" t="n">
@@ -2453,31 +2453,31 @@
         <v>43</v>
       </c>
       <c r="Z17" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA17" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>93</v>
+      </c>
+      <c r="AA17" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB17" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:9(9.68%) | INC:34(36.56%) | BJP:14 | SAD:3</t>
         </is>
       </c>
       <c r="AC17" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD17" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → UNDECIDED</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE17" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -2487,12 +2487,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Booth 15 - Amritsar South</t>
+          <t>Govt. Elementary School - Gali Mochian, Gate Khazana Amritsar</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 15 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਗਾਲੀ ਮੋਚੀਆਂ, ਗੇਟ ਖਜ਼ਾਨਾ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D18" s="21" t="n">
@@ -2556,7 +2556,7 @@
       <c r="V18" s="21" t="n">
         <v>42</v>
       </c>
-      <c r="W18" s="28" t="inlineStr">
+      <c r="W18" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -2570,31 +2570,31 @@
         <v>73</v>
       </c>
       <c r="Z18" s="21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA18" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>108</v>
+      </c>
+      <c r="AA18" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB18" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(4.17%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:14(12.96%) | INC:46(42.59%) | BJP:5 | SAD:5</t>
         </is>
       </c>
       <c r="AC18" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD18" s="20" t="inlineStr">
         <is>
-          <t>AAP → INC → AAP</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE18" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (AAP → INC → AAP)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>Booth 16 - Amritsar South</t>
+          <t>Govt. Elementary School - Himmatpura Bhagtanwala Amritsar</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 16 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਹਿੰਮਤਪੁਰਾ ਭਗਤਾਂਵਾਲਾ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D19" s="27" t="n">
@@ -2636,7 +2636,7 @@
       <c r="K19" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="L19" s="30" t="inlineStr">
+      <c r="L19" s="28" t="inlineStr">
         <is>
           <t>SAD</t>
         </is>
@@ -2673,7 +2673,7 @@
       <c r="V19" s="27" t="n">
         <v>104</v>
       </c>
-      <c r="W19" s="28" t="inlineStr">
+      <c r="W19" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -2687,31 +2687,31 @@
         <v>59</v>
       </c>
       <c r="Z19" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA19" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>87</v>
+      </c>
+      <c r="AA19" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB19" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:13(14.94%) | INC:30(34.48%) | BJP:6 | SAD:8</t>
         </is>
       </c>
       <c r="AC19" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD19" s="26" t="inlineStr">
         <is>
-          <t>SAD → INC → UNDECIDED</t>
+          <t>SAD → INC → INC</t>
         </is>
       </c>
       <c r="AE19" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (SAD → INC → UNDECIDED)</t>
+          <t>INC Leading Survey (SAD → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Abadi Radha Krishan Colony, Nagar Nigam Amritsar, Ward No. 50 + Abadi Quarters, Mulle Chak, Nagar Nigam Amritsar, Ward No. 50</t>
+          <t>Bhagtanwala - Punjab National School, Bhai Veer Singh Colony, Mulle Chak, Amritsar</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>ਆਬਾਦੀ ਰਾਧਾ ਕ੍ਰਿਸ਼ਨ ਕੈਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਅਬਾਦੀ ਕਵਾਂਟਰ, ਮੁ้ਲੇ ਚੱਕ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਭਗਤਾਂਵਾਲਾ - ਪੰਜਾਬ ਨੈਸ਼ਨਲ ਸਕੂਲ, ਭਾਈ ਵੀਰ ਸਿੰਘ ਕੋਲਨੀ, ਮੁੱਲੇ ਚੱਕ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D20" s="21" t="n">
@@ -2753,7 +2753,7 @@
       <c r="K20" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="L20" s="28" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -2790,7 +2790,7 @@
       <c r="V20" s="21" t="n">
         <v>73</v>
       </c>
-      <c r="W20" s="28" t="inlineStr">
+      <c r="W20" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -2804,31 +2804,31 @@
         <v>24</v>
       </c>
       <c r="Z20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="24" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>100</v>
+      </c>
+      <c r="AA20" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB20" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:32(32.0%) | INC:21(21.0%) | BJP:5 | SAD:7</t>
         </is>
       </c>
       <c r="AC20" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD20" s="20" t="inlineStr">
         <is>
-          <t>INC → INC → PENDING</t>
+          <t>INC → INC → AAP</t>
         </is>
       </c>
       <c r="AE20" s="20" t="inlineStr">
         <is>
-          <t>INC → INC → Survey Pending</t>
+          <t>AAP Regained from INC (INC → INC → AAP)</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>Abadi Quarter, Mulle Chowk, Nagar Nigam Amritsar, Ward No. 50</t>
+          <t>Bhagtanwala - Punjab National School, Bhai Veer Singh Colony, Mulle Chowk, Amritsar</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਕਵਾਟਰ, ਮੁ้ਲੇ ਚੌਕ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਭਗਤਾਂਵਲਾ - ਪੰਜਾਬ ਨੈਸ਼ਨਲ ਸਕੂਲ, ਭਾਈ ਵੀਰ ਸਿੰਘ ਕੋਲਨੀ, ਮੁੱਲੇ ਚੌਕ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D21" s="27" t="n">
@@ -2870,7 +2870,7 @@
       <c r="K21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L21" s="28" t="inlineStr">
+      <c r="L21" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -2907,7 +2907,7 @@
       <c r="V21" s="27" t="n">
         <v>123</v>
       </c>
-      <c r="W21" s="28" t="inlineStr">
+      <c r="W21" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -2921,31 +2921,31 @@
         <v>98</v>
       </c>
       <c r="Z21" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>97</v>
+      </c>
+      <c r="AA21" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB21" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:9(9.28%) | INC:44(45.36%) | BJP:3 | SAD:6</t>
         </is>
       </c>
       <c r="AC21" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD21" s="26" t="inlineStr">
         <is>
-          <t>INC → INC → PENDING</t>
+          <t>INC → INC → INC</t>
         </is>
       </c>
       <c r="AE21" s="26" t="inlineStr">
         <is>
-          <t>INC → INC → Survey Pending</t>
+          <t>INC Leading Survey (INC → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Gali Chhiura Wali, Nagar Nigam Amritsar Ward No. 48 + Gali Devi Wali, (Jora Pipal) Nagar Nigam Amritsar, Ward No. 48 + Gali Nalke Wali, Nagar Nigam Amritsar, Ward No. 48 + Gali Pehalwana, Nagar Nigam Amritsar, Ward No. 48 + Gali Diwan Singh, Nagar Nigam Amritsar, Ward No. 48 + Gali Chela Ram, Nagar Nigam Amritsar, Ward No. 48</t>
+          <t>Govt. High School (Girls) - Road Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਛਿਉੜਾ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਦੇਵੀ ਵਾਲੀ, (ਜੋੜਾ ਪਿੱਪਲ) ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਨਲਕੇ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਪਹਿਲਵਾਨਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਦੀਵਾਨ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਚੇਲਾ ਰਾਮ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਰੋਡ ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D22" s="21" t="n">
@@ -3038,16 +3038,16 @@
         <v>170</v>
       </c>
       <c r="Z22" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA22" s="28" t="inlineStr">
+        <v>96</v>
+      </c>
+      <c r="AA22" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
       </c>
       <c r="AB22" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(6.67%) | INC:9(30.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:15(15.62%) | INC:35(36.46%) | BJP:11 | SAD:1</t>
         </is>
       </c>
       <c r="AC22" s="20" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>Bazar Bhagtan Wala, Nagar Nigam Amritsar, Ward No. 48 + Gali Shahdin, Nagar Nigam Amritsar, Ward No. 48 + Bazar Gujran Wala, Nagar Nigam Amritsar, Ward No. 48 + Gali Masit Wali, Nagar Nigam Amritsar, Ward No. 48 + Bazar Gujran Chowk Chabutra, Nagar Nigam Amritsar, Ward No. 48 + Kucha Hari Singh, Nagar Nigam Amritsar, Ward No. 48 + Kucha Raiyan Wala, Nagar Nigam Amritsar, Ward No. 48 + Gali Shahdin, Nagar Nigam Amritsar Ward No. 48 + Gali Nati Baksh, Nagar Nigam Amritsar, Ward No. 48</t>
+          <t>Govt. High School (Girls) - Gate Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>ਬਾਜ਼ਾਰ ਭਗਤਾਂ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਸ਼ਾਹਦੀਨ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਬਾਜ਼ਾਰ ਗੁਜਰਾਂ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਮਸੀਤ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਬਾਜ਼ਾਰ ਗੁਜਰਾਂ ਚੌਂਕ ਚਬੂਤਰਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਕੂਚਾ ਹਰੀ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਕੂਚਾ ਰਾਈਆਂ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਸ਼ਾਹਦੀਨ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਨਤੀ ਬਖਸ਼, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਗੇਟ ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D23" s="27" t="n">
@@ -3155,31 +3155,31 @@
         <v>41</v>
       </c>
       <c r="Z23" s="27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA23" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>73</v>
+      </c>
+      <c r="AA23" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB23" s="26" t="inlineStr">
         <is>
-          <t>AAP:5(17.86%) | INC:4(14.29%) | BJP:0 | SAD:1</t>
+          <t>AAP:13(17.81%) | INC:25(34.25%) | BJP:6 | SAD:3</t>
         </is>
       </c>
       <c r="AC23" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD23" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE23" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Kucha Gujran Wala, Nagar Nigam Amritsar, Ward No. 48 + Gali Guru Nanak Wali, Nagar Nigam, Amritsar, Ward No. 48 + Kucha Tahil Singh Circular Road Nagar Nigam Amritsar Ward No. 48 + Gali Sedhiyan, Nagar Nigam Amritsar, Ward No. 46 + Gali Moole Wali, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Govt. High School (Girls) - Gate Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>ਕੂਚਾ ਗੁਜਰਾਂ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਗੁਰੂ ਨਾਨਕ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਕੂਚਾ ਟਹਿਲ ਸਿੰਘ ਸਰਕੂਲਰ ਰੋਡ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਸੇਢੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਮੂਲੇ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਗੇਟ ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D24" s="21" t="n">
@@ -3272,31 +3272,31 @@
         <v>65</v>
       </c>
       <c r="Z24" s="21" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA24" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>93</v>
+      </c>
+      <c r="AA24" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB24" s="20" t="inlineStr">
         <is>
-          <t>AAP:11(24.44%) | INC:5(11.11%) | BJP:2 | SAD:0</t>
+          <t>AAP:16(17.2%) | INC:32(34.41%) | BJP:8 | SAD:3</t>
         </is>
       </c>
       <c r="AC24" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD24" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE24" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>Gali Pehalwana Wali Bazar Bhagtan Wala, Nagar Nigam Amritsar, Ward No. 48 + Gali Tind Shah, Nagar Nigam Amritsar, Ward No. 48 + Mohalla Balmiki, Nagar Nigam Amritsar, Ward No. 48 + Mandir Wali Gali, Nagar Nigam Amritsar Ward No. 48 + Gali Dharek Wali, Nagar Nigam Amritsar Ward No. 48</t>
+          <t>Govt. High School (Girls) - Gate Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਪਹਿਲਵਾਨਾਂ ਵਾਲੀ ਬਾਜ਼ਾਰ ਭਗਤਾਂ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਟਿੰਡ ਸ਼ਾਹ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਮੁਹੱਲਾ ਬਾਲਮੀਕੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਮੰਦਿਰ ਵਾਲੀ ਗਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਧਰੇਕ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਗੇਟ ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D25" s="27" t="n">
@@ -3375,7 +3375,7 @@
       <c r="V25" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="W25" s="28" t="inlineStr">
+      <c r="W25" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -3389,31 +3389,31 @@
         <v>107</v>
       </c>
       <c r="Z25" s="27" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA25" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>85</v>
+      </c>
+      <c r="AA25" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB25" s="26" t="inlineStr">
         <is>
-          <t>AAP:4(11.43%) | INC:6(17.14%) | BJP:2 | SAD:0</t>
+          <t>AAP:22(25.88%) | INC:17(20.0%) | BJP:8 | SAD:8</t>
         </is>
       </c>
       <c r="AC25" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD25" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → INC</t>
+          <t>AAP → INC → AAP</t>
         </is>
       </c>
       <c r="AE25" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → INC → INC)</t>
+          <t>AAP Regained from INC (AAP → INC → AAP)</t>
         </is>
       </c>
     </row>
@@ -3423,12 +3423,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Guru Teg Bahadur Avenue, Nagar Nigam Amritsar, Ward No. 46 + Bazaar Ghumiaran, Nagar Nigam Amritsar, Ward No. 48 + Gali Guru Nanak, Nagar Nigam Amritsar, Ward No. 48 + Gali Krishna, Nagar Nigam Amritsar, Ward No. 48 + Gali Mistra Nagar Nigam Amritsar, Ward No. 48 + Gali Jawala Wali, Nagar Nigam Amritsar, Ward No. 48 + Gali Chappar Wali, Nagar Nigam Amritsar, Ward No. 48 + Bazaar Ghumiaran Wala Near Shivala Behar Wala Chowk, Nagar Nigam Amritsar, Ward No. 48</t>
+          <t>Govt. High School (Girls), Bhagtanwala - Gate Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>ਗੁਰੂ ਤੇਗ ਬਹਾਦਰ ਐਵੀਨਿਊ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਾਜ਼ਾਰ ਘੁਮਿਆਰਾਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਗੁਰੂ ਨਾਨਕ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਕ੍ਰਿਸ਼ਨਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਮਿਸਤਰਾ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਜਵਾਲਾ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਛੱਪੜ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਬਾਜ਼ਾਰ ਘੁਮਿਆਰਾਂ ਵਾਲਾ ਨੇੜੇ ਸ਼ਿਵਾਲਾ ਬੇਹੜ ਵਾਲਾ ਚੌਕ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ (ਲੜਕੀਆਂ), ਭਗਤਾਂਵਾਲਾ - ਗੇਟ ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D26" s="21" t="n">
@@ -3506,31 +3506,31 @@
         <v>11</v>
       </c>
       <c r="Z26" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA26" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>71</v>
+      </c>
+      <c r="AA26" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB26" s="20" t="inlineStr">
         <is>
-          <t>AAP:3(23.08%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:12(16.9%) | INC:26(36.62%) | BJP:6 | SAD:1</t>
         </is>
       </c>
       <c r="AC26" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD26" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE26" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>Kucha Rahimshu Khila, Nagar Nigam Amritsar, Ward No. 48 + Androon Gilwali Gate, Nagar Nigam Amritsar, Ward No. 48 + Bazaar Jattan Wala, Nagar Nigam Amritsar, Ward No. 48 + Gali Jameetan Kamboj, Nagar Nigam Amritsar, Ward No. 48 + Gali Aave Wali, Nagar Nigam Amritsar, Ward No. 48</t>
+          <t>Govt. Elementary Smart School, Gate Bhagtanwala - Gate Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>ਕੂਚਾ ਰਹੀਮਸ਼ੁ ਖਿਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਅੰਦਰੂਨ ਗਿਲਵਾਲੀ ਗੇਟ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਬਾਜ਼ਾਰ ਜੱਟਾਂ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਜਮੀਤਾਂ ਕੰਬੋਜ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਆਵੇ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਮਾਰਟ ਸਕੂਲ, ਗੇਟ ਭਗਤਾਂਵਾਲਾ - ਗੇਟ ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D27" s="27" t="n">
@@ -3623,7 +3623,7 @@
         <v>25</v>
       </c>
       <c r="Z27" s="27" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="AA27" s="22" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AB27" s="26" t="inlineStr">
         <is>
-          <t>AAP:8(15.69%) | INC:5(9.8%) | BJP:0 | SAD:0</t>
+          <t>AAP:34(36.96%) | INC:16(17.39%) | BJP:7 | SAD:3</t>
         </is>
       </c>
       <c r="AC27" s="26" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Gali Aave Wali, Androon Gate Bhagtanwala, Nagar Nigam Amritsar Ward No. 48 + Gali Megha Katra Garbha Singh, Nagar Nigam Amritsar. Ward No. 48, Amritsar. + Gali Aave Wali Devi, Androon Gate Bhagtanwala, Nagar Nigam Amritsar Ward No. 48 + Gali Rahimuj Bazar Gujra, Nagar Nigam Amritsar. Ward No. 48, Amritsar. + Bazar Gujra Katra Garbha Singh, Nagar Nigam Amritsar Ward No. 48, Amritsar.</t>
+          <t>Govt. Elementary Smart School, Gate Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਆਵੇ ਵਾਲੀ, ਅੰਦਰੂਨ ਗੇਟ ਭਗਤਾਂਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 48 + ਗਲੀ ਮੇਘਾ ਕਟੜਾ ਗਰਭਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ. ਵਾਰਡ ਨੰ 48, ਅੰਮ੍ਰਿਤਸਰ. + ਗਲੀ ਆਵੇ ਵਾਲੀ ਦੇਵੀ, ਅੰਦਰੂਨ ਗੇਟ ਭਗਤਾਂਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 48 + ਗਲੀ ਰਹਿਮੁਜ ਬਜਾਰ ਗੁਜਰਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ. ਵਾਰਡ ਨੰ 48, ਅੰਮ੍ਰਿਤਸਰ. + ਬਾਜਾਰ ਗੁਜਰਾ ਕਟੜਾ ਗਰਭਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 48, ਅੰਮ੍ਰਿਤਸਰ.</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਮਾਰਟ ਸਕੂਲ, ਗੇਟ ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D28" s="21" t="n">
@@ -3740,31 +3740,31 @@
         <v>152</v>
       </c>
       <c r="Z28" s="21" t="n">
-        <v>49</v>
-      </c>
-      <c r="AA28" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>124</v>
+      </c>
+      <c r="AA28" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB28" s="20" t="inlineStr">
         <is>
-          <t>AAP:7(14.29%) | INC:10(20.41%) | BJP:0 | SAD:0</t>
+          <t>AAP:38(30.65%) | INC:21(16.94%) | BJP:18 | SAD:4</t>
         </is>
       </c>
       <c r="AC28" s="20" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD28" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → INC</t>
+          <t>AAP → BJP → AAP</t>
         </is>
       </c>
       <c r="AE28" s="20" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → BJP → INC)</t>
+          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
         </is>
       </c>
     </row>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>Gali Taliyan Wali, Nagar Nigam Amritsar Ward No. 49 + Bazaar Jora Pippal, Nagar Nigam Amritsar Ward No. 48 + Gali Kamboj Wali, Nagar Nigam Amritsar Ward No. 48 + Bazaar Khooh Berian, Nagar Nigam Amritsar Ward No. 48 + Gali Aadivasian, Nagar Nigam Amritsar Ward No. 48 + Ram Gali, Jora Pippal, Nagar Nigam Amritsar Ward No. 48 + New Dashmesh Avenue Amritsar Ward No. 50</t>
+          <t>Govt. Elementary Smart School - Gate Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਤਲੀਆਂ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 49 + ਬਜ਼ਾਰ ਜੋੜਾ ਪਿੱਪਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਕੰਬੋਜ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48 + ਬਜ਼ਾਰ ਖੂਹ ਬੇਰੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਆਦੀਵਾਸੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48 + ਰਾਮ ਗਲੀ, ਜੋੜਾ ਪਿੱਪਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 48 + ਨਿਊ ਦਸਮੇਸ਼ ਐਵੀਨਿਊ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਮਾਰਟ ਸਕੂਲ - ਗੇਟ ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D29" s="27" t="n">
@@ -3857,31 +3857,31 @@
         <v>139</v>
       </c>
       <c r="Z29" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA29" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>109</v>
+      </c>
+      <c r="AA29" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB29" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(25.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:25(22.94%) | INC:32(29.36%) | BJP:10 | SAD:4</t>
         </is>
       </c>
       <c r="AC29" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD29" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE29" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Gali Veerowali, Nagar Nigam, Amritsar, Ward No. 49 + Gali Mela Singh, Nagar Nigam Amritsar, Ward No. 49 + Gali Dasodha Wali, Nagar Nigam Amritsar, Ward No. 49 + Hak Malviyan, Nagar Nigam Amritsar, Ward No. 48 + Bazaar Joda Pipal, Nagar Nigam Amritsar, Ward No. 48 + Gali Deva Singh, Nagar Nigam Amritsar, Ward No. 48 + Kucha Shaheed Pehalwan, Nagar Nigam Amritsar, Ward No. 48 + Kucha Dayal Singh, Nagar Nigam Amritsar, Ward No. 49 + Kanak Mandi, Nagar Nigam Amritsar, Ward No. 49 + Lakkar Mandi, Nagar Nigam Amritsar, Ward No. 49 + Chah Basti Ram, Nagar Nigam Amritsar, Ward No. 49 + Chitpurni Chowk, Nagar Nigam Amritsar, Ward No. 49 + Gali Tambaku Kuta, Nagar Nigam Amritsar, Ward No. 49</t>
+          <t>Krishan Kanya Maha Vidyalaya - Namak Mandi, Amritsar</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਵੀਰੋਵਾਲੀ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਮੇਲਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.49 + ਗਲੀ ਦਸੌਧਾ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਹਾਕ ਮਾਲਵੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਬਾਜ਼ਾਰ ਜੋੜਾ ਪਿੱਪਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਦੇਵਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਕੂਚਾ ਸ਼ਹੀਦ ਪਹਿਲਵਾਨ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਕੂਚਾ ਦਿਆਲ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਕਣਕ ਮੰਡੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਲੱਕੜ ਮੰਡੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਚਾਹ ਬਸਤੀ ਰਾਮ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਚਿੱਤਪੁਰਨੀ ਚੌਕ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਤੰਬਾਕੂ ਕੁਟਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49</t>
+          <t>ਕ੍ਰਿਸ਼ਨ ਕੰਨਿਆ ਮਹਾ ਵਿਦਿਆਲਾ - ਨਮਕ ਮੰਡੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D30" s="21" t="n">
@@ -3974,31 +3974,31 @@
         <v>153</v>
       </c>
       <c r="Z30" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA30" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>83</v>
+      </c>
+      <c r="AA30" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB30" s="20" t="inlineStr">
         <is>
-          <t>AAP:4(57.14%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:8(9.64%) | INC:33(39.76%) | BJP:12 | SAD:1</t>
         </is>
       </c>
       <c r="AC30" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD30" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE30" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -4008,12 +4008,12 @@
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>Gali Veere Wali, Nagar Nigam Amritsar, Ward No. 49 + Gali Ichha Ram, Nagar Nigam Amritsar, Ward No. 49 + Shiv Gali, Nagar Nigam Amritsar, Ward No. 49 + Swank Mandi, Nagar Nigam Amritsar, Ward No. 49</t>
+          <t>Krishan Kanya Maha Vidyalaya - Namak Mandi, Amritsar</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਵੀਰੇ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਇੱਛਾਂ ਰਾਮ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਸ਼ਿਵ ਗਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਸਵਾਂਕ ਮੰਡੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49</t>
+          <t>ਕ੍ਰਿਸ਼ਨ ਕੰਨਿਆ ਮਹਾ ਵਿਦਿਆਲਾ - ਨਮਕ ਮੰਡੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D31" s="27" t="n">
@@ -4091,31 +4091,31 @@
         <v>189</v>
       </c>
       <c r="Z31" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA31" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>82</v>
+      </c>
+      <c r="AA31" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB31" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:9(10.98%) | INC:26(31.71%) | BJP:16 | SAD:2</t>
         </is>
       </c>
       <c r="AC31" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD31" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → UNDECIDED</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE31" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Bazaar Chhatrian, Nagar Nigam Amritsar, Ward No. 49 + Namak Mandi, Nagar Nigam Amritsar, Ward No. 49 + Gali Jandi Wali, Nagar Nigam Amritsar, Ward No. 49 + Kandhariyan Gali, Nagar Nigam Amritsar, Ward No. 49</t>
+          <t>Krishan Kanya Maha Vidyalaya - Namak Mandi, Amritsar</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>ਬਾਜ਼ਾਰ ਛੱਤਰੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਨਮਕ ਮੰਡੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਜੰਡੀ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਕੰਧਾਰੀਆਂ ਗਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49</t>
+          <t>ਕ੍ਰਿਸ਼ਨ ਕੰਨਿਆ ਮਹਾ ਵਿਦਿਆਲਾ - ਨਮਕ ਮੰਡੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D32" s="21" t="n">
@@ -4208,7 +4208,7 @@
         <v>181</v>
       </c>
       <c r="Z32" s="21" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="AA32" s="22" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB32" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:21(26.25%) | INC:15(18.75%) | BJP:14 | SAD:2</t>
         </is>
       </c>
       <c r="AC32" s="20" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>Gali Talian Wali, Nagar Nigam Amritsar, Ward No. 49 + Krishna Gali, Nagar Nigam Amritsar, Ward No. 49</t>
+          <t>Krishan Kanya Maha Vidyalaya - Namak Mandi, Amritsar</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਤਲੀਆਂ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.49 + ਕ੍ਰਿਸ਼ਨਾ ਗਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49</t>
+          <t>ਕ੍ਰਿਸ਼ਨ ਕੰਨਿਆ ਮਹਾ ਵਿਦਿਆਲਾ - ਨਮਕ ਮੰਡੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D33" s="27" t="n">
@@ -4325,31 +4325,31 @@
         <v>69</v>
       </c>
       <c r="Z33" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA33" s="23" t="inlineStr">
-        <is>
-          <t>BJP</t>
+        <v>118</v>
+      </c>
+      <c r="AA33" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB33" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:1 | SAD:0</t>
+          <t>AAP:23(19.49%) | INC:35(29.66%) | BJP:13 | SAD:6</t>
         </is>
       </c>
       <c r="AC33" s="26" t="inlineStr">
         <is>
-          <t>Harjinder Singh Thekedar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD33" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → BJP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE33" s="26" t="inlineStr">
         <is>
-          <t>BJP Leading Survey (AAP → BJP → BJP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Chowk Bazar Lachhmansar, Nagar Nigam Amritsar, Ward No. 46 + Gali Gujjran Wali, Nagar Nigam Amritsar, Ward No. 46 + Gali Hansli Wali Kucha Harnam Das, Nagar Nigam Amritsar, Ward No. 46 + Kucha Deen (Neel Wali Gali), Nagar Nigam Amritsar, Ward No. 46 + Kucha Maape Shah Gali Hansli, Nagar Nigam Amritsar, Ward No. 46 + Kucha Deen Ghumiar, Nagar Nigam Amritsar, Ward No. 46 + Kucha Roadways Gali Hansli Wali, Nagar Nigam Amritsar, Ward No. 46 + Bazar Baba Sahib, Nagar Nigam Amritsar, Ward No. 46 + Gali Hansli Wali, Nagar Nigam Amritsar, Ward No. 46 + Gali Budha Singh, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>S.S. Nursery School - Gali Gujran Wali, Amritsar</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>ਚੌਕ ਬਜ਼ਾਰ ਲਛਮਣਸਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਗੁੱਜਰਾਂ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਹੰਸਲੀ ਵਾਲੀ ਕੁਚਾ ਹਰਨਾਮ ਦਾਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਕੁਚਾ ਦੀਨ (ਨੀਲ ਵਾਲੀ ਗਲੀ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਕੁਚਾ ਮਾਪੇ ਸ਼ਾਹ ਗਲੀ ਹੰਸਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਕੁਚਾ ਦੀਨ ਘੁਮਿਆਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਕੁਚਾ ਰੋਡਵੈਂਸ ਗਲੀ ਹੰਸਲੀ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਾਜ਼ਾਰ ਬਾਬਾ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਹੰਸਲੀ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਬੁੱਢਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਐਸ.ਐਸ.ਨਰਸਰੀ ਸਕੂਲ - ਗਾਲੀ ਗੁੱਜਰਾਂ ਵਾਲੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D34" s="21" t="n">
@@ -4442,7 +4442,7 @@
         <v>92</v>
       </c>
       <c r="Z34" s="21" t="n">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="AA34" s="22" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AB34" s="20" t="inlineStr">
         <is>
-          <t>AAP:6(54.55%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:25(28.74%) | INC:17(19.54%) | BJP:13 | SAD:1</t>
         </is>
       </c>
       <c r="AC34" s="20" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="B35" s="26" t="inlineStr">
         <is>
-          <t>Gali Suniarian, Nagar Nigam Amritsar, Ward No. 49 + Gali Beri Wali Katra Mit Singh, Nagar Nigam Amritsar, Ward No. 49 + Katra Dal Singh Bucha Kalian, Nagar Nigam Amritsar, Ward No. 49 + Meti Bazar Katra Mit Singh, Nagar Nigam Amritsar, Ward No. 49 + Katra Dal Singh Bucha Putap Singh, Nagar Nigam Amritsar, Ward No. 49 + Gali Makhaiyan Meti Bazar Katra Mit Singh, Nagar Nigam Amritsar, Ward No. 49 + Bazar Katra Mit Singh Bucha Balwant Singh, Nagar Nigam Amritsar, Ward No. 49 + Katra Mit Singh Pethe Wala Bazar, Nagar Nigam Amritsar, Ward No. 49 + Bazar Pethe Wala Katra Mit Singh, Nagar Nigam Amritsar, Ward No. 49 + Gali Ruda Mal Bhatia Meti Bazar, Nagar Nigam Amritsar, Ward No. 49 + Bazar Katra Mit Singh Gali Tara Chand, Nagar Nigam Amritsar, Ward No. 49 + Gali Bura Attar Meti Bazar, Nagar Nigam Amritsar, Ward No. 49 + Katra Mit Singh Gali Charan Singh, Nagar Nigam Amritsar, Ward No. 49 + Gali Sukha Thanedar Meti Bazar, Nagar Nigam Amritsar, Ward No. 49 + Gali Nikka Meti Bazar, Nagar Nigam Amritsar, Ward No. 49</t>
+          <t>Guru Ramdas Senior Secondary School (Girls) - Chowk Chatti Khuhi, Amritsar</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਸੁਨਿਆਰਿਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਬੇਰੀ ਵਾਲੀ ਕਟੜਾ ਮਿੱਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਕਟੜਾ ਦੱਲ ਸਿੰਘ ਬੂਚਾ ਕਾਲੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.49 + ਮੇਤੀ ਬਾਜ਼ਾਰ ਕਟੜਾ ਮਿੱਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਕਟੜਾ ਦੱਲ ਸਿੰਘ ਬੂਚਾ ਪੁਤਾਪ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਮਖਾਇਆਂ ਮੇਤੀ ਬਾਜ਼ਾਰ ਕਟੜਾ ਮਿੱਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਬਾਜ਼ਾਰ ਕਟੜਾ ਮਿੱਤ ਸਿੰਘ ਬੂਚਾ ਬਲਵੰਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਕਟੜਾ ਮਿੱਤ ਸਿੰਘ ਪੇਠੇ ਵਾਲਾ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਬਾਜ਼ਾਰ ਪੇਠੇ ਵਾਲਾ ਕਟੜਾ ਮਿੱਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਰੂੜਾ ਮੱਲ ਭਾਟੀਆ ਮੇਤੀ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.49 + ਬਾਜ਼ਾਰ ਕਟੜਾ ਮਿੱਤ ਸਿੰਘ ਗਲੀ ਤਾਰਾ ਚੰਦ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਬੂੜਾ ਅੱਤਰ ਮੇਤੀ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਕਟੜਾ ਮਿੱਤ ਸਿੰਘ ਗਲੀ ਚਰਨ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਸੁੱਖਾ ਠਾਣੇਦਾਰ ਮੇਤੀ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਨਿੱਕਾ ਮੇਤੀ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49</t>
+          <t>ਗੁਰੂ ਰਾਮਦਾਸ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਚੌਂਕ ਛੱਤੀ ਖੂਹੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D35" s="27" t="n">
@@ -4559,31 +4559,31 @@
         <v>107</v>
       </c>
       <c r="Z35" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>91</v>
+      </c>
+      <c r="AA35" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB35" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:23(25.27%) | INC:14(15.38%) | BJP:20 | SAD:2</t>
         </is>
       </c>
       <c r="AC35" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD35" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → UNDECIDED</t>
+          <t>AAP → BJP → AAP</t>
         </is>
       </c>
       <c r="AE35" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → UNDECIDED)</t>
+          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Gali Gujjran Wali, Nagar Nigam Amritsar Ward No. 46 + Gali Sangal Wali Nagar Nigam Amritsar, Ward No. 46 + Baba Sahib Chowk Gali Gujjran, Nagar Nigam Amritsar, Ward No. 46 + Gali Gujjran (Gali Jiwan Singh), Nagar Nigam Amritsar Ward No. 46 + Lakkad Mandi Dhab Basti Ram, Nagar Nigam Amritsar, Ward No. 46 + Kucha Dharname Shah, Nagar Nigam Amritsar, Ward No. 46 + Gali Bagh Wali (Kaka Singh), Nagar Nigam Amritsar, Ward No. 46 + Ram Vehra, Nagar Nigam Amritsar Ward No. 46</t>
+          <t>Guru Ramdas Senior Secondary School (Girls) - Chowk Chatti Khuhi, Amritsar</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਗุੱਜਰਾਂ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਸੰਗਲ ਵਾਲੀ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਾਬਾ ਸਾਹਿਬ ਚੌਕ ਗਲੀ ਗੁੱਜਰਾਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਗੁੱਜਰਾਂ (ਗਲੀ ਜੀਵਨ ਸਿੰਘ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਲੱਕੜ ਮੰਡੀ ਢਾਬ ਬਸਤੀ ਰਾਮ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਕੂਚਾ ਧਰਨਾਮੇ ਸ਼ਾਹ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਬਾਗ ਵਾਲੀ (ਕਾਕਾ ਸਿੰਘ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਰਾਮ ਵੇਹੜਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 46</t>
+          <t>ਗੁਰੂ ਰਾਮਦਾਸ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਚੌਂਕ ਛੱਤੀ ਖੂਹੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D36" s="21" t="n">
@@ -4676,7 +4676,7 @@
         <v>18</v>
       </c>
       <c r="Z36" s="21" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="AA36" s="22" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="AB36" s="20" t="inlineStr">
         <is>
-          <t>AAP:7(25.93%) | INC:1(3.7%) | BJP:1 | SAD:0</t>
+          <t>AAP:34(44.74%) | INC:8(10.53%) | BJP:4 | SAD:2</t>
         </is>
       </c>
       <c r="AC36" s="20" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>Chawal Mandi Nagar Nigam Amritsar Ward No. 49 + Bazar Chatti Khuhi, Nagar Nigam Amritsar Ward No. 49 + Gali Mana Wali, Nagar Nigam Amritsar Ward No. 49 + Kucha Hari Ram Bazar Chatti Khuhi, Nagar Nigam Amritsar, Ward No. 49 + Bazar Chatti Khuhi Kucha Hari Dhobian, Nagar Nigam Amritsar, Ward No. 49 + Gali Khooh Wali Katra Dal Singh, Gali Arak Wali, Nagar Nigam Amritsar Ward No. 49 + Katra Dal Singh Arak Wali Gali Nagpal, Nagar Nigam Amritsar, Ward No. 49 + Gali Nagpal, Nagar Nigam Amritsar Ward No. 49 + Gali Arak Wali, Nagar Nigam Amritsar Ward No. 49 + Atta Mandi Chowk Chatti Khuhi Vehra Akalian, Nagar Nigam Amritsar, Ward No. 49 + Gali Chaudhrian Atta Mandi, Nagar Nigam Amritsar Ward No. 49 + Gali Dindi Mall, Nagar Nigam Amritsar Ward No. 49 + Gali Hansli, Nagar Nigam Amritsar Ward No. 49 + Gali Atta Mandi Dera Baba Sham Singh, Nagar Nigam Amritsar Ward No. 49</t>
+          <t>Guru Ramdas Senior Secondary School (Girls) - Chowk Chatti Khuhi, Amritsar</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>ਚਾਵਲ ਮੰਡੀ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49 + ਬਜ਼ਾਰ ਛੱਤੀ ਖੂਹੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49 + ਗਲੀ ਮਾਨਾਂ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49 + ਕੂਚਾ ਹਰੀ ਰਾਮ ਬਾਜ਼ਾਰ ਛੱਤੀ ਖੂਹੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.49 + ਬਜ਼ਾਰ ਛੱਤੀ ਖੂਹੀ ਕੂਚਾ ਹਰੀ ਧੋਬੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.49 + ਗਲੀ ਖੂਹ ਵਾਲੀ ਕਟੜਾ ਦਲ ਸਿੰਘ, ਗਲੀ ਅਰਕ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49 + ਕਟੜਾ ਦਲ ਸਿੰਘ ਅਰਕ ਵਾਲੀ ਗਲੀ ਨਾਗਪਾਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 49 + ਗਲੀ ਨਾਗਪਾਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49 + ਗਲੀ ਅਰਕ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49 + ਆਟਾ ਮੰਡੀ ਚੌਕ ਛੱਤੀ ਖੂਹੀ ਵੇਹੜਾ ਅਕਾਲੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.49 + ਗਲੀ ਚੌਧਰੀਆਂ ਆਟਾ ਮੰਡੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49 + ਗਲੀ ਡਿੰਡੀ ਮੱਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49 + ਗਲੀ ਹੰਸਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49 + ਗਲੀ ਆਟਾ ਮੰਡੀ ਡੇਰਾ ਬਾਬਾ ਸ਼ਾਮ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.49</t>
+          <t>ਗੁਰੂ ਰਾਮਦਾਸ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਚੌਂਕ ਛੱਤੀ ਖੂਹੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D37" s="27" t="n">
@@ -4793,31 +4793,31 @@
         <v>54</v>
       </c>
       <c r="Z37" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA37" s="29" t="inlineStr">
-        <is>
-          <t>TIED</t>
+        <v>96</v>
+      </c>
+      <c r="AA37" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB37" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(25.0%) | INC:1(25.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:26(27.08%) | INC:25(26.04%) | BJP:9 | SAD:2</t>
         </is>
       </c>
       <c r="AC37" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD37" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → TIED</t>
+          <t>AAP → BJP → AAP</t>
         </is>
       </c>
       <c r="AE37" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → TIED)</t>
+          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Guru Ramdas Nagar Gali No. 1 Bhagtanwala Nagar Nigam Amritsar Ward No. 50 + S.D. School Amritsar, Nagar Nigam Amritsar Ward No. 50 + Thatheri Mohalla Bhagtanwala, Nagar Nigam Amritsar Ward No. 50</t>
+          <t>Amritsar - District Mandi Bhawan Office, Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>ਗੁਰੂ ਰਾਮਦਾਸ ਨਗਰ ਗਲੀ ਨੰ.1 ਭਗਤਾਂਵਾਲਾ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50 + ਐਸ.ਡੀ. ਸਕੂਲ ਅੰਮ੍ਰਿਤਸਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50 + ਠਠੇਰੀ ਮੁਹੱਲਾ ਭਗਤਾਂਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਅੰਮ੍ਰਿਤਸਰ - ਜਿਲ੍ਹਾ ਮੰਡੀ ਭਵਨ ਦਫਤਰ, ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D38" s="21" t="n">
@@ -4859,7 +4859,7 @@
       <c r="K38" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="L38" s="30" t="inlineStr">
+      <c r="L38" s="28" t="inlineStr">
         <is>
           <t>SAD</t>
         </is>
@@ -4896,7 +4896,7 @@
       <c r="V38" s="21" t="n">
         <v>73</v>
       </c>
-      <c r="W38" s="28" t="inlineStr">
+      <c r="W38" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -4910,31 +4910,31 @@
         <v>38</v>
       </c>
       <c r="Z38" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA38" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>131</v>
+      </c>
+      <c r="AA38" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB38" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:12(9.16%) | INC:57(43.51%) | BJP:5 | SAD:11</t>
         </is>
       </c>
       <c r="AC38" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD38" s="20" t="inlineStr">
         <is>
-          <t>SAD → INC → AAP</t>
+          <t>SAD → INC → INC</t>
         </is>
       </c>
       <c r="AE38" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (SAD → INC → AAP)</t>
+          <t>INC Leading Survey (SAD → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -4944,12 +4944,12 @@
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>Anusuchit Jati Colony, Bhagtanwala Nagar Nigam Amritsar Ward No. 50 + Gurudware Wali Gali Main Road, Nagar Nigam Amritsar Ward No. 50 + Mohan Flour Mills, Nagar Nigam Amritsar Ward No. 50 + Guru Nanak Chips, Nagar Nigam Amritsar Ward No. 50 + Anusuchit Jati Colony, Main Gali, Nagar Nigam Amritsar Ward No. 50 + Balmik Mandir Bhagtanwala, Nagar Nigam Amritsar Ward No. 50</t>
+          <t>District Mandi Bhawan Office - Bhagtanwala, Amritsar</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>ਅਨੁਸੂਚਿਤ ਜਾਤੀ ਕਲੋਨੀ, ਭਗਤਾਂਵਾਲਾ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50 + ਗੁਰਦੁਆਰੇ ਵਾਲੀ ਗਲੀ ਮੇਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50 + ਮੋਹਣ ਫਲੋਰ ਮਿਲਜ਼, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50 + ਗੁਰੂ ਨਾਨਕ ਚਿਪਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50 + ਅਨੁਸੂਚਿਤ ਜਾਤੀ ਕਲੋਨੀ, ਮੇਨ ਗਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50 + ਬਾਲਮੀਕ ਮੰਦਿਰ ਭਗਤਾਂਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਜਿਲ੍ਹਾ ਮੰਡੀ ਭਵਨ ਦਫਤਰ - ਭਗਤਾਂਵਾਲਾ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D39" s="27" t="n">
@@ -4976,7 +4976,7 @@
       <c r="K39" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L39" s="28" t="inlineStr">
+      <c r="L39" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -5013,7 +5013,7 @@
       <c r="V39" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="W39" s="28" t="inlineStr">
+      <c r="W39" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -5027,31 +5027,31 @@
         <v>171</v>
       </c>
       <c r="Z39" s="27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA39" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>99</v>
+      </c>
+      <c r="AA39" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB39" s="26" t="inlineStr">
         <is>
-          <t>AAP:4(18.18%) | INC:3(13.64%) | BJP:0 | SAD:0</t>
+          <t>AAP:6(6.06%) | INC:49(49.49%) | BJP:4 | SAD:5</t>
         </is>
       </c>
       <c r="AC39" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD39" s="26" t="inlineStr">
         <is>
-          <t>INC → INC → AAP</t>
+          <t>INC → INC → INC</t>
         </is>
       </c>
       <c r="AE39" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (INC → INC → AAP)</t>
+          <t>INC Leading Survey (INC → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Gali Basant Singh Chowk Karedi, Nagar Nigam Amritsar Ward No. 46 + Gali Visakha Singh, Nagar Nigam Amritsar, Ward No. 46 + Gali Karam Singh, Nagar Nigam Amritsar, Ward No. 46 + Gali Mian Singh, Chowk Karedi to Gali Mona Singh, Nagar Nigam Amritsar, Ward No. 46 + Chowk Karedi Gali Mona Singh, Nagar Nigam Amritsar, Ward No. 46 + Gali Sarmukh Singh, Chowk Karedi Nagar Nigam Amritsar Ward No. 46</t>
+          <t>Ramsar Public School - Mahant Mool Singh Colony, Bibeksar Road, Amritsar</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਬਸੰਤ ਸਿੰਘ ਚੌਕ ਕਰੇੜੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਵਿਸਾਖਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਕਰਮ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਮੀਆਂ ਸਿੰਘ, ਚੌਕ ਕਰੇੜੀ ਤੋਂ ਗਲੀ ਮੋਨਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਕਰੇੜੀ ਗਲੀ ਮੋਨਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਸਰਮੁੱਖ ਸਿੰਘ, ਚੌਕ ਕਰੇੜੀ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਰਾਮਸਰ ਪਬਲਿਕ ਸਕੂਲ - ਮਹੰਤ ਮੂਲ ਸਿੰਘ ਕਲੋਨੀ, ਬਿਬੇਕਸਰ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D40" s="21" t="n">
@@ -5144,31 +5144,31 @@
         <v>29</v>
       </c>
       <c r="Z40" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA40" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>54</v>
+      </c>
+      <c r="AA40" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB40" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(16.67%) | INC:1(8.33%) | BJP:1 | SAD:0</t>
+          <t>AAP:10(18.52%) | INC:20(37.04%) | BJP:4 | SAD:1</t>
         </is>
       </c>
       <c r="AC40" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD40" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE40" s="20" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>Kucha Ramgarhian Chowk Baba Bohri Wala, Nagar Nigam Amritsar, Ward No. 46 + Gali Mai Mohno Baba Bohri Wala, Nagar Nigam Amritsar, Ward No. 46 + Main Bazar Chowk Baba Bohri Wala, Nagar Nigam Amritsar Ward No. 46 + Gali Masit Wali Chowk Baba Bohri Wala, Nagar Nigam Amritsar, Ward No. 46 + Gali Uttamgarh Main Bazar Chowk Baba Bohri Wala, Nagar Nigam Amritsar, Ward No. 46 + Akaliyan De Quarter, Nagar Nigam Amritsar Ward No. 46 + Jhaunti Nihang Singh Main Bazar Chowk Baba Bohri Wala, Nagar Nigam Amritsar Ward No. 46 + Gali Phat Wali Main Bazar Chowk Baba Bohri Wala, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Ramsar Public School - Mahant Mool Singh Colony, Bibeksar Road, Amritsar</t>
         </is>
       </c>
       <c r="C41" s="26" t="inlineStr">
         <is>
-          <t>ਕੂਚਾ ਰਾਮਗੜ੍ਹੀਆਂ ਚੌਕ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਮਾਈ ਮੋਹਨੋ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਮੇਨ ਬਜ਼ਾਰ ਚੌਕ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਮਸੀਤ ਵਾਲੀ ਚੌਕ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਉੱਤਮਗੜ੍ਹ ਮੇਨ ਬਜ਼ਾਰ ਚੌਕ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਅਕਾਲੀਆਂ ਦੇ ਕਵਾਟਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਝਾਉਟੀ ਨਿਹੰਗ ਸਿੰਘ ਮੇਨ ਬਜ਼ਾਰ ਚੌਕ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਫੱਟ ਵਾਲੀ ਮੇਨ ਬਜ਼ਾਰ ਚੌਕ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਰਾਮਸਰ ਪਬਲਿਕ ਸਕੂਲ - ਮਹੰਤ ਮੂਲ ਸਿੰਘ ਕਲੋਨੀ, ਬਿਬੇਕਸਰ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D41" s="27" t="n">
@@ -5261,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="Z41" s="27" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="AA41" s="22" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AB41" s="26" t="inlineStr">
         <is>
-          <t>AAP:22(42.31%) | INC:10(19.23%) | BJP:0 | SAD:1</t>
+          <t>AAP:24(30.0%) | INC:16(20.0%) | BJP:5 | SAD:7</t>
         </is>
       </c>
       <c r="AC41" s="26" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Kishangarh, Nagar Nigam Amritsar Ward No. 46 + Gali Baba Deep Singh, Nagar Nigam Amritsar Ward No. 46 + Gali Variyam Singh Wali, Nagar Nigam Amritsar Ward No. 46 + Gali Ishar Singh, Nagar Nigam Amritsar, Ward No. 46 + Chowk Koreri, Nagar Nigam Amritsar Ward No. 46 + Chowk Manna Singh Main Road, Nagar Nigam Amritsar Ward No. 46 + Gali Dasodha Singh, Nagar Nigam Amritsar Ward No. 46 + Gali Budha Beant Singh, Nagar Nigam Amritsar Ward No. 46 + Gali Captain Piara Singh Shaheed, Nagar Nigam Amritsar Ward No. 46 + Gali Mehtab, Nagar Nigam Amritsar, Ward No. 46 + Gali Jawala Singh, Nagar Nigam Amritsar Ward No. 46 + Gali Koreri, Nagar Nigam Amritsar, Ward No. 46 + Gurdwara Ramsar Printing Press Quarter, Nagar Nigam Amritsar, Ward No. 46 + Gurdwara Bibeksar Road Quarters, Nagar Nigam Amritsar, Ward No. 46 + Guru Teg Bahadur Avenue, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Guru Ram Das Khalsa Senior Secondary School, Amritsar (Building-1) - Ramsar Road, Amritsar</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>ਕਿਸ਼ਨਗੜ੍ਹ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਬਾਬਾ ਦੀਪ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਵਰਿਆਮ ਸਿੰਘ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਈਸ਼ਰ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਕੋਰੇੜੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਮੰਨਾ ਸਿੰਘ ਮੇਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਦਸੌਧਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਬੂਢਾ ਬੇਅੰਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਕੈਪਟਨ ਪਿਆਰਾ ਸਿੰਘ ਸ਼ਹੀਦ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਮਹਿਤਾਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਜਵਾਲਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਕੋਰੇੜੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗੁਰਦੁਆਰਾ ਰਾਮਸਰ ਪ੍ਰਿੰਟਿੰਗ ਪ੍ਰੈਸ ਕੁਆਟਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗੁਰਦੁਆਰਾ ਬਿਬੇਕਸਰ ਰੋਡ ਕੁਆਟਰਜ਼, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗੁਰੂ ਤੇਗ ਬਹਾਦਰ ਐਵੀਨਿਊ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਗੁਰੂ ਰਾਮ ਦਾਸ ਖਾਲਸਾ ਸੀਨੀਅਰ ਸਕੈੱਡਰੀ ਸਕੂਲ, ਅੰਮ੍ਰਿਤਸਰ (ਬਿਲਡਿੰਗ-1) - ਰਾਮਸਰ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D42" s="21" t="n">
@@ -5378,16 +5378,16 @@
         <v>36</v>
       </c>
       <c r="Z42" s="21" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="AA42" s="24" t="inlineStr">
         <is>
-          <t>TIED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB42" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(14.29%) | INC:2(14.29%) | BJP:0 | SAD:1</t>
+          <t>AAP:18(24.66%) | INC:24(32.88%) | BJP:2 | SAD:3</t>
         </is>
       </c>
       <c r="AC42" s="20" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="AD42" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → TIED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE42" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → TIED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>Gali Lachhi Wali S-16, Nagar Nigam Amritsar, Ward No. 46 + Haveli Kohlu Wali, Nagar Nigam Amritsar, Ward No. 46 + Gali Darjian Wali, Nagar Nigam Amritsar, Ward No. 46 + Gali Heera Chopri Wali, Nagar Nigam Amritsar, Ward No. 46 + Chowk Kareri, Nagar Nigam Amritsar, Ward No. 46 + Gali Nihal Singh (Chowk Kareri), Nagar Nigam Amritsar, Ward No. 46 + Gali Atar Singh, Nagar Nigam Amritsar, Ward No. 46 + Gali Gopal Singh Wali, Nagar Nigam Amritsar, Ward No. 46 + Gali Lal Singh Wali, Nagar Nigam Amritsar, Ward No. 46 + Gali Mai Wali, Nagar Nigam Amritsar, Ward No. 46 + Gali Nihal Singh Khooh Wali, Nagar Nigam Amritsar, Ward No. 46 + Chowk Moni Haveli Rai Sahib, Nagar Nigam Amritsar, Ward No. 46 + Gali Varpalian, Nagar Nigam Amritsar, Ward No. 46 + Gali Sanpan Wali, Nagar Nigam Amritsar, Ward No. 46 + Chowk Moni Vehra, Nagar Nigam Amritsar, Ward No. 46 + Chowk Moni Atma Ram, Nagar Nigam Amritsar, Ward No. 46 + Gali Jassa Singh, Nagar Nigam Amritsar, Ward No. 46 + Chowk Moni, Nagar Nigam Amritsar, Ward No. 46 + Ramsar Road, Nagar Nigam Amritsar Ward No. 46 + Ramsar Road Chowk Kareri, Nagar Nigam Amritsar Ward No. 46 + Gali Jawahar Singh Chowk Kareri Nagar Nigam Amritsar Ward No. 46 + Bazar Chowk Kareri Moni, Nagar Nigam Amritsar Ward No. 46</t>
+          <t>Guru Ram Das Khalsa Senior Secondary School (Building-1) - Ramsar Road, Amritsar</t>
         </is>
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਲੱਛੀ ਵਾਲੀ ਐਸ-16, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਹਵੇਲੀ ਕੋਹਲੂ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਦਰਜੀਆਂ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਹੀਰਾ ਚੌਪੜੀ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46 + ਚੌਕ ਕਰੇੜੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਨਿਹਾਲ ਸਿੰਘ (ਚੌਕ ਕਰੇੜੀ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਅਤਰ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46 + ਗਲੀ ਗੋਪਾਲ ਸਿੰਘ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਲਾਲ ਸਿੰਘ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਮਾਈ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46 + ਗਲੀ ਨਿਹਾਲ ਸਿੰਘ ਖੂਹ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਮੋਨੀ ਹਵੇਲੀ ਰਾਏ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਵਰਪਾਲੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਸਾਂਪਾਂ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਮੋਨੀ ਵਿਹੜਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਮੋਨੀ ਆਤਮਾ ਰਾਮ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਜੱਸਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਮੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਰਾਮਸਰ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.46 + ਰਾਮਸਰ ਰੋਡ ਚੌਕ ਕਰੇੜੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ,46 + ਗਲੀ ਜਵਾਹਰ ਸਿੰਘ ਚੌਕ ਕਰੇੜੀ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 46 + ਬਾਜ਼ਾਰ ਚੌਕ ਕਰੇੜੀ ਮੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 46</t>
+          <t>ਗੁਰੂ ਰਾਮ ਦਾਸ ਖਾਲਸਾ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ (ਬਿਲਡਿੰਗ-1) - ਰਾਮਸਰ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D43" s="27" t="n">
@@ -5481,7 +5481,7 @@
       <c r="V43" s="27" t="n">
         <v>46</v>
       </c>
-      <c r="W43" s="28" t="inlineStr">
+      <c r="W43" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -5495,31 +5495,31 @@
         <v>21</v>
       </c>
       <c r="Z43" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA43" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>78</v>
+      </c>
+      <c r="AA43" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB43" s="26" t="inlineStr">
         <is>
-          <t>AAP:6(35.29%) | INC:1(5.88%) | BJP:0 | SAD:1</t>
+          <t>AAP:10(12.82%) | INC:37(47.44%) | BJP:1 | SAD:3</t>
         </is>
       </c>
       <c r="AC43" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD43" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → AAP</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE43" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (AAP → INC → AAP)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Gali No. 1 Uttamgarh, Nagar Nigam Amritsar, Ward No. 46 + Gali No. 2 Uttamgarh Chowk Baba Bohri Wala, Nagar Nigam Amritsar, Ward No. 46 + Gali No. 3 Uttamgarh Chowk Baba Bohri Wala, Nagar Nigam Amritsar, Ward No. 46 + Uttamgarh Gali No. 3, Nagar Nigam Amritsar, Ward No. 46 + Gali No. 4 Bazar Baba Bohri Wala, Nagar Nigam Amritsar, Ward No. 46 + Bazar Baba Bohri Wala Bibeksar Road, Nagar Nigam Amritsar, Ward No. 46 + Baba Bohri Wala (Akhara), Nagar Nigam Amritsar, Ward No. 46 + Bibeksar Road Gali Berian Wali Puran Singh Marg, Nagar Nigam Amritsar, Ward No. 46 + Bibeksar Road, Nagar Nigam Amritsar, Ward No. 46 + Mahant Mall Singh Colony, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Guru Ram Das Khalsa Senior Secondary School - Ramsar Road, Amritsar</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਨੰ.1 ਉੱਤਮਗੜ੍ਹ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਨੰ.2 ਉੱਤਮਗੜ੍ਹ ਚੌਕ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਨੰ.3 ਉੱਤਮਗੜ੍ਹ ਚੌਕ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਉੱਤਮਗੜ੍ਹ ਗਲੀ ਨੰ.3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਨੰ. 4 ਬਾਜ਼ਾਰ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਾਜ਼ਾਰ ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ ਬਿਬੇਕਸਰ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਾਬਾ ਬੋਹੜੀ ਵਾਲਾ (ਅਖਾੜਾ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਿਬੇਕਸਰ ਰੋਡ ਗਲੀ ਬੇਰੀਆਂ ਵਾਲੀ ਪੂਰਨ ਸਿੰਘ ਮਾਰਗ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਿਬੇਕਸਰ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਮਹੰਤ ਮੱਲ ਸਿੰਘ ਕਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਗੁਰੂ ਰਾਮ ਦਾਸ ਖਾਲਸਾ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ - ਰਾਮਸਰ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D44" s="21" t="n">
@@ -5612,7 +5612,7 @@
         <v>54</v>
       </c>
       <c r="Z44" s="21" t="n">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="AA44" s="22" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="AB44" s="20" t="inlineStr">
         <is>
-          <t>AAP:8(24.24%) | INC:5(15.15%) | BJP:1 | SAD:0</t>
+          <t>AAP:27(24.77%) | INC:25(22.94%) | BJP:12 | SAD:7</t>
         </is>
       </c>
       <c r="AC44" s="20" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>Gali Khanda Singh Wali Nagar Nigam Amritsar Ward No. 46 + Gali Punjab Singh Chowk Baba Sahib, Nagar Nigam Amritsar, Ward No. 46 + Koochan Singh Haveli Daroga, Nagar Nigam Amritsar, Ward No. 46 + Chowk Baba Sahib Main Bazar, Nagar Nigam Amritsar, Ward No. 46 + Gali Gianiian, Nagar Nigam Amritsar, Ward No. 46 + Gali Jai Singh, Nagar Nigam Amritsar, Ward No. 46 + Gali Pisoorian, Nagar Nigam Amritsar, Ward No. 46 + Dharamshala Doabian, Nagar Nigam Amritsar, Ward No. 46 + Gali Manmohat Singh, Nagar Nigam Amritsar, Ward No. 46 + Gali Narain Singh, Nagar Nigam Amritsar, Ward No. 46 + Chowk Parag Das Main Bazar, Nagar Nigam Amritsar, Ward No. 46 + Gali Nisanchian, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Sri Harkrishan Public School - Chowk Baba Sahib, Parag Das Chowk, Amritsar</t>
         </is>
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਖਮੰਡਾ ਸਿੰਘ ਵਾਲੀ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ.46 + ਗਲੀ ਪੰਜਾਬ ਸਿੰਘ ਚੌਕ ਬਾਬਾ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਕੂਚਨ ਸਿੰਘ ਹਵੇਲੀ ਦਰੋਗਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਬਾਬਾ ਸਾਹਿਬ ਮੇਨ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਗਿਆਨੀਆਾਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਜੈ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਪਿਸੋਰੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਧਰਮਸ਼ਾਲਾ ਦੋਆਬਿਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਮਨਮੋਹਟ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਨਰੈਣ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਪਰਾਗ ਦਾਸ ਮੇਨ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਨਿਸਾਨਚੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਸ੍ਰੀ ਹਰਕ੍ਰਿਸ਼ਨ ਪਬਲਿਕ ਸਕੂਲ - ਚੌਂਕ ਬਾਬਾ ਸਾਹਿਬ, ਪਰਾਗ ਦਾਸ ਚੌਂਕ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D45" s="27" t="n">
@@ -5729,16 +5729,16 @@
         <v>131</v>
       </c>
       <c r="Z45" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA45" s="29" t="inlineStr">
-        <is>
-          <t>TIED</t>
+        <v>85</v>
+      </c>
+      <c r="AA45" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB45" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:0(0.0%) | BJP:0 | SAD:1</t>
+          <t>AAP:33(38.82%) | INC:16(18.82%) | BJP:1 | SAD:5</t>
         </is>
       </c>
       <c r="AC45" s="26" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="AD45" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → TIED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE45" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → TIED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -5763,12 +5763,12 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Gali Wadhau Wali, Nagar Nigam Amritsar, Ward No. 46 + Haveli Ganesh Das, Nagar Nigam Amritsar, Ward No. 46 + Gali Fatehbadia, Nagar Nigam Amritsar, Ward No. 46 + Chaur Gali (Shiv Gali), Nagar Nigam Amritsar, Ward No. 46 + Gali Shan Wali, Nagar Nigam Amritsar, Ward No. 46 + Chowk Baba Sahib, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Shri Harkrishan Public School - Chowk Baba Sahib, Parag Das Chowk, Amritsar</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਵਧਾਊ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਹਵੇਲੀ ਗਨੇਸ਼ ਦਾਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਫਤਿਹਬਾਦੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਰ ਗਲੀ (ਸ਼ਿਵ ਗਲੀ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਸ਼ਾਨ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਬਾਬਾ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਸ਼੍ਰੀ ਹਰਕ੍ਰਿਸ਼ਨ ਪਬਲਿਕ ਸਕੂਲ - ਚੌਂਕ ਬਾਬਾ ਸਾਹਿਬ, ਪਰਾਗ ਦਾਸ ਚੌਂਕ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D46" s="21" t="n">
@@ -5846,7 +5846,7 @@
         <v>60</v>
       </c>
       <c r="Z46" s="21" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="AA46" s="22" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="AB46" s="20" t="inlineStr">
         <is>
-          <t>AAP:10(24.39%) | INC:6(14.63%) | BJP:0 | SAD:0</t>
+          <t>AAP:23(28.75%) | INC:13(16.25%) | BJP:14 | SAD:2</t>
         </is>
       </c>
       <c r="AC46" s="20" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>Kot Harnamdas Gali No. 5, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnamdas Gali No. 6, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnamdas Gali No. 7, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnam Das Gali No. 1, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnam Das Gali No. 2, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnam Das Gali No. 3, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnam Das Gali No. 4, Nagar Nigam Amritsar, Ward No. 42</t>
+          <t>Govt. Senior Secondary School (Boys) Kot Baba Deep Singh - Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਹਰਨਾਮਦਾਸ ਗਲੀ ਨੰ.5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮਦਾਸ ਗਲੀ ਨੰ.6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮਦਾਸ ਗਲੀ.ਨੰ.7, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ.1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ.2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ.3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ.4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42</t>
+          <t>ਸਰਕਾਰੀ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ (ਲੜਕੇ) ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D47" s="27" t="n">
@@ -5963,31 +5963,31 @@
         <v>70</v>
       </c>
       <c r="Z47" s="27" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA47" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>54</v>
+      </c>
+      <c r="AA47" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB47" s="26" t="inlineStr">
         <is>
-          <t>AAP:23(25.56%) | INC:29(32.22%) | BJP:6 | SAD:3</t>
+          <t>AAP:19(35.19%) | INC:13(24.07%) | BJP:2 | SAD:1</t>
         </is>
       </c>
       <c r="AC47" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD47" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE47" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -5997,12 +5997,12 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Guru Nanak Pura Bazar No. 6, Nagar Nigam Amritsar, Ward No. 42 + Guru Nanak Pura Bazar No. 7 Barsati Wala Nala, Nagar Nigam Amritsar, Ward No. 42 + Krishna Nagar Near Purani Chungi Nagar Nigam Amritsar Ward No. 42</t>
+          <t>Govt. Senior Secondary School (Boys) Kot Baba Deep Singh - Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>ਗੁਰੂ ਨਾਨਕ ਪੁਰਾ ਬਾਜ਼ਾਰ ਨੰ.6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਗੁਰੂ ਨਾਨਕ ਪੁਰਾ ਬਾਜ਼ਾਰ ਨੰ.7 ਬਰਸਾਤੀ ਵਾਲਾ ਨਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕ੍ਰਿਸ਼ਨਾ ਨਗਰ ਨੇੜੇ ਪੁਰਾਣੀ ਚੁੰਗੀ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 42</t>
+          <t>ਸਰਕਾਰੀ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ (ਲੜਕੇ) ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D48" s="21" t="n">
@@ -6080,31 +6080,31 @@
         <v>50</v>
       </c>
       <c r="Z48" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="24" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>77</v>
+      </c>
+      <c r="AA48" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB48" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:25(32.47%) | INC:20(25.97%) | BJP:1 | SAD:3</t>
         </is>
       </c>
       <c r="AC48" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD48" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE48" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>Kot Harnam Das Gali No. 8, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnam Das Gali No. 9, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnam Das Gali No. 10, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnam Das Gali No. 11, Nagar Nigam Amritsar, Ward No. 42 + Main Bazar Kot Harnam Das, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnam Das Gali No. 12, Nagar Nigam Amritsar, Ward No. 42 + Kot Harnam Das Gali No. 13, Nagar Nigam Amritsar, Ward No. 42</t>
+          <t>Govt. Senior Secondary School (Boys) Kot Baba Deep Singh - Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ. 8, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ. 9, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ. 10, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ. 11, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਮੇਨ ਬਾਜ਼ਾਰ ਕੋਟ ਹਰਨਾਮ ਦਾਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ. 12, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਗਲੀ ਨੰ. 13, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42</t>
+          <t>ਸਰਕਾਰੀ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ (ਲੜਕੇ) ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D49" s="27" t="n">
@@ -6197,31 +6197,31 @@
         <v>38</v>
       </c>
       <c r="Z49" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>86</v>
+      </c>
+      <c r="AA49" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB49" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:20(23.26%) | INC:25(29.07%) | BJP:3 | SAD:7</t>
         </is>
       </c>
       <c r="AC49" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD49" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE49" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -6231,12 +6231,12 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Kot Ralia Ram Sultanwind Road (Right Side), Nagar Nigam Amritsar, Ward No. 47</t>
+          <t>Govt. Senior Secondary School (Boys) Kot Baba Deep Singh - Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਰਲੀਆ ਰਾਮ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ (ਸੱਜਾ ਪਾਸਾ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47</t>
+          <t>ਸਰਕਾਰੀ ਸੀਨੀਅਰ ਸਕੈਂਡਰੀ ਸਕੂਲ (ਲੜਕੇ) ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D50" s="21" t="n">
@@ -6300,7 +6300,7 @@
       <c r="V50" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="W50" s="28" t="inlineStr">
+      <c r="W50" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -6314,31 +6314,31 @@
         <v>9</v>
       </c>
       <c r="Z50" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="24" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>67</v>
+      </c>
+      <c r="AA50" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB50" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:21(31.34%) | INC:13(19.4%) | BJP:3 | SAD:6</t>
         </is>
       </c>
       <c r="AC50" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD50" s="20" t="inlineStr">
         <is>
-          <t>AAP → INC → PENDING</t>
+          <t>AAP → INC → AAP</t>
         </is>
       </c>
       <c r="AE50" s="20" t="inlineStr">
         <is>
-          <t>AAP → INC → Survey Pending</t>
+          <t>AAP Regained from INC (AAP → INC → AAP)</t>
         </is>
       </c>
     </row>
@@ -6348,12 +6348,12 @@
       </c>
       <c r="B51" s="26" t="inlineStr">
         <is>
-          <t>Kot Ralia Ram Sultanwind Road (Sajja Pasa), Nagar Nigam Amritsar, Ward No. 47 + Kot Baba Deep Singh Gali No. 1, Nagar Nigam Amritsar, Ward No. 47 + Abadi Mahant Lachhman Das, Nagar Nigam Amritsar, Ward No. 47</t>
+          <t>Govt. Senior Secondary School (Boys) Kot Baba Deep Singh - Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਰਲੀਆ ਰਾਮ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ (ਸੱਜਾ ਪਾਸਾ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਗਲੀ ਨੰ. 1,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਆਬਾਦੀ ਮਹੰਤ ਲਛਮਣ ਦਾਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47</t>
+          <t>ਸਰਕਾਰੀ ਸੀਨੀਅਰ ਸਕੈੰਡਰੀ ਸਕੂਲ (ਲੜਕੇ) ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D51" s="27" t="n">
@@ -6431,31 +6431,31 @@
         <v>31</v>
       </c>
       <c r="Z51" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA51" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>50</v>
+      </c>
+      <c r="AA51" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB51" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:11(22.0%) | INC:15(30.0%) | BJP:3 | SAD:3</t>
         </is>
       </c>
       <c r="AC51" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD51" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE51" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -6465,12 +6465,12 @@
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Rajhe di Haveli Guru Nanakpura Bazar, Nagar Nigam Amritsar, Ward No. 42 + Rajhe di Haveli, Nagar Nigam Amritsar, Ward No. 42 + Abai Guru Nanakpura Bazar No. 4, Nagar Nigam Amritsar, Ward No. 42</t>
+          <t>M.G.S. Memorial Antarjami Model School - Antarjami Colony, Amritsar</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>ਰਾਝੇ ਦੀ ਹਵੇਲੀ ਗੁਰੂ ਨਾਨਕਪੁਰਾ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਰਾਝੇ ਦੀ ਹਵੇਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਅਬਾਈ ਗੁਰੂ ਨਾਨਕਪੁਰਾ ਬਾਜ਼ਾਰ ਨੰ.4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42</t>
+          <t>ਐਮ.ਜੀ.ਐਸ. ਮੈਮੋਰੀਅਲ, ਅੰਤਰਜਾਮੀ ਮਾਡਲ ਸਕੂਲ - ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D52" s="21" t="n">
@@ -6548,31 +6548,31 @@
         <v>107</v>
       </c>
       <c r="Z52" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA52" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>104</v>
+      </c>
+      <c r="AA52" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB52" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:25(24.04%) | INC:30(28.85%) | BJP:3 | SAD:10</t>
         </is>
       </c>
       <c r="AC52" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD52" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE52" s="20" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -6582,12 +6582,12 @@
       </c>
       <c r="B53" s="26" t="inlineStr">
         <is>
-          <t>Gurudwara Baba Jeevan Singh Guru Nanakpura Gali No. 7, Nagar Nigam Amritsar, Ward No. 47 + Gurudwara Baba Jeevan Singh Guru Nanakpura Gali No. 8, Nagar Nigam Amritsar, Ward No. 47 + Gurudwara Baba Jeevan Singh Guru Nanak Pura Gali No. 7, Nagar Nigam Amritsar, Ward No. 47 + Abadi Guru Nanak Pura Jujhari Abadi Sarwar Pura, Nagar Nigam Amritsar, Ward No. 47 + Abadi Guru Nanakpura Nede Ranjhe Di Haveli Gali No. 7, Nagar Nigam Amritsar, Ward No. 47</t>
+          <t>M.G.S. Memorial, Antarjami Model School - Antarjami Colony, Amritsar</t>
         </is>
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>ਗੁਰਦੁਆਰਾ ਬਾਬਾ ਜੀਵਨ ਸਿੰਘ ਗੁਰੂ ਨਾਨਕਪੁਰਾ ਗਲੀ ਨੰ. 7, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਗੁਰਦੁਆਰਾ ਬਾਬਾ ਜੀਵਨ ਸਿੰਘ ਗੁਰੂ ਨਾਨਕਪੁਰਾ ਗਲੀ ਨੰ. 8, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਗੁਰਦੁਆਰਾ ਬਾਬਾ ਜੀਵਨ ਸਿੰਘ ਗੁਰੂ ਨਾਨਕ ਪੁਰਾ ਗਲੀ ਨੰ. 7, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਅਬਾਦੀ ਗੁਰੂ ਨਾਨਕ ਪੁਰਾ ਜੁਝਾਰੀ ਅਬਾਦੀ ਸਰਵਰ ਪੁਰਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਅਬਾਦੀ ਗੁਰੂ ਨਾਨਕਪੁਰਾ ਨੇੜੇ ਰਾਂਝੇ ਦੀ ਹਵੇਲੀ ਗਲੀ ਨੰ. 7, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47</t>
+          <t>ਐਮ.ਜੀ.ਐਸ. ਮੈਮੋਰੀਅਲ, ਅੰਤਰਜਾਮੀ ਮਾਡਲ ਸਕੂਲ - ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D53" s="27" t="n">
@@ -6665,16 +6665,16 @@
         <v>52</v>
       </c>
       <c r="Z53" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA53" s="29" t="inlineStr">
-        <is>
-          <t>TIED</t>
+        <v>99</v>
+      </c>
+      <c r="AA53" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB53" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:1(50.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:42(42.42%) | INC:12(12.12%) | BJP:3 | SAD:6</t>
         </is>
       </c>
       <c r="AC53" s="26" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="AD53" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → TIED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE53" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → TIED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -6699,12 +6699,12 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Antarjami Colony, Gali No. 6, Nagar Nigam Amritsar, Ward No. 42 + Antarjami Colony, Gali No. 2, Nagar Nigam Amritsar, Ward No. 42 + Antarjami Colony, Gali No. 4, Nagar Nigam Amritsar, Ward No. 42 + Antarjami Colony, Gali No. 5, Nagar Nigam Amritsar, Ward No. 42 + Antarjami Colony, Gali No. 7, Nagar Nigam Amritsar, Ward No. 42 + Antarjami Colony, Gali No. 8, Nagar Nigam Amritsar, Ward No. 42 + Antarjami Colony, Gali No. 9, Nagar Nigam Amritsar, Ward No. 42 + Antarjami Colony, Gali No. 3, Nagar Nigam Amritsar, Ward No. 42</t>
+          <t>M.G.S. Memorial, Antarjami Model School - Antarjami Colony, Amritsar</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 7, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 8, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 9, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42</t>
+          <t>ਐਮ.ਜੀ.ਐਸ. ਮੈਮੋਰੀਅਲ, ਅੰਤਰਜਾਮੀ ਮਾਡਲ ਸਕੂਲ - ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D54" s="21" t="n">
@@ -6782,31 +6782,31 @@
         <v>66</v>
       </c>
       <c r="Z54" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA54" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>84</v>
+      </c>
+      <c r="AA54" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB54" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:24(28.57%) | INC:21(25.0%) | BJP:2 | SAD:8</t>
         </is>
       </c>
       <c r="AC54" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD54" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE54" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -6816,12 +6816,12 @@
       </c>
       <c r="B55" s="26" t="inlineStr">
         <is>
-          <t>Antarjami Colony, Gali No. 1, Nagar Nigam Amritsar, Ward No. 42 + New Antarjami Colony, Gali No. 2, Nagar Nigam Amritsar, Ward No. 42 + New Antarjami Colony, Gali No. 1, Nagar Nigam Amritsar, Ward No. 42 + Main Bazar Antarjami Colony, Gali No. 1, Nagar Nigam Amritsar, Ward No. 42 + Baba Deep Singh Avenue Chatiwind Nala Taran Taran Road, Nagar Nigam Amritsar Ward No. 47</t>
+          <t>M.G.S. Memorial Antarjami Model School - Antarjami Colony, Amritsar</t>
         </is>
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਨਿਊ ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਨਿਊ ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਮੇਨ ਬਜਾਰ ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਗਲੀ ਨੰ 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਐਵੀਨਿਊ ਚਾਟੀਵਿੰਡ ਨਾਲਾ ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 47</t>
+          <t>ਐਮ.ਜੀ.ਐਸ. ਮੈਮੋਰੀਅਲ, ਅੰਤਰਜਾਮੀ ਮਾਡਲ ਸਕੂਲ - ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D55" s="27" t="n">
@@ -6899,31 +6899,31 @@
         <v>36</v>
       </c>
       <c r="Z55" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>123</v>
+      </c>
+      <c r="AA55" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB55" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:29(23.58%) | INC:41(33.33%) | BJP:7 | SAD:2</t>
         </is>
       </c>
       <c r="AC55" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD55" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE55" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -6933,12 +6933,12 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Gali Masit Wali, Nagar Nigam, Amritsar, Ward No. 46 + Baba Deep Singh Colony, Nagar Nigam Amritsar, Ward No. 46 + Chowk Baba Deep Sahib, Nagar Nigam. Amritsar, Ward No. 46</t>
+          <t>Sri Guru Ramdas Khalsa Senior Secondary School (Building No. 2) - Ramsar Road, Amritsar</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਮਸੀਤ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਕਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਂਕ ਬਾਬਾ ਦੀਪ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ. ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਸ੍ਰੀ ਗੁਰੂ ਰਾਮਦਾਸ ਖਾਲਸਾ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਬਿਲਡਿੰਗ ਨੰ. 2) - ਰਾਮਸਰ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D56" s="21" t="n">
@@ -7016,31 +7016,31 @@
         <v>27</v>
       </c>
       <c r="Z56" s="21" t="n">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="AA56" s="24" t="inlineStr">
         <is>
-          <t>UNDECIDED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB56" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:15(13.27%) | INC:44(38.94%) | BJP:10 | SAD:4</t>
         </is>
       </c>
       <c r="AC56" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD56" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE56" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="B57" s="26" t="inlineStr">
         <is>
-          <t>Abadi Fire Brigade, Nagar Nigam, Amritsar, Ward No. 48 + Gali Brahm Acharya Gill Wali Gate, Nagar Nigam Amritsar, Ward No. 48 + Gali Gor Kanda Guru Arjan Dev Gali, Nagar Nigam Amritsar, Ward No. 48 + Kucha Gujran Chowk Jai Singh, Nagar Nigam Amritsar, Ward No. 48 + Chowk Jai Singh, Nagar Nigam Amritsar, Ward No. 48 + Kucha Kahan Singh, Nagar Nigam Amritsar, Ward No. 48</t>
+          <t>Jai Ram Das Senior Secondary School - Chowk Lachhmansar, Amritsar</t>
         </is>
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>ਆਬਾਦੀ ਫਾਇਰ ਬ੍ਰਿਗੇਡ,ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਬ੍ਰਹਮ ਅਚਾਰੀਆ ਗਿੱਲ ਵਾਲੀ ਗੇਟ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਗੋਰ ਕੰਡਾ ਗੁਰੂ ਅਰਜਨ ਦੇਵ ਗਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਕੂਚਾ ਗੁਜਰਾਂ ਚੌਕ ਜੈ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਚੌਕ ਜੈ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਕੂਚਾ ਕਾਹਨ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48</t>
+          <t>ਜੈ ਰਾਮ ਦਾਸ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਚੌਂਕ ਲਛਮਣਸਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D57" s="27" t="n">
@@ -7133,7 +7133,7 @@
         <v>9</v>
       </c>
       <c r="Z57" s="27" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="AA57" s="22" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="AB57" s="26" t="inlineStr">
         <is>
-          <t>AAP:24(35.82%) | INC:9(13.43%) | BJP:0 | SAD:0</t>
+          <t>AAP:30(35.71%) | INC:16(19.05%) | BJP:7 | SAD:1</t>
         </is>
       </c>
       <c r="AC57" s="26" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Chauk Lachhmansar, Nagar Nigam Amritsar, Ward No. 48 + Bakkar Wali Haveli, Nagar Nigam Amritsar, Ward No. 48 + Gali Bhaktiya, Nagar Nigam, Amritsar, Ward No. 48 + Gali Khajoor Wali, Nagar Nigam Amritsar, Ward No. 48 + Gali Khalsa Wali (Chauk Chabutra), Nagar Nigam, Amritsar, Ward No. 48 + Gali Leharaan, Nagar Nigam Amritsar, Ward No. 48 + Gali Kamboj, Nagar Nigam Amritsar, Ward No. 48 + Gali Saleta Wali, Nagar Nigam Ward No. 48 Amritsar</t>
+          <t>Govt. Elementary School - Chowk Lachhmansar, Amritsar</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>ਚੌਕ ਲੱਛਮਣਸਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਬੱਕਰ ਵਾਲੀ ਹਵੇਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਭਕਟੀਆ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਖਜੂਰ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਖਾਲਸਾ ਵਾਲੀ (ਚੌਕ ਚਬੂਤਰਾ), ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਲੇਹਾਰਾਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਕੰਬੋਜ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਸਲੇਟਾ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ. 48 ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਚੌਂਕ ਲੱਛਮਣਸਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D58" s="21" t="n">
@@ -7250,7 +7250,7 @@
         <v>16</v>
       </c>
       <c r="Z58" s="21" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AA58" s="22" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AB58" s="20" t="inlineStr">
         <is>
-          <t>AAP:10(26.32%) | INC:3(7.89%) | BJP:0 | SAD:0</t>
+          <t>AAP:32(33.68%) | INC:22(23.16%) | BJP:4 | SAD:4</t>
         </is>
       </c>
       <c r="AC58" s="20" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="B59" s="26" t="inlineStr">
         <is>
-          <t>Chonk Chabutra, Nagar Nigam Amritsar, Ward No. 48 + Kucha Salamat Singh, Nagar Nigam Amritsar, Ward No. 48 + Gali Abdullah Khan, Nagar Nigam Amritsar, Ward No. 48 + Bazar Ambalwalian, Nagar Nigam Amritsar, Ward No. 48</t>
+          <t>Govt. Elementary School - Chowk Lachhmansar, Amritsar</t>
         </is>
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>ਚੌਂਕ ਚਬੂਤਰਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਕੂਚਾ ਸਲਾਮਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਅਬਦੁੱਲਾ ਖਾਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਬਜ਼ਾਰ ਅੰਬਲਵਾਲੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਚੌਂਕ ਲਛਮਣਸਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D59" s="27" t="n">
@@ -7316,7 +7316,7 @@
       <c r="K59" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="L59" s="30" t="inlineStr">
+      <c r="L59" s="28" t="inlineStr">
         <is>
           <t>SAD</t>
         </is>
@@ -7353,7 +7353,7 @@
       <c r="V59" s="27" t="n">
         <v>51</v>
       </c>
-      <c r="W59" s="28" t="inlineStr">
+      <c r="W59" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -7367,31 +7367,31 @@
         <v>103</v>
       </c>
       <c r="Z59" s="27" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA59" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>77</v>
+      </c>
+      <c r="AA59" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB59" s="26" t="inlineStr">
         <is>
-          <t>AAP:9(20.93%) | INC:3(6.98%) | BJP:3 | SAD:1</t>
+          <t>AAP:5(6.49%) | INC:40(51.95%) | BJP:1 | SAD:4</t>
         </is>
       </c>
       <c r="AC59" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD59" s="26" t="inlineStr">
         <is>
-          <t>SAD → INC → AAP</t>
+          <t>SAD → INC → INC</t>
         </is>
       </c>
       <c r="AE59" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (SAD → INC → AAP)</t>
+          <t>INC Leading Survey (SAD → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7401,12 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Haveli Panna Singh, Nagar Nigam Amritsar, Ward No. 48 + Bazaar Chowk Moni, Nagar Nigam Amritsar, Ward No. 46 + Mandi Bhagat Singh Road, Nagar Nigam Amritsar, Ward No. 46 + Bazaar Androon Chatiwind, Nagar Nigam Amritsar, Ward No. 46 + Bazaar Loharan, Nagar Nigam Amritsar, Ward No. 48 + Gali Ali Munshi Gill Wali Gate, Nagar Nigam Amritsar, Ward No. 48 + Gali Mast Khooh, Nagar Nigam Amritsar, Ward No. 48</t>
+          <t>Govt. Elementary School - Chowk Lachhmansar, Amritsar</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>ਹਵੇਲੀ ਪੰਨਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਬਾਜ਼ਾਰ ਚੌਕ ਮੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਮੰਡੀ ਭਗਤ ਸਿੰਘ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਾਜ਼ਾਰ ਅੰਦਰੂਨ ਚਾਟੀਵਿੰਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਾਜ਼ਾਰ ਲੋਹਾਰਾਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਅਲੀ ਮੁਨਸ਼ੀ ਗਿੱਲ ਵਾਲੀ ਗੇਟ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਮਸਤ ਖੂਹ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਚੌਕ ਲਛਮਣਸਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D60" s="21" t="n">
@@ -7470,7 +7470,7 @@
       <c r="V60" s="21" t="n">
         <v>31</v>
       </c>
-      <c r="W60" s="28" t="inlineStr">
+      <c r="W60" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -7484,31 +7484,31 @@
         <v>60</v>
       </c>
       <c r="Z60" s="21" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA60" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>90</v>
+      </c>
+      <c r="AA60" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB60" s="20" t="inlineStr">
         <is>
-          <t>AAP:10(28.57%) | INC:7(20.0%) | BJP:0 | SAD:1</t>
+          <t>AAP:22(24.44%) | INC:24(26.67%) | BJP:6 | SAD:6</t>
         </is>
       </c>
       <c r="AC60" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD60" s="20" t="inlineStr">
         <is>
-          <t>AAP → INC → AAP</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE60" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (AAP → INC → AAP)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -7518,12 +7518,12 @@
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>Ghar Maliyan De Sakatri Bagh, Nagar Nigam, Amritsar, Ward No. 50 + Lal Quarters Sakatri Bagh Bahar Var Anusuchit Jati Colony, Gilwali Gate, Nagar Nigam Amritsar, Ward No. 50, Amritsar + Baba Khadak Singh Baba Darshan Singh, I.T.I Vidyak Sanstha, Nagar Nigam Amritsar, Ward No. 47 + Gawala Enclave Kot Baba Deep Singh, Nagar Nigam Amritsar, Ward No. 47 + Tuttia Baba Sahaiya Singh Taran Taran Road, Nagar Nigam Amritsar, Ward No. 47 + Outside Gillwali Gate Main Road Nede, Nagar Nigam Amritsar, Ward No. 50</t>
+          <t>Basic Education Center High School - Kot Baba Deep Singh, Amritsar</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>ਘਰ ਮਾਲੀਆਂ ਦੇ ਸਕੱਤਰੀ ਬਾਗ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਲਾਲ ਕੁਆਟਰ ਸਕਤਰੀ ਬਾਗ ਬਾਹਰ ਵਾਰ ਅਨੁਸੂਚਿਤ ਜਾਤੀ ਕਲੋਨੀ, ਗਿਲਵਾਲੀ ਗੇਟ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 50, ਅੰਮ੍ਰਿਤਸਰ + ਬਾਬਾ ਖੜਕ ਸਿੰਘ ਬਾਬਾ ਦਰਸ਼ਨ ਸਿੰਘ,ਆਈ.ਟੀ,ਆਈ ਵਿਦਿਅਕ ਸੰਸਥਾ.ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਗਾਵਾਲਾ ਇਨਕਲੇਵ ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਟੁੱਟੀਆ ਬਾਬਾ ਸਹਾਇਆ ਸਿੰਘ ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਆਊਟ ਸਾਇਡ ਗਿੱਲਵਾਲੀ ਗੇਟ ਮੇਨ ਰੋਡ ਨੇੜੇ,, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਬੇਸਿਕ ਸਿੱਖਿਆ ਕੇਂਦਰ ਹਾਈ ਸਕੂਲ - ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D61" s="27" t="n">
@@ -7601,31 +7601,31 @@
         <v>127</v>
       </c>
       <c r="Z61" s="27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA61" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>83</v>
+      </c>
+      <c r="AA61" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB61" s="26" t="inlineStr">
         <is>
-          <t>AAP:4(28.57%) | INC:1(7.14%) | BJP:1 | SAD:1</t>
+          <t>AAP:9(10.84%) | INC:30(36.14%) | BJP:13 | SAD:2</t>
         </is>
       </c>
       <c r="AC61" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD61" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE61" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -7635,12 +7635,12 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Kachhe Pakke Ghar, Anusuchit Jati Colony, Dera Adhukiya Das, Nagar Nigam Amritsar, Ward No. 50, Amritsar. + Double Steri 24-Quarter, Nagar Nigam, Amritsar, Ward No. 50 + Shiv Bhola Nath Mandir, Nagar Nigam Amritsar, Ward No. 50 + Aare Wali, Nagar Nigam Amritsar, Ward No. 50 + Lakshmi Avenue Nede State Bank Bhagta Wala Road, Nagar Nigam Amritsar, Ward No. 50 + Pichhla Pasa Guru Ramdas Atta Mill Nagar Nigam Amritsar, Ward No. 50 + Tarsem Lal Dukanedar Ate Guru Ram Das Atta Mill, Nagar Nigam Amritsar, Ward No. 50 + Baba Jeevan Singh Colony, Railway Line Bhagta Wala Road, Nagar Nigam Amritsar, Ward No. 50 + Center Warehouse Railway Paar Nede Dana Mandi Bhagta Wala Road, Nagar Nigam Amritsar, Ward No. 50</t>
+          <t>Basic Sikhiya Kendra High School - Kot Baba Deep Singh, Amritsar</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>ਕੱਚੇ ਪੱਕੇ ਘਰ, ਅਨੁਸੂਚਿਤ ਜਾਤੀ ਕਲੋਨੀ, ਡੇਰਾ ਅਧੁਕਿਆ ਦਾਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 50, ਅੰਮ੍ਰਿਤਸਰ. + ਡਬਲ ਸਟੇਰੀ 24-ਕੁਆਟਰ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਸ਼ਿਵ ਭੋਲਾ ਨਾਥ ਮੰਦਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਆਰੇ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਲਕਸ਼ਮੀ ਐਵਿਨਿਊ ਨੇੜੇ ਸਟੇਟ ਬੈਂਕ ਭਗਤਾ ਵਾਲਾ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਪਿਛਲਾ ਪਾਸਾ ਗੁਰੂ ਰਾਮਦਾਸ ਆਟਾ ਮਿੱਲ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਤਰਸੇਮ ਲਾਲ ਦੁਕਾਨਦਾਰ ਅਤੇ ਗੁਰੂ ਰਾਮ ਦਾਸ ਆਟਾ ਮਿੱਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਬਾਬਾ ਜੀਵਨ ਸਿੰਘ ਕਲੋਨੀ, ਰੇਲਵੇ ਲਾਈਨ ਭਗਤਾ ਵਾਲਾ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਸένटर ਵੇਅਰ ਹਾਊਸ ਰੇਲਵੇ ਪਾਰ ਨੇੜੇ ਦਾਣਾ ਮੰਡੀ ਭਗਤਾ ਵਾਲਾ ਰੋਡ, ਨਗਰ ਨਿਗਮ. ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਬੇਸਿਕ ਸਿੱਖਿਆ ਕੇਂਦਰ ਹਾਈ ਸਕੂਲ - ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D62" s="21" t="n">
@@ -7704,7 +7704,7 @@
       <c r="V62" s="21" t="n">
         <v>73</v>
       </c>
-      <c r="W62" s="28" t="inlineStr">
+      <c r="W62" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -7718,16 +7718,16 @@
         <v>17</v>
       </c>
       <c r="Z62" s="21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA62" s="28" t="inlineStr">
+        <v>93</v>
+      </c>
+      <c r="AA62" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
       </c>
       <c r="AB62" s="20" t="inlineStr">
         <is>
-          <t>AAP:5(27.78%) | INC:6(33.33%) | BJP:0 | SAD:0</t>
+          <t>AAP:19(20.43%) | INC:25(26.88%) | BJP:10 | SAD:5</t>
         </is>
       </c>
       <c r="AC62" s="20" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>Karkhana Bazar, Nagar Nigam Amritsar, Ward No. 46 + Purani Lakkad Mandi, Nagar Nigam Amritsar, Ward. 46 + Neevi Gali Nede Purani Lakkad Mandi, Nagar Nigam, Amritsar, Ward No. 46 + Valtoiyan Wali Gali, Mahana Singh Road, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Govt. Secondary School (Girls) - Mahna Singh Road, Amritsar</t>
         </is>
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>ਕਾਰਖਾਨਾ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਪੁਰਾਣੀ ਲੱਕੜ ਮੰਡੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ. 46 + ਨੀਂਵੀ ਗਲੀ ਨੇੜੇ ਪੁਰਾਣੀ ਲੱਕੜ ਮੰਡੀ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਵਲਟੋਈਆਂ ਵਾਲੀ ਗਲੀ, ਮਾਹਨਾ ਸਿੰਘ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ, (ਲੜਕੀਆਂ) - ਮਾਹਣਾ ਸਿੰਘ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D63" s="27" t="n">
@@ -7835,31 +7835,31 @@
         <v>20</v>
       </c>
       <c r="Z63" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA63" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>88</v>
+      </c>
+      <c r="AA63" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB63" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:14(15.91%) | INC:34(38.64%) | BJP:7 | SAD:1</t>
         </is>
       </c>
       <c r="AC63" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD63" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE63" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -7869,12 +7869,12 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Karkhana Bazar (Near Chauli Chowk), Nagar Nigam Amritsar, Ward No. 46 + Gali Phat Wali, Nagar Nigam Amritsar, Ward No. 46 + Gali Madan Lal Bhatia, Nagar Nigam Amritsar, Ward No. 46 + Basti Isaiyan, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Govt. Secondary School (Girls) - Mahna Singh Road, Amritsar</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>ਕਾਰਖਾਨਾ ਬਾਜ਼ਾਰ (ਨੇੜੇ ਚੌਲੀ ਚੌਕ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਫੱਟ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਮਦਨ ਲਾਲ ਭਾਟੀਆ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਸਤੀ ਇਸਾਈਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ, (ਲੜਕੀਆਂ) - ਮਾਹਣਾ ਸਿੰਘ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D64" s="21" t="n">
@@ -7952,7 +7952,7 @@
         <v>35</v>
       </c>
       <c r="Z64" s="21" t="n">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="AA64" s="22" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB64" s="20" t="inlineStr">
         <is>
-          <t>AAP:7(26.92%) | INC:1(3.85%) | BJP:0 | SAD:0</t>
+          <t>AAP:32(34.41%) | INC:17(18.28%) | BJP:1 | SAD:10</t>
         </is>
       </c>
       <c r="AC64" s="20" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B65" s="26" t="inlineStr">
         <is>
-          <t>Gali Mahna Singh, Nagar Nigam Amritsar, Ward No. 46 + Mahna Singh Road, Nagar Nigam Amritsar, Ward No. 46 + Bazar Bagh Jallian Wala, Nagar Nigam, Amritsar, Ward No. 46 + Haveli Mahanta Di (Nede Dholi Chowk), Nagar Nigam, Amritsar, Ward No. 46 + Haveli Mai Toni (Nede Dakkhana Dholi Chowk), Nagar Nigam Amritsar, Ward No. 46 + Singhariyan Wali Gali (Nede Dakkhana Dholi Chowk), Nagar Nigam Amritsar, Ward No. 46 + Haveli Babu Ram (Nede Dholi Chowk), Nagar Nigam Amritsar, Ward No. 46 + Gali Dasaunda Singh, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Government Secondary School, (Girls) - Mahna Singh Road, Amritsar</t>
         </is>
       </c>
       <c r="C65" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਮਾਹਣਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਮਾਹਣਾ ਸਿੰਘ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬਾਜ਼ਾਰ ਬਾਗ ਜਲਿਆਂ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਹਵੇਲੀ ਮਹੰਤਾ ਦੀ (ਨੇੜੇ ਢੋਲੀ ਚੌਕ), ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਹਵੇਲੀ ਮਾਈ ਟੋਨੀ (ਨੇੜੇ ਡਾਕਖਾਨਾ ਢੋਲੀ ਚੌਕ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਸਿੰਘਾੜਿਆਂ ਵਾਲੀ ਗਲੀ (ਨੇੜੇ ਡਾਕਖਾਨਾ ਢੋਲੀ ਚੌਕ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਹਵੇਲੀ ਬਾਬੂ ਰਾਮ (ਨੇੜੇ ਢੋਲੀ ਚੌਕ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਦਸੌਦਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ, (ਲੜਕੀਆਂ) - ਮਾਹਣਾ ਸਿੰਘ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D65" s="27" t="n">
@@ -8055,7 +8055,7 @@
       <c r="V65" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="W65" s="28" t="inlineStr">
+      <c r="W65" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -8069,7 +8069,7 @@
         <v>5</v>
       </c>
       <c r="Z65" s="27" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="AA65" s="22" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AB65" s="26" t="inlineStr">
         <is>
-          <t>AAP:7(50.0%) | INC:1(7.14%) | BJP:0 | SAD:0</t>
+          <t>AAP:18(29.03%) | INC:16(25.81%) | BJP:6 | SAD:0</t>
         </is>
       </c>
       <c r="AC65" s="26" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Gali Chuhar Singh, Nagar Nigam Amritsar, Ward No. 46 + Chowk Manda Singh, Nagar Nigam Amritsar, Ward No. 46 + Gali Jiwan Choudhary, Nagar Nigam Amritsar, Ward No. 46 + Gali Amir Khushiar, Nagar Nigam Amritsar, Ward No. 46 + Chowk Manna Singh Gali Nadhalia Wali, Nagar Nigam Amritsar, Ward No. 46 + Gali Pippal Wali, Nagar Nigam Amritsar, Ward No. 46 + Mana Singh Road, Chowk Ghanta Ghar, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>Govt. Elementary School - Mahna Singh Road, Amritsar</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਚੁਹੜ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਮਾਣਦਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਜੀਵਨ ਚੌਧਰੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਅਮੀਰ ਖ਼ੁਸ਼ਿਆਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਮੰਨਾ ਸਿੰਘ ਗਲੀ ਨਢਾਲੀਆ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 46 + ਗਲੀ ਪਿੱਪਲ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਮਾਨਾ ਸਿੰਘ ਰੋਡ, ਚੌਕ ਘੰਟਾ ਘਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਮਾਹਣਾ ਸਿੰਘ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D66" s="21" t="n">
@@ -8186,31 +8186,31 @@
         <v>120</v>
       </c>
       <c r="Z66" s="21" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="AA66" s="24" t="inlineStr">
         <is>
-          <t>TIED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB66" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(25.0%) | INC:1(25.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:11(14.67%) | INC:22(29.33%) | BJP:16 | SAD:0</t>
         </is>
       </c>
       <c r="AC66" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD66" s="20" t="inlineStr">
         <is>
-          <t>AAP → BJP → TIED</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE66" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → BJP → TIED)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -8220,12 +8220,12 @@
       </c>
       <c r="B67" s="26" t="inlineStr">
         <is>
-          <t>Gali Mangal Singh, Nagar Nigam Amritsar, Ward No. 46 + Akhara Chhat Wala, Nagar Nigam Amritsar, Ward No 46 + Sarai Guru Ramdas, Nagar Nigam Amritsar, Ward No. 46 + Budh Boota Market, Nagar Nigam Amritsar, Ward No. 46 + Madho Singh Road Gali No. 1, Nagar Nigam Amritsar, Ward No. 46 + Gali Sodhiyan, Nagar Nigam Amritsar, Ward No. 46 + Mahana Singh Road, Gali No 2, Nagar Nigam Amritsar, Ward No. 46 + Gali Thuthan Wali, Chowk Parag Das Nagar Nigam Amritsar Ward 46 + Akhara Budh Boota, Nagar Nigam Amritsar, Ward No. 46 + Dhobi Bazar, Nagar Nigam Amritsar, Ward No. 46 + Gali Samadhiyan, Nagar Nigam Amritsar, Ward No. 46 + Bazar Sarai, Guru Ramdas, Nagar Nigam Amritsar, Ward No. 46 + Gali Pujariyan Nede Bijli Ghar, Nagar Nigam Ward No. 46 Amritsar</t>
+          <t>Sahibzada Nand Girls High School - Chowk Parag Das, Amritsar</t>
         </is>
       </c>
       <c r="C67" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਮੰਗਲ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਅਖਾੜਾ ਛੱਤ ਵਾਲਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 46 + ਸਰਾਏ ਗੁਰੂ ਰਾਮਦਾਸ,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਬੂਧ ਬੂਟਾ ਮਾਰਕਿਟ,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46 + ਮਾਧੋ ਸਿੰਘ ਰੋਡ ਗਲੀ ਨੰ. 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46 + ਗਲੀ ਸੋਢੀਆਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਮਹਾਣਾ ਸਿੰਘ ਰੋਡ, ਗਲੀ ਨੰ 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46 + ਗਲੀ ਠੂਠਾਂ ਵਾਲੀ, ਚੌਕ ਪਰਾਗ ਦਾਸ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ 46 + ਅਖਾੜਾ ਬੂਧ ਬੂਟਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46 + ਧੋਬੀ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46 + ਗਲੀ ਸਮਾਧੀਆਂ,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.46 + ਬਾਜ਼ਾਰ ਸਰਾਏ, ਗੁਰੂ ਰਾਮਦਾਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਪੁਜਾਰੀਆਂ ਨੇੜੇ ਬਿਜਲੀ ਘਰ, ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ. 46 ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਸਾਹਿਬਜ਼ਾਦਾ ਨੰਦ ਗਰਲਜ਼ ਹਾਈ ਸਕੂਲ - ਚੌਂਕ ਪਰਾਗ ਦਾਸ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D67" s="27" t="n">
@@ -8303,31 +8303,31 @@
         <v>56</v>
       </c>
       <c r="Z67" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>68</v>
+      </c>
+      <c r="AA67" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB67" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:20(29.41%) | INC:18(26.47%) | BJP:3 | SAD:2</t>
         </is>
       </c>
       <c r="AC67" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD67" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE67" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -8337,12 +8337,12 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Gali Thaiyan Nagar Nigam Amritsar, Ward No. 46 + Chowk Lachhmansar to Chowk Baba Sahib (Bagichi Seth Tara Chand), Nagar Nigam Amritsar, Ward No. 46 + Chowk Lachhmansar to Chowk Baba Sahib, Nagar Nigam Amritsar, Ward No. 46 + Gali Dabariya Wali, Nagar Nigam Amritsar, Ward No. 46 + Chowk Moni to Chowk Katri, Nagar Nigam Amritsar, Ward No. 46</t>
+          <t>D.A.V. Elementary School - Chowk Lachhmansar, Amritsar</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਥਾਈਆਂ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਲਛਮਣਸਰ ਤੋਂ ਚੌਕ ਬਾਬਾ ਸਾਹਿਬ (ਬਗੀਚੀ ਸੇਠ ਤਾਰਾ ਚੰਦ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਲਛਮਣਸਰ ਤੋਂ ਚੌਕ ਬਾਬਾ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਗਲੀ ਡਾਬੜਿਆ ਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46 + ਚੌਕ ਮੋਨੀ ਤੋਂ ਚੌਕ ਕਟੜੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 46</t>
+          <t>ਡੀ.ਏ.ਵੀ. ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਚੌਂਕ ਲਛਮਣਸਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D68" s="21" t="n">
@@ -8420,31 +8420,31 @@
         <v>96</v>
       </c>
       <c r="Z68" s="21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA68" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>73</v>
+      </c>
+      <c r="AA68" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB68" s="20" t="inlineStr">
         <is>
-          <t>AAP:3(8.82%) | INC:4(11.76%) | BJP:2 | SAD:0</t>
+          <t>AAP:24(32.88%) | INC:21(28.77%) | BJP:1 | SAD:1</t>
         </is>
       </c>
       <c r="AC68" s="20" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD68" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE68" s="20" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B69" s="26" t="inlineStr">
         <is>
-          <t>Kot Baba Deep Singh Gali No. 2, Nagar Nigam, Amritsar, Ward No. 47 + Kot Baba Deep Singh Gali No. 3, Nagar Nigam Amritsar, Ward No. 47 + Kot Baba Deep Singh Gali No. 4, Nagar Nigam Amritsar, Ward No. 47</t>
+          <t>Govt. Secondary School (Girls) - Kot Baba Deep Singh Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C69" s="26" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਗਲੀ ਨੰ. 2,ਨਗਰ ਨਿਗਮ . ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਗਲੀ ਨੰ. 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਗਲੀ ਨੰ.4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47</t>
+          <t>ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D69" s="27" t="n">
@@ -8537,7 +8537,7 @@
         <v>48</v>
       </c>
       <c r="Z69" s="27" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="AA69" s="22" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AB69" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:40(41.24%) | INC:13(13.4%) | BJP:7 | SAD:3</t>
         </is>
       </c>
       <c r="AC69" s="26" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Kot Baba Deep Singh Gali No. 4, Nagar Nigam Amritsar, Ward No. 47 + Guru Ramdas Nagar Gali No. 1, Nagar Nigam Amritsar, Ward No. 47 + Kot Baba Deep Singh Gali No. 5, Nagar Nigam Amritsar, Ward No. 47 + Guru Ramdas Nagar Gali No. 3, Nagar Nigam Amritsar, Ward No. 47</t>
+          <t>Govt. Secondary School (Girls) - Kot Baba Deep Singh Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਗਲੀ ਨੰ. 4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਗੁਰੂ ਰਾਮਦਾਸ ਨਗਰ ਗਲੀ ਨੰ. 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਗਲੀ ਨੰ. 5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਗੁਰੂ ਰਾਮਦਾਸ ਨਗਰ ਗਲੀ ਨੰ. 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47</t>
+          <t>ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D70" s="21" t="n">
@@ -8654,16 +8654,16 @@
         <v>126</v>
       </c>
       <c r="Z70" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA70" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>99</v>
+      </c>
+      <c r="AA70" s="29" t="inlineStr">
+        <is>
+          <t>TIED</t>
         </is>
       </c>
       <c r="AB70" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:29(29.29%) | INC:29(29.29%) | BJP:1 | SAD:5</t>
         </is>
       </c>
       <c r="AC70" s="20" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="AD70" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → TIED</t>
         </is>
       </c>
       <c r="AE70" s="20" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>Close / Undecided (AAP → AAP → TIED)</t>
         </is>
       </c>
     </row>
@@ -8688,12 +8688,12 @@
       </c>
       <c r="B71" s="26" t="inlineStr">
         <is>
-          <t>Guru Ramdas Nagar Gali No. 4, Nagar Nigam Amritsar, Ward No. 47 + Kot Baba Deep Singh Gali No 6 Nagar Nigam Amritsar, Ward No. 47 + Guru Ramdas Nagar Gali No. 2, Nagar Nigam. Amritsar, Ward No 47</t>
+          <t>Govt. Secondary School (Girls) - Kot Baba Deep Singh Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C71" s="26" t="inlineStr">
         <is>
-          <t>ਗੁਰੂ ਰਾਮਦਾਸ ਨਗਰ ਗਲੀ ਨੰ. 4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਗਲੀ ਨੰ 6 ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਗੁਰੂ ਰਾਮਦਾਸ ਨਗਰ ਗਲੀ ਨੰ. 2,ਨਗਰ ਨਿਗਮ. ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 47</t>
+          <t>ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D71" s="27" t="n">
@@ -8771,31 +8771,31 @@
         <v>53</v>
       </c>
       <c r="Z71" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA71" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>113</v>
+      </c>
+      <c r="AA71" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB71" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:26(23.01%) | INC:36(31.86%) | BJP:4 | SAD:6</t>
         </is>
       </c>
       <c r="AC71" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD71" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE71" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Bahadur Nagar Sultan Pind Road (Right Side), Nagar Nigam Amritsar, Ward No. 47 + Kot Baba Deep Singh Gali No. 7, Nagar Nigam Amritsar, Ward No. 47</t>
+          <t>Govt. Secondary School (Girls) - Kot Baba Deep Singh Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>ਬਹਾਦਰ ਨਗਰ ਸੁਲਤਾਨ ਪਿੰਡ ਰੋਡ (ਸੱਜਾ ਪਾਸਾ),ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਗਲੀ ਨੰ. 7, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47</t>
+          <t>ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D72" s="21" t="n">
@@ -8888,31 +8888,31 @@
         <v>86</v>
       </c>
       <c r="Z72" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>93</v>
+      </c>
+      <c r="AA72" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB72" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(40.0%) | INC:1(20.0%) | BJP:0 | SAD:1</t>
+          <t>AAP:23(24.73%) | INC:31(33.33%) | BJP:5 | SAD:1</t>
         </is>
       </c>
       <c r="AC72" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD72" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE72" s="20" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="B73" s="26" t="inlineStr">
         <is>
-          <t>Sardarpura Sultanwind Road, Nagar Nigam Amritsar, Ward No. 47</t>
+          <t>Govt. Secondary School (Girls) - Kot Baba Deep Singh Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C73" s="26" t="inlineStr">
         <is>
-          <t>ਸਰਦਰਪੁਰਾ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47</t>
+          <t>ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ) - ਕੋਟ ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D73" s="27" t="n">
@@ -9005,31 +9005,31 @@
         <v>26</v>
       </c>
       <c r="Z73" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA73" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>57</v>
+      </c>
+      <c r="AA73" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB73" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(100.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:22(38.6%) | INC:11(19.3%) | BJP:2 | SAD:2</t>
         </is>
       </c>
       <c r="AC73" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD73" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE73" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -9039,12 +9039,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Nimbu Kot Aatma Ram, Nagar Nigam Amritsar, Ward No. 41 + Kot Aatma Ram, Nagar Nigam Amritsar, Ward No. 41</t>
+          <t>Rosy Modern Senior Secondary School - Shaheed Udham Singh Nagar, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>ਨਿੰਬੂ ਕੋਟ ਆਤਮਾ ਰਾਮ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਕੋਟ ਆਤਮਾ ਰਾਮ,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41</t>
+          <t>ਰੋਜ਼ੀ ਮਾਡਰਨ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D74" s="21" t="n">
@@ -9122,16 +9122,16 @@
         <v>36</v>
       </c>
       <c r="Z74" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA74" s="28" t="inlineStr">
+        <v>119</v>
+      </c>
+      <c r="AA74" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
       </c>
       <c r="AB74" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(50.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:26(21.85%) | INC:39(32.77%) | BJP:5 | SAD:6</t>
         </is>
       </c>
       <c r="AC74" s="20" t="inlineStr">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="B75" s="26" t="inlineStr">
         <is>
-          <t>Nimbu Kot Aatma Ram Gali No. 2, Nagar Nigam, Amritsar, Ward No. 41</t>
+          <t>Rosy Modern Senior Secondary School - Shaheed Udham Singh Nagar, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C75" s="26" t="inlineStr">
         <is>
-          <t>ਨਿੰਬੂ ਕੋਟ ਆਤਮਾ ਰਾਮ ਗਲੀ ਨੰ. 2, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41</t>
+          <t>ਰੋਜ਼ੀ ਮਾਡਰਨ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D75" s="27" t="n">
@@ -9225,7 +9225,7 @@
       <c r="V75" s="27" t="n">
         <v>78</v>
       </c>
-      <c r="W75" s="28" t="inlineStr">
+      <c r="W75" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -9239,31 +9239,31 @@
         <v>67</v>
       </c>
       <c r="Z75" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA75" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>138</v>
+      </c>
+      <c r="AA75" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB75" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:32(23.19%) | INC:46(33.33%) | BJP:7 | SAD:4</t>
         </is>
       </c>
       <c r="AC75" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD75" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → UNDECIDED</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE75" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → INC → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>New Shaheed Udham Singh Nagar gali.2, Nagar Nigam, Amritsar, Ward No. 43 + New Kapoor Nagar, Gali No.6, Nagar Nigam Amritsar.Ward No.40</t>
+          <t>Rosy Modern Senior Secondary School, Shaheed Udham Singh Nagar, Amritsar - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ.2, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਕਪੂਰ ਨਗਰ, ਗਲੀ ਨੰ.6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ.ਵਾਰਡ ਨੰ.40</t>
+          <t>ਰੋਜ਼ੀ ਮਾਡਰਨ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ, ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D76" s="21" t="n">
@@ -9356,7 +9356,7 @@
         <v>100</v>
       </c>
       <c r="Z76" s="21" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="AA76" s="22" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="AB76" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:50(51.02%) | INC:9(9.18%) | BJP:1 | SAD:4</t>
         </is>
       </c>
       <c r="AC76" s="20" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B77" s="26" t="inlineStr">
         <is>
-          <t>New Shaheed Udham Singh Nagar Gali.2, Nagar Nigam Amritsar, Ward No. 43 + New Kapur Nagar Gali No. 6, Nagar Nigam Amritsar, Ward No. 40</t>
+          <t>Rozi Modern Senior Secondary School, Shaheed Udham Singh Nagar, Amritsar - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C77" s="26" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ.2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਕਪੂਰ ਨਗਰ ਗਲੀ ਨੰ. 6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 40 + ਨਿਊ ਕਪੂਰ ਨਗਰ ਗਲੀ ਨੰ. 6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 40</t>
+          <t>ਰੋਜ਼ੀ ਮਾਡਰਨ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ, ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D77" s="27" t="n">
@@ -9473,7 +9473,7 @@
         <v>150</v>
       </c>
       <c r="Z77" s="27" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="AA77" s="22" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="AB77" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:41(39.05%) | INC:16(15.24%) | BJP:6 | SAD:4</t>
         </is>
       </c>
       <c r="AC77" s="26" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>New Kapoor Nagar Sultan Pind Road Gali No. 1,2,3,4,5, Nagar Nigam Amritsar, Ward No. 40 + New Kapoor Nagar Barf Karkhane Vali Gali, Nagar Nigam Amritsar, Ward No. 40 + New Kapoor Nagar Gali No. 6, Nagar Nigam Amritsar, Ward No. 40</t>
+          <t>Rosy Modern Senior Secondary School - Shaheed Udham Singh Nagar, Amritsar</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਕਪੂਰ ਨਗਰ ਸੁਲਤਾਨ ਪਿੰਡ ਰੋਡ ਗਲੀ ਨੰ.1,2,3,4,5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.40 + ਨਿਊ ਕਪੂਰ ਨਗਰ ਬਰਫ ਕਾਰਖਾਨੇ ਵਾਲੀ ਗਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 40 + ਨਿਊ ਕਪੂਰ ਨਗਰ ਗਲੀ ਨੰ. 6,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 40</t>
+          <t>ਰੋਜ਼ੀ ਮਾਡਰਨ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D78" s="21" t="n">
@@ -9590,31 +9590,31 @@
         <v>142</v>
       </c>
       <c r="Z78" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA78" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>93</v>
+      </c>
+      <c r="AA78" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB78" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:27(29.03%) | INC:24(25.81%) | BJP:2 | SAD:7</t>
         </is>
       </c>
       <c r="AC78" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD78" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE78" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="B79" s="26" t="inlineStr">
         <is>
-          <t>Guru Nanak Nagar, Nagar Nigam Amritsar, Ward No. 42 + Kot Gurmeet Nagar, Nagar Nigam, Amritsar, Ward No. 41 + Kot Salig Ram, Nagar Nigam Amritsar, Ward No. 41 + Shaheed Udham Singh Nagar Gali No.4, Nagar Nigam, Amritsar, Ward No. 43 + New Shaheed Udham Singh Nagar Gali No.2, Nagar Nigam Amritsar, Ward No. 43 + Guru Nanak Nirankari Colony, Sultanwind Road, Nagar Nigam Ward No. 40 + New Shaheed Udham Singh Nagar Mehar Wala Bazar No.3, Nagar Nigam Ward 43 Amritsar</t>
+          <t>Sarv Shakti Public School - Gali No. 6, Shaheed Udham Singh Nagar, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C79" s="26" t="inlineStr">
         <is>
-          <t>ਗੁਰੂ ਨਾਨਕ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਗੁਰਮੀਤ ਨਗਰ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਕੋਟ ਸਾਲਿਗ ਰਾਮ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.4, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਗੁਰੂ ਨਾਨਕ ਨਿਰੰਕਾਰੀ ਕਲੋਨੀ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ. 40 + ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਮੇਂਹਰ ਵਾਲਾ ਬਾਜ਼ਾਰ ਨੰ.3, ਨਗਰ ਨਿਗਮ ਵਾਰਡ 43 ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਸਰਵ ਸ਼ਕਤੀ ਪਬਲਿਕ ਸਕੂਲ - ਗਾਲੀ ਨੰ. 6, ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D79" s="27" t="n">
@@ -9707,7 +9707,7 @@
         <v>65</v>
       </c>
       <c r="Z79" s="27" t="n">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="AA79" s="22" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AB79" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(14.29%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:41(42.27%) | INC:8(8.25%) | BJP:7 | SAD:7</t>
         </is>
       </c>
       <c r="AC79" s="26" t="inlineStr">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Shaheed Udham Singh Nagar Gali No.6, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar Gali No.5, Nagar Nigam Amritsar, Ward No. 43 + New Shaheed Udham Singh Nagar Mandir Wala Bazar No.3, Nagar Nigam Ward No.43 Amritsar</t>
+          <t>Sarv Shakti Public School - Gali No. 6, Shaheed Udham Singh Nagar, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਮੰਦਰ ਵਾਲਾ ਬਾਜ਼ਾਰ ਨੰ.3, ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ.43 ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਸਰਵ ਸ਼ਕਤੀ ਪਬਲਿਕ ਸਕੂਲ - ਗਾਲੀ ਨੰ. 6, ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D80" s="21" t="n">
@@ -9824,31 +9824,31 @@
         <v>87</v>
       </c>
       <c r="Z80" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA80" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>102</v>
+      </c>
+      <c r="AA80" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB80" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(50.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:39(38.24%) | INC:16(15.69%) | BJP:3 | SAD:7</t>
         </is>
       </c>
       <c r="AC80" s="20" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD80" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE80" s="20" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="B81" s="26" t="inlineStr">
         <is>
-          <t>Shaheed Udham Singh Nagar Gali No. 5, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar Gali No. 3, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar Gali No. 6, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar Gali No. 4, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar Bazar No. 5, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar Mandir Wala Bazar Gali No. 8, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar No. 7, Nagar Nigam Amritsar, Ward No. 43</t>
+          <t>Sarv Shakti Public School - Gali No. 6, Shaheed Udham Singh Nagar, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C81" s="26" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ.5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ. 4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਬਾਜ਼ਾਰ ਨੰ.5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਮੰਦਰ ਵਾਲਾ ਬਾਜ਼ਾਰ ਗਲੀ.ਨੰ 8, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਨੰ. 7, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43</t>
+          <t>ਸਰਵ ਸ਼ਕਤੀ ਪਬਲਿਕ ਸਕੂਲ - ਗਾਲੀ ਨੰ. 6, ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D81" s="27" t="n">
@@ -9941,31 +9941,31 @@
         <v>78</v>
       </c>
       <c r="Z81" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA81" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>122</v>
+      </c>
+      <c r="AA81" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB81" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:33(27.05%) | INC:35(28.69%) | BJP:5 | SAD:5</t>
         </is>
       </c>
       <c r="AC81" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD81" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE81" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -9975,12 +9975,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>New Shaheed Udham Singh Nagar Mandir Wala Bazar Gali No. 8, Nagar Nigam Amritsar, Ward No. 43 + New Shaheed Udham Singh Nagar Gali No. 3, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar Bazar No. 5, Nagar Nigam Amritsar, Ward No. 43</t>
+          <t>Sarv Shakti Public School - Gali No. 6, Shaheed Udham Singh Nagar, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਮੰਦਰ ਵਾਲਾ ਬਾਜ਼ਾਰ ਗਲੀ ਨੰ 8, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ. 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਬਜ਼ਾਰ ਨੰ. 5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43</t>
+          <t>ਸਰਵ ਸ਼ਕਤੀ ਪਬਲਿਕ ਸਕੂਲ - ਗਾਲ਼ੀ ਨੰ. 6, ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D82" s="21" t="n">
@@ -10058,7 +10058,7 @@
         <v>84</v>
       </c>
       <c r="Z82" s="21" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="AA82" s="22" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AB82" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(66.67%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:29(38.67%) | INC:11(14.67%) | BJP:2 | SAD:7</t>
         </is>
       </c>
       <c r="AC82" s="20" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="B83" s="26" t="inlineStr">
         <is>
-          <t>Jawala Ji Nagar Gali No. 8, Nagar Nigam Amritsar, Ward No. 42 + Kot Karnail Singh, Nagar Nigam Amritsar, Ward No. 42 + Jawala Ji Nagar Gali No. 7, Nagar Nigam Amritsar, Ward No. 42</t>
+          <t>New Flower Public High School (Building No.1) - New Antarjami Colony, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C83" s="26" t="inlineStr">
         <is>
-          <t>ਜਵਾਲਾ ਜੀ ਨਗਰ ਗਲੀ ਨੰ. 8,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਕਰਨੈਲ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਜਵਾਲਾ ਜੀ ਨਗਰ ਗਲੀ ਨੰ. 7,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42</t>
+          <t>ਨਿਊ ਫਲਾਵਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ (ਬਿਲਡਿੰਗ ਨੰ.1) - ਨਿਊ ਅੰਤਰਜਾਮੀ ਕੋਲਨੀ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D83" s="27" t="n">
@@ -10175,31 +10175,31 @@
         <v>35</v>
       </c>
       <c r="Z83" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA83" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>103</v>
+      </c>
+      <c r="AA83" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB83" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:35(33.98%) | INC:19(18.45%) | BJP:4 | SAD:9</t>
         </is>
       </c>
       <c r="AC83" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD83" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE83" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -10209,12 +10209,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Bazar No. 3 Tej Nagar, Nagar Nigam, Amritsar Ward No. 42 + Bazar No. 2 Tej Nagar Sultanwind Road, Nagar Nigam Amritsar Ward No. 42 + New Tej Nagar, Nagar Nigam, Amritsar Ward No. 42 + Main Bazar Tej Nagar, Nagar Nigam Amritsar Ward No. 42 + Bazar No. 1 Tej Nagar Sultanwind Road, Nagar Nigam Amritsar Ward No. 42</t>
+          <t>New Flower Public High School (Building No.1) - New Antaryami Colony, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>ਬਾਜ਼ਾਰ ਨੰ. 3 ਤੇਜ ਨਗਰ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 42 + ਬਾਜ਼ਾਰ ਨੰ. 2 ਤੇਜ ਨਗਰ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 42 + ਨਿਊ ਤੇਜ ਨਗਰ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 42 + ਮੇਨ ਬਾਜ਼ਾਰ ਤੇਜ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 42 + ਬਾਜ਼ਾਰ ਨੰ. 1 ਤੇਜ ਨਗਰ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 42</t>
+          <t>ਨਿਊ ਫਲਾਵਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ (ਬਿਲਡਿੰਗ ਨੰ.1) - ਨਿਊ ਅੰਤਰਯਾਮੀ ਕੋਲਨੀ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D84" s="21" t="n">
@@ -10292,7 +10292,7 @@
         <v>52</v>
       </c>
       <c r="Z84" s="21" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="AA84" s="22" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="AB84" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:24(31.17%) | INC:21(27.27%) | BJP:1 | SAD:4</t>
         </is>
       </c>
       <c r="AC84" s="20" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="B85" s="26" t="inlineStr">
         <is>
-          <t>New Shaheed Udham Singh Nagar Street No. 4, Municipal Corporation Amritsar, Ward No. 43</t>
+          <t>New Flower Public High School (Building No. 1) - Tarn Taran Road, New Antarjami Colony, Amritsar</t>
         </is>
       </c>
       <c r="C85" s="26" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.4,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43</t>
+          <t>ਨਿਊ ਫਲਾਵਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ (ਬਿਲਡਿੰਗ ਨੰ.1) - ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨਿਊ ਅੰਤਰਜਾਮੀ ਕੋਲਨੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D85" s="27" t="n">
@@ -10409,16 +10409,16 @@
         <v>35</v>
       </c>
       <c r="Z85" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA85" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>73</v>
+      </c>
+      <c r="AA85" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB85" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:18(24.66%) | INC:20(27.4%) | BJP:1 | SAD:7</t>
         </is>
       </c>
       <c r="AC85" s="26" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="AD85" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE85" s="26" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -10443,12 +10443,12 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>New Shaheed Udham Singh Gali No. 3, Nagar Nigam Amritsar, Ward No. 43 + New Shaheed Udham Singh Gali No. 2 Nagar Nigam Amritsar, Ward No. 43</t>
+          <t>New Flower Public High School (Building No.1) - New Antarjami Colony, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਗਲੀ ਨੰ. 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਗਲੀ ਨੰ. 2 ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43</t>
+          <t>ਨਿਊ ਫਲਾਵਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ (ਬਿਲਡਿੰਗ ਨੰ.1) - ਨਿਊ ਅੰਤਰਜਾਮੀ ਕੋਲਨੀ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D86" s="21" t="n">
@@ -10526,31 +10526,31 @@
         <v>96</v>
       </c>
       <c r="Z86" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA86" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>66</v>
+      </c>
+      <c r="AA86" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB86" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:30(45.45%) | INC:5(7.58%) | BJP:2 | SAD:5</t>
         </is>
       </c>
       <c r="AC86" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD86" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE86" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="B87" s="26" t="inlineStr">
         <is>
-          <t>Habib Pura Gali No. 2, 3, 4, 9 Nagar Nigam Amritsar, Ward No. 47 + Kot Harnam Das, Nagar Nigam Amritsar, Ward No. 42 + Habib Pura Sultan Wind Road, Nagar Nigam Amritsar, Ward No. 47</t>
+          <t>Sultanwind Road Amritsar - Sacred Souls Public School, Antarjami Colony, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C87" s="26" t="inlineStr">
         <is>
-          <t>ਹਬੀਬ ਪুরা ਗਲੀ ਨੰ. 2, 3, 4, 9 ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਹਬੀਬ ਪੁਰਾ ਸੁਲਤਾਨ ਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 47</t>
+          <t>ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਸੈਕਰਡ ਸੋਲਜ਼ ਪਬਲਿਕ ਸਕੂਲ, ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D87" s="27" t="n">
@@ -10643,31 +10643,31 @@
         <v>148</v>
       </c>
       <c r="Z87" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA87" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>110</v>
+      </c>
+      <c r="AA87" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB87" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(50.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:35(31.82%) | INC:27(24.55%) | BJP:6 | SAD:4</t>
         </is>
       </c>
       <c r="AC87" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD87" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE87" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -10677,12 +10677,12 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Habib Pura, Nagar Nigam Amritsar, Ward No 47 + Kot Harnam Das Bhag No.2, Nagar Nigam, Amritsar, Ward No. 42 + Teerth Pura Main Bazar, Nagar Nigam Amritsar, Ward No.47 + Ram Singh Gali No. 2, Nagar Nigam Amritsar, Ward No.47 + Sant Chandan Singh Colony, Nagar Nigam Amritsar, Ward No. 42 + Ram Singh Colony, Gali No. 1, Nagar Nigam Amritsar, Ward No. 42 + Bagihee Mahanta, Nagar Nigam Amritsar, Ward No.47</t>
+          <t>Sultanwind Road Amritsar - Sacred Souls Public School, Antarjami Colony, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>ਹਬੀਬ ਪੁਰਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 47 + ਕੋਟ ਹਰਨਾਮ ਦਾਸ ਭਾਗ ਨੰ.2, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਤੀਰਥ ਪੁਰਾ ਮੇਨ ਬਜਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.47 + ਰਾਮ ਸਿੰਘ ਗਲੀ ਨੰ. 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.47 + ਸੰਤ ਚੰਦਨ ਸਿੰਘ ਕਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਰਾਮ ਸਿੰਘ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਬਗੀਚੀ ਮਹੰਤਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.47</t>
+          <t>ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਸੈਕਰਡ ਸੋਲਜ਼ ਪਬਲਿਕ ਸਕੂਲ, ਅੰਤਰਜਾਮੀ ਕਲੋਨੀ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D88" s="21" t="n">
@@ -10760,31 +10760,31 @@
         <v>91</v>
       </c>
       <c r="Z88" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA88" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>113</v>
+      </c>
+      <c r="AA88" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB88" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(50.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:32(28.32%) | INC:29(25.66%) | BJP:9 | SAD:3</t>
         </is>
       </c>
       <c r="AC88" s="20" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD88" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE88" s="20" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -10794,12 +10794,12 @@
       </c>
       <c r="B89" s="26" t="inlineStr">
         <is>
-          <t>Kot Aatma Ram Sultanwind Road, Nagar Nigam Amritsar, Ward No. 41</t>
+          <t>Prim Roses English School - Near Gurdwara Miri Piri, Kot Atma Ram, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C89" s="26" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਆਤਮਾ ਰਾਮ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41</t>
+          <t>ਪ੍ਰਿਮ ਰੋਜ਼ਿਸ ਇੰਗਲਿਸ਼ ਸਕੂਲ - ਨੇੜੇ ਗੁਰੂਦੁਆਰਾ ਮੀਰੀ ਪੀਰੀ, ਕੋਟ ਆਤਮਾ ਰਾਮ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D89" s="27" t="n">
@@ -10877,7 +10877,7 @@
         <v>81</v>
       </c>
       <c r="Z89" s="27" t="n">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="AA89" s="22" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="AB89" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:40(32.79%) | INC:32(26.23%) | BJP:5 | SAD:1</t>
         </is>
       </c>
       <c r="AC89" s="26" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Amiyadarjit Purana Dhobi Ghat, Nagar Nigam Amritsar, Ward No. 41 + Kot Atma Ram, Nagar Nigam, Amritsar, Ward No. 41 + Kot Salig Ram, Nagar Nigam, Amritsar, Ward No. 41</t>
+          <t>Prim Roses English School - Near Gurdwara Miri Piri, Kot Atma Ram, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>ਅਮਿਅਦਰਜੀਤ ਪੁਰਾਣਾ ਧੋਬੀ ਘਾਟ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਕੋਟ ਆਤਮਾ ਰਾਮ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 41 + ਕੋਟ ਸਾਲਿਗ ਰਾਮ,ਨਗਰ ਨਿਗਮ. ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.41</t>
+          <t>ਪ੍ਰਿਮ ਰੋਜ਼ਿਸ ਇੰਗਲਿਸ਼ ਸਕੂਲ - ਨੇੜੇ ਗੁਰੂਦੁਆਰਾ ਮੀਰੀ ਪੀਰੀ, ਕੋਟ ਆਤਮਾ ਰਾਮ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D90" s="21" t="n">
@@ -10994,31 +10994,31 @@
         <v>30</v>
       </c>
       <c r="Z90" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA90" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>35</v>
+      </c>
+      <c r="AA90" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB90" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:4(11.43%) | INC:11(31.43%) | BJP:6 | SAD:1</t>
         </is>
       </c>
       <c r="AC90" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD90" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE90" s="20" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="B91" s="26" t="inlineStr">
         <is>
-          <t>Bhagat Singh Pura, Nagar Nigam Amritsar, Ward No. 41 + Dasmesh Colony, Nagar Nigam Amritsar, Ward No. 41 + Juhri Sultanwind Road, Nagar Nigam Amritsar, Ward No. 41</t>
+          <t>Prim Roses English School - Tarn Taran Road, Near Gurdwara Miri Piri, Kot Atma Ram, Amritsar</t>
         </is>
       </c>
       <c r="C91" s="26" t="inlineStr">
         <is>
-          <t>ਭਗਤ ਸਿੰਘ ਪੁਰਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਦਸਮੇਸ਼ ਕਲੋਨੀ,, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.41 + ਜੁਹੜੀ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.41.</t>
+          <t>ਪ੍ਰਿਮ ਰੋਜ਼ਿਸ ਇੰਗਲਿਸ਼ ਸਕੂਲ - ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨੇੜੇ ਗੁਰੂਦੁਆਰਾ ਮੀਰੀ ਪੀਰੀ, ਕੋਟ ਆਤਮਾ ਰਾਮ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D91" s="27" t="n">
@@ -11111,31 +11111,31 @@
         <v>57</v>
       </c>
       <c r="Z91" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA91" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>89</v>
+      </c>
+      <c r="AA91" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB91" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:24(26.97%) | INC:26(29.21%) | BJP:4 | SAD:4</t>
         </is>
       </c>
       <c r="AC91" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD91" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE91" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -11145,12 +11145,12 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Shaheed Udham Singh Gali No.1, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar Gali No. 5, Nagar Nigam Amritsar, Ward No. 43</t>
+          <t>New Flower Public High School, (Building No.2) - Tarn Taran Road, New Antarjami Colony, Amritsar</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਗਾਲੀ ਨੰ.1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਾਲੀ ਨੰ. 5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43</t>
+          <t>ਨਿਊ ਫਲਾਵਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, (ਬਿਲਡਿੰਗ ਨੰ.2) - ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨਿਊ ਅੰਤਰਜਾਮੀ ਕੋਲੋਨੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D92" s="21" t="n">
@@ -11228,31 +11228,31 @@
         <v>43</v>
       </c>
       <c r="Z92" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA92" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>71</v>
+      </c>
+      <c r="AA92" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB92" s="20" t="inlineStr">
         <is>
-          <t>AAP:3(42.86%) | INC:1(14.29%) | BJP:0 | SAD:0</t>
+          <t>AAP:20(28.17%) | INC:23(32.39%) | BJP:0 | SAD:3</t>
         </is>
       </c>
       <c r="AC92" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD92" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE92" s="20" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -11262,12 +11262,12 @@
       </c>
       <c r="B93" s="26" t="inlineStr">
         <is>
-          <t>Shaheed Udham Singh Nagar Gali No.3, Nagar Nigam Amritsar, Ward No. 43</t>
+          <t>New Flower Public High School, (Building No.2) - New Antaryami Colony, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C93" s="26" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43</t>
+          <t>ਨਿਊ ਫਲਾਵਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, (ਬਿਲਡਿੰਗ ਨੰ.2) - ਨਿਊ ਅੰਤਰਯਾਮੀ ਕੋਲਨੀ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D93" s="27" t="n">
@@ -11345,31 +11345,31 @@
         <v>115</v>
       </c>
       <c r="Z93" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA93" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>100</v>
+      </c>
+      <c r="AA93" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB93" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(50.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:37(37.0%) | INC:13(13.0%) | BJP:9 | SAD:6</t>
         </is>
       </c>
       <c r="AC93" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD93" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE93" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -11379,12 +11379,12 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Gaali No.6 Shaheed Udham Singh Nagar, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Gaali No.2, Nagar Nigam Amritsar, Ward No 43</t>
+          <t>New Flower Public High School, (Building No. 2) - New Antarjami Colony, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>ਗਾਲੀ ਨੰ.6 ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਗਾਲੀ ਨੰ.2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 43</t>
+          <t>ਨਿਊ ਫਲਾਵਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, (ਬਿਲਡਿੰਗ ਨੰ.2) - ਨਿਊ ਅੰਤਰਜਾਮੀ ਕੋਲਨੀ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D94" s="21" t="n">
@@ -11462,7 +11462,7 @@
         <v>62</v>
       </c>
       <c r="Z94" s="21" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="AA94" s="22" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="AB94" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(33.33%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:26(32.91%) | INC:21(26.58%) | BJP:1 | SAD:2</t>
         </is>
       </c>
       <c r="AC94" s="20" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="B95" s="26" t="inlineStr">
         <is>
-          <t>New Shaheed Udham Singh Nagar Gali No. 6, Nagar Nigam Amritsar, Ward No. 43 + New Shaheed Udham Singh Nagar Gali No. 4, Nagar Nigam Amritsar, Ward No. 43 + New Shaheed Udham Singh Nagar Mandir Wala Bazar Gali No. 10, Nagar Nigam Amritsar, Ward No. 43 + New Shaheed Udham Singh Nagar Gali No. 3, Nagar Nigam Amritsar, Ward No. 43</t>
+          <t>Amritsar Public School - Gali No. 5 Shaheed Udham Singh Nagar, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C95" s="26" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ. 6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 43 + ਨਿਊ ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਮੰਦਰ ਵਾਲਾ ਬਾਜ਼ਾਰ ਗਾਲੀ.ਨੰ 10 ,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ. 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43</t>
+          <t>ਅੰਮ੍ਰਿਤਸਰ ਪਬਲਿਕ ਸਕੂਲ - ਗਾਲੀ ਨੰ.5 ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D95" s="27" t="n">
@@ -11579,31 +11579,31 @@
         <v>60</v>
       </c>
       <c r="Z95" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA95" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>83</v>
+      </c>
+      <c r="AA95" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB95" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(100.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:28(33.73%) | INC:16(19.28%) | BJP:2 | SAD:8</t>
         </is>
       </c>
       <c r="AC95" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD95" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE95" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -11613,12 +11613,12 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>New Shaheed Udham Singh Nagar Bazar No. 5, Municipal Corporation Amritsar, Ward No. 43 + New Shaheed Udham Singh Nagar Gali No. 3, Municipal Corporation Amritsar, Ward No. 43</t>
+          <t>Amritsar Public School - Gali No.5 Shaheed Udham Singh Nagar, Amritsar</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਬਜ਼ਾਰ ਨੰ. 5 , ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਾਲੀ ਨੰ.3 ,ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਨਿਊ ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਾਲੀ ਨੰ. 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43</t>
+          <t>ਅੰਮ੍ਰਿਤਸਰ ਪਬਲਿਕ ਸਕੂਲ - ਗਾਲੀ ਨੰ.5 ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D96" s="21" t="n">
@@ -11696,31 +11696,31 @@
         <v>120</v>
       </c>
       <c r="Z96" s="21" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="AA96" s="24" t="inlineStr">
         <is>
-          <t>UNDECIDED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB96" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:28(23.53%) | INC:37(31.09%) | BJP:6 | SAD:6</t>
         </is>
       </c>
       <c r="AC96" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD96" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE96" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="B97" s="26" t="inlineStr">
         <is>
-          <t>New Shaheed Udham Singh Nagar Mandir Wala Bazar No.9, Nagar Nigam Amritsar, Ward No. 43 + New Shaheed Udham Singh Nagar Gali No. 3, Nagar Nigam Amritsar, Ward No. 43 + Shaheed Udham Singh Nagar Gali No. 6, Nagar Nigam Amritsar, Ward No. 43</t>
+          <t>Amritsar Public School - Gali No. 5 Shaheed Udham Singh Nagar, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C97" s="26" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਮੰਦਰ ਵਾਲਾ ਬਾਜ਼ਾਰ ਨੰ.9, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.43 + ਨਿਊ ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਾਲੀ ਨੰ. 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ.43 + ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ ਗਾਲੀ ਨੰ.6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43</t>
+          <t>ਅੰਮ੍ਰਿਤਸਰ ਪਬਲਿਕ ਸਕੂਲ - ਗਾਲੀ ਨੰ.5 ਸ਼ਹੀਦ ਉਧਮ ਸਿੰਘ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D97" s="27" t="n">
@@ -11813,7 +11813,7 @@
         <v>146</v>
       </c>
       <c r="Z97" s="27" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="AA97" s="22" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="AB97" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:31(32.98%) | INC:18(19.15%) | BJP:2 | SAD:10</t>
         </is>
       </c>
       <c r="AC97" s="26" t="inlineStr">
@@ -11847,12 +11847,12 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Jaspal Nagar Sultanwind Road, Nagar Nigam Amritsar, Ward No. 41</t>
+          <t>Baba Deep Singh Khalsa Senior Secondary School - Jaspal Nagar, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>ਜਸਪਾਲ ਨਗਰ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41</t>
+          <t>ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਖਾਲਸਾ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਜਸਪਾਲ ਨਗਰ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D98" s="21" t="n">
@@ -11930,31 +11930,31 @@
         <v>52</v>
       </c>
       <c r="Z98" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA98" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>140</v>
+      </c>
+      <c r="AA98" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB98" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:51(36.43%) | INC:32(22.86%) | BJP:3 | SAD:1</t>
         </is>
       </c>
       <c r="AC98" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD98" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE98" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -11964,12 +11964,12 @@
       </c>
       <c r="B99" s="26" t="inlineStr">
         <is>
-          <t>New Jaspal Nagar Sultanwind Road, Nagar Nigam Amritsar, Ward No. 41</t>
+          <t>Baba Deep Singh Khalsa Senior Secondary School - Jaspal Nagar, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C99" s="26" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਜਸਪਾਲ ਨਗਰ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41</t>
+          <t>ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਖਾਲਸਾ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਜਸਪਾਲ ਨਗਰ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D99" s="27" t="n">
@@ -12047,7 +12047,7 @@
         <v>61</v>
       </c>
       <c r="Z99" s="27" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="AA99" s="22" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="AB99" s="26" t="inlineStr">
         <is>
-          <t>AAP:2(33.33%) | INC:1(16.67%) | BJP:0 | SAD:0</t>
+          <t>AAP:29(29.0%) | INC:26(26.0%) | BJP:6 | SAD:4</t>
         </is>
       </c>
       <c r="AC99" s="26" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Namdev Colony, Main Bazar, Nagar Nigam Amritsar, Ward No. 41 + Gali No.4 Namdev Colony, Near Gurudwara Toot Sahib, Nagar Nigam Amritsar, Ward No. 41 + Namdev Colony, Gali No.6 Gurudwara Toot Sahib, Nagar Nigam Amritsar, Ward No. 41 + Gali No 4 Namdev Colony, Gurdwara Toot Sahib, Nagar Nigam Amritsar, Ward No. 41 + Gali No. 6 Namdev Colony, Nagar Nigam Amritsar, Ward No. 41 + Jaspal Nagar Sultanwind Road, Nagar Nigam Amritsar, Ward No. 41</t>
+          <t>Baba Deep Singh Khalsa Senior Secondary School, Jaspal Nagar Sultanwind Road, Amritsar - Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>ਨਾਮਦੇਵ ਕਲੋਨੀ, ਮੇਨ ਬਾਜ਼ਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਗਾਲੀ ਨੰ.4 ਨਾਮਦੇਵ ਕਲੋਨੀ, ਨੇੜੇ ਗੁਰੂਦੁਆਰਾ ਤੂਤ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਨਾਮਦੇਵ ਕਲੋਨੀ, ਗਾਲੀ ਨੰ.6 ਗੁਰੂਦੁਆਰਾ ਤੂਤ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਗਾਲੀ ਨੰ 4 ਨਾਮਦੇਵ ਕਲੋਨੀ, ਗੁਰਦੁਆਰਾ ਤੂਤ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਗਾਲੀ ਨੰ. 6 ਨਾਮਦੇਵ ਕਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਜਸਪਾਲ ਨਗਰ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41</t>
+          <t>ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਖਾਲਸਾ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ, ਜਸਪਾਲ ਨਗਰ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D100" s="21" t="n">
@@ -12164,7 +12164,7 @@
         <v>108</v>
       </c>
       <c r="Z100" s="21" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="AA100" s="22" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
       </c>
       <c r="AB100" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:30(32.26%) | INC:26(27.96%) | BJP:0 | SAD:4</t>
         </is>
       </c>
       <c r="AC100" s="20" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="B101" s="26" t="inlineStr">
         <is>
-          <t>New Jaspal Nagar Sultanwind Road, Nagar Nigam Amritsar, Ward No. 41 + Gali No. 4 Namdev Colony, Nagar Nigam Amritsar, Ward No. 41</t>
+          <t>Baba Deep Singh Khalsa Senior Secondary School - Jaspal Nagar, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C101" s="26" t="inlineStr">
         <is>
-          <t>ਨਿਊ ਜਸਪਾਲ ਨਗਰ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41 + ਗਾਲੀ ਨੰ. 4 ਨਾਮਦੇਵ ਕਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 41</t>
+          <t>ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਖਾਲਸਾ ਸੀਨੀਅਰ ਸੈਕੰਡਰੀ ਸਕੂਲ - ਜਸਪਾਲ ਨਗਰ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D101" s="27" t="n">
@@ -12281,16 +12281,16 @@
         <v>68</v>
       </c>
       <c r="Z101" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>84</v>
+      </c>
+      <c r="AA101" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB101" s="26" t="inlineStr">
         <is>
-          <t>AAP:3(60.0%) | INC:1(20.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:16(19.05%) | INC:26(30.95%) | BJP:3 | SAD:10</t>
         </is>
       </c>
       <c r="AC101" s="26" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="AD101" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE101" s="26" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -12315,12 +12315,12 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Akali Colony, Gurnam Nagar near Saint Kabir School, Municipal Corporation Amritsar, Ward No. 40 + New Gurnam Nagar Street No.20 Ward No. 40</t>
+          <t>Saint Kabir Public High School, Gurnam Nagar Amritsar - Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
         <is>
-          <t>ਅਕਾਲੀ ਕਾਲੋਨੀ, ਗੁਰਨਾਮ ਨਗਰ ਨੇੜੇ ਸੈਂਟ ਕਬੀਰ ਸਕੂਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 40 + ਨਿਊ ਗੁਰਨਾਮ ਨਗਰ ਗਲੀ ਨੰ.20 ਵਾਰਡ ਨੰ. 40</t>
+          <t>ਸੰਟ ਕਬੀਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਗੁਰਨਾਮ ਨਗਰ ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D102" s="21" t="n">
@@ -12398,31 +12398,31 @@
         <v>85</v>
       </c>
       <c r="Z102" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA102" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>117</v>
+      </c>
+      <c r="AA102" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB102" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:38(32.48%) | INC:30(25.64%) | BJP:5 | SAD:2</t>
         </is>
       </c>
       <c r="AC102" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD102" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE102" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -12432,12 +12432,12 @@
       </c>
       <c r="B103" s="26" t="inlineStr">
         <is>
-          <t>Booth 100 - Amritsar South</t>
+          <t>St Kabir Public High School, Gurnam Nagar Amritsar - Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C103" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 100 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸੰਟ ਕਬੀਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਗੁਰਨਾਮ ਨਗਰ ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D103" s="27" t="n">
@@ -12515,16 +12515,16 @@
         <v>146</v>
       </c>
       <c r="Z103" s="27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA103" s="28" t="inlineStr">
+        <v>111</v>
+      </c>
+      <c r="AA103" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
       </c>
       <c r="AB103" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:2(9.52%) | BJP:0 | SAD:0</t>
+          <t>AAP:26(23.42%) | INC:39(35.14%) | BJP:6 | SAD:1</t>
         </is>
       </c>
       <c r="AC103" s="26" t="inlineStr">
@@ -12549,12 +12549,12 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Booth 101 - Amritsar South</t>
+          <t>St. Kabir Public High School - Gurnam Nagar, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 101 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸੇਂਟ ਕਬੀਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ - ਗੁਰਨਾਮ ਨਗਰ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D104" s="21" t="n">
@@ -12632,7 +12632,7 @@
         <v>102</v>
       </c>
       <c r="Z104" s="21" t="n">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="AA104" s="22" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="AB104" s="20" t="inlineStr">
         <is>
-          <t>AAP:3(5.88%) | INC:2(3.92%) | BJP:0 | SAD:0</t>
+          <t>AAP:36(30.0%) | INC:34(28.33%) | BJP:6 | SAD:2</t>
         </is>
       </c>
       <c r="AC104" s="20" t="inlineStr">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="B105" s="26" t="inlineStr">
         <is>
-          <t>Booth 102 - Amritsar South</t>
+          <t>St. Kabir Public High School, Gurnam Nagar, Amritsar - Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C105" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 102 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸੰਟ ਕਬੀਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਗੁਰਨਾਮ ਨਗਰ ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D105" s="27" t="n">
@@ -12749,31 +12749,31 @@
         <v>108</v>
       </c>
       <c r="Z105" s="27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA105" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>108</v>
+      </c>
+      <c r="AA105" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB105" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(4.76%) | BJP:0 | SAD:0</t>
+          <t>AAP:35(32.41%) | INC:24(22.22%) | BJP:1 | SAD:10</t>
         </is>
       </c>
       <c r="AC105" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD105" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE105" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -12783,12 +12783,12 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Booth 103 - Amritsar South</t>
+          <t>St. Kabir Public High School, Gurnam Nagar, Amritsar - Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 103 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸੰਟ ਕਬੀਰ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਗੁਰਨਾਮ ਨਗਰ ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D106" s="21" t="n">
@@ -12866,31 +12866,31 @@
         <v>47</v>
       </c>
       <c r="Z106" s="21" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="AA106" s="24" t="inlineStr">
         <is>
-          <t>UNDECIDED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB106" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:16(18.18%) | INC:31(35.23%) | BJP:4 | SAD:6</t>
         </is>
       </c>
       <c r="AC106" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD106" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE106" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="B107" s="26" t="inlineStr">
         <is>
-          <t>Booth 104 - Amritsar South</t>
+          <t>Shaheed Baba Pratap Singh Memorial Public School, Jaspal Nagar - Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C107" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 104 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸ਼ਹੀਦ ਬਾਬਾ ਪ੍ਰਤਾਪ ਸਿੰਘ ਮੈਮੋਰੀਅਲ ਪਬਲਿਕ ਸਕੂਲ, ਜਸਪਾਲ ਨਗਰ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D107" s="27" t="n">
@@ -12983,31 +12983,31 @@
         <v>67</v>
       </c>
       <c r="Z107" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA107" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>68</v>
+      </c>
+      <c r="AA107" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB107" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(25.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:19(27.94%) | INC:16(23.53%) | BJP:6 | SAD:3</t>
         </is>
       </c>
       <c r="AC107" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD107" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE107" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -13017,12 +13017,12 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Booth 105 - Amritsar South</t>
+          <t>Shaheed Baba Pratap Singh Memorial Public School, Jaspal Nagar, Amritsar - Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 105 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸ਼ਹੀਦ ਬਾਬਾ ਪ੍ਰਤਾਪ ਸਿੰਘ ਮੈਮੋਰੀਅਲ ਪਬਲਿਕ ਸਕੂਲ, ਜਸਪਾਲ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D108" s="21" t="n">
@@ -13100,31 +13100,31 @@
         <v>41</v>
       </c>
       <c r="Z108" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA108" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>119</v>
+      </c>
+      <c r="AA108" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB108" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:38(31.93%) | INC:27(22.69%) | BJP:9 | SAD:2</t>
         </is>
       </c>
       <c r="AC108" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD108" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE108" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -13134,12 +13134,12 @@
       </c>
       <c r="B109" s="26" t="inlineStr">
         <is>
-          <t>Booth 106 - Amritsar South</t>
+          <t>Shaheed Baba Partap Singh Memorial Public School, Jaspal Nagar, Amritsar - Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C109" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 106 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸ਼ਹੀਦ ਬਾਬਾ ਪ੍ਰਤਾਪ ਸਿੰਘ ਮੈਮੋਰੀਅਲ ਪਬਲਿਕ ਸਕੂਲ, ਜਸਪਾਲ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D109" s="27" t="n">
@@ -13217,7 +13217,7 @@
         <v>63</v>
       </c>
       <c r="Z109" s="27" t="n">
-        <v>2</v>
+        <v>141</v>
       </c>
       <c r="AA109" s="22" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AB109" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:52(36.88%) | INC:27(19.15%) | BJP:5 | SAD:7</t>
         </is>
       </c>
       <c r="AC109" s="26" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>Booth 107 - Amritsar South</t>
+          <t>Govt Elementary School, Guru Arjan Dev Nagar - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C110" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 107 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਗੁਰੂ ਅਰਜਨ ਦੇਵ ਨਗਰ - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D110" s="21" t="n">
@@ -13334,7 +13334,7 @@
         <v>1</v>
       </c>
       <c r="Z110" s="21" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="AA110" s="22" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="AB110" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:37(36.27%) | INC:18(17.65%) | BJP:2 | SAD:9</t>
         </is>
       </c>
       <c r="AC110" s="20" t="inlineStr">
@@ -13368,12 +13368,12 @@
       </c>
       <c r="B111" s="26" t="inlineStr">
         <is>
-          <t>Booth 108 - Amritsar South</t>
+          <t>Govt Elementary School, Guru Arjan Dev Nagar,, Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C111" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 108 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਗੁਰੂ ਅਰਜਨ ਦੇਵ ਨਗਰ,, ਤਰਨਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D111" s="27" t="n">
@@ -13437,7 +13437,7 @@
       <c r="V111" s="27" t="n">
         <v>62</v>
       </c>
-      <c r="W111" s="28" t="inlineStr">
+      <c r="W111" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -13451,31 +13451,31 @@
         <v>5</v>
       </c>
       <c r="Z111" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA111" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>91</v>
+      </c>
+      <c r="AA111" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB111" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:29(31.87%) | INC:26(28.57%) | BJP:3 | SAD:1</t>
         </is>
       </c>
       <c r="AC111" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD111" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → PENDING</t>
+          <t>AAP → INC → AAP</t>
         </is>
       </c>
       <c r="AE111" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → Survey Pending</t>
+          <t>AAP Regained from INC (AAP → INC → AAP)</t>
         </is>
       </c>
     </row>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Booth 109 - Amritsar South</t>
+          <t>Govt Elementary School, Guru Arjan Dev Nagar,, Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C112" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 109 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਗੁਰੂ ਅਰਜਨ ਦੇਵ ਨਗਰ,, ਤਰਨਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D112" s="21" t="n">
@@ -13554,7 +13554,7 @@
       <c r="V112" s="21" t="n">
         <v>35</v>
       </c>
-      <c r="W112" s="28" t="inlineStr">
+      <c r="W112" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -13568,31 +13568,31 @@
         <v>173</v>
       </c>
       <c r="Z112" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA112" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>121</v>
+      </c>
+      <c r="AA112" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB112" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:26(21.49%) | INC:46(38.02%) | BJP:3 | SAD:3</t>
         </is>
       </c>
       <c r="AC112" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD112" s="20" t="inlineStr">
         <is>
-          <t>AAP → INC → AAP</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE112" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (AAP → INC → AAP)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B113" s="26" t="inlineStr">
         <is>
-          <t>Booth 110 - Amritsar South</t>
+          <t>Govt. Elementary School - Abadi Kot Mangal Singh, Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C113" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 110 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਅਬਾਦੀ ਕੋਟ ਮੰਗਲ ਸਿੰਘ, ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D113" s="27" t="n">
@@ -13685,7 +13685,7 @@
         <v>57</v>
       </c>
       <c r="Z113" s="27" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="AA113" s="22" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="AB113" s="26" t="inlineStr">
         <is>
-          <t>AAP:2(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:26(27.96%) | INC:19(20.43%) | BJP:6 | SAD:9</t>
         </is>
       </c>
       <c r="AC113" s="26" t="inlineStr">
@@ -13719,12 +13719,12 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>Booth 111 - Amritsar South</t>
+          <t>Govt Elementary School - Abadi Kot Mangal Singh, Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 111 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ - ਅਬਾਦੀ ਕੋਟ ਮੰਗਲ ਸਿੰਘ, ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D114" s="21" t="n">
@@ -13802,31 +13802,31 @@
         <v>84</v>
       </c>
       <c r="Z114" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA114" s="24" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>89</v>
+      </c>
+      <c r="AA114" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB114" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:27(30.34%) | INC:23(25.84%) | BJP:5 | SAD:3</t>
         </is>
       </c>
       <c r="AC114" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD114" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE114" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -13836,12 +13836,12 @@
       </c>
       <c r="B115" s="26" t="inlineStr">
         <is>
-          <t>Booth 112 - Amritsar South</t>
+          <t>Govt. Elementary School, Abadi Kot Mangal Singh, Sultanwind Amritsar - Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C115" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 112 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਅਬਾਦੀ ਕੋਟ ਮੰਗਲ ਸਿੰਘ, ਸੁਲਤਾਨਵਿੰਡ ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D115" s="27" t="n">
@@ -13919,31 +13919,31 @@
         <v>110</v>
       </c>
       <c r="Z115" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA115" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>108</v>
+      </c>
+      <c r="AA115" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB115" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:31(28.7%) | INC:28(25.93%) | BJP:2 | SAD:8</t>
         </is>
       </c>
       <c r="AC115" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD115" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE115" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -13953,12 +13953,12 @@
       </c>
       <c r="B116" s="20" t="inlineStr">
         <is>
-          <t>Booth 113 - Amritsar South</t>
+          <t>Taran Taran Road Amritsar - Gurukul Public School, Guru Nanak Colony, Taran Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C116" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 113 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਗੁਰੂਕੁਲ ਪਬਲਿਕ ਸਕੂਲ, ਗੁਰੂ ਨਾਨਕ ਕਲੋਨੀ, ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D116" s="21" t="n">
@@ -14036,31 +14036,31 @@
         <v>129</v>
       </c>
       <c r="Z116" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA116" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>105</v>
+      </c>
+      <c r="AA116" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB116" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(50.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:31(29.52%) | INC:27(25.71%) | BJP:1 | SAD:9</t>
         </is>
       </c>
       <c r="AC116" s="20" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD116" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE116" s="20" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -14070,12 +14070,12 @@
       </c>
       <c r="B117" s="26" t="inlineStr">
         <is>
-          <t>Booth 114 - Amritsar South</t>
+          <t>Taran Taran Road Amritsar - Gurukul Public School, Guru Nanak Colony, Taran Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C117" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 114 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਗੁਰੂਕੁਲ ਪਬਲਿਕ ਸਕੂਲ, ਗੁਰੂ ਨਾਨਕ ਕੈਲੋਨੀ, ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D117" s="27" t="n">
@@ -14153,16 +14153,16 @@
         <v>58</v>
       </c>
       <c r="Z117" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA117" s="29" t="inlineStr">
-        <is>
-          <t>TIED</t>
+        <v>103</v>
+      </c>
+      <c r="AA117" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB117" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(25.0%) | INC:1(25.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:27(26.21%) | INC:32(31.07%) | BJP:3 | SAD:3</t>
         </is>
       </c>
       <c r="AC117" s="26" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="AD117" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → TIED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE117" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → TIED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -14187,12 +14187,12 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>Booth 115 - Amritsar South</t>
+          <t>Saint Kabir Public School English Medium, Gurnam Nagar Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C118" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 115 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸੇਂਟ ਕਬੀਰ ਪਬਲਿਕ ਸਕੂਲ ਇੰਗਲਿਸ਼ ਮੀਡੀਅਮ, ਗੁਰਨਾਮ ਨਗਰ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D118" s="21" t="n">
@@ -14270,31 +14270,31 @@
         <v>49</v>
       </c>
       <c r="Z118" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA118" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>77</v>
+      </c>
+      <c r="AA118" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB118" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:24(31.17%) | INC:20(25.97%) | BJP:1 | SAD:5</t>
         </is>
       </c>
       <c r="AC118" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD118" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE118" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -14304,12 +14304,12 @@
       </c>
       <c r="B119" s="26" t="inlineStr">
         <is>
-          <t>Booth 116 - Amritsar South</t>
+          <t>Govt. Elementary School (Boys), Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C119" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 116 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ (ਲੜਕੇ), ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D119" s="27" t="n">
@@ -14336,7 +14336,7 @@
       <c r="K119" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L119" s="28" t="inlineStr">
+      <c r="L119" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -14373,7 +14373,7 @@
       <c r="V119" s="27" t="n">
         <v>111</v>
       </c>
-      <c r="W119" s="28" t="inlineStr">
+      <c r="W119" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -14387,31 +14387,31 @@
         <v>29</v>
       </c>
       <c r="Z119" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA119" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>133</v>
+      </c>
+      <c r="AA119" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB119" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:25(18.8%) | INC:50(37.59%) | BJP:5 | SAD:5</t>
         </is>
       </c>
       <c r="AC119" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD119" s="26" t="inlineStr">
         <is>
-          <t>INC → INC → PENDING</t>
+          <t>INC → INC → INC</t>
         </is>
       </c>
       <c r="AE119" s="26" t="inlineStr">
         <is>
-          <t>INC → INC → Survey Pending</t>
+          <t>INC Leading Survey (INC → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -14421,12 +14421,12 @@
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>Booth 117 - Amritsar South</t>
+          <t>Govt. Elementary School (Boys), Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 117 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ (ਲੜਕੇ), ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D120" s="21" t="n">
@@ -14453,7 +14453,7 @@
       <c r="K120" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="L120" s="30" t="inlineStr">
+      <c r="L120" s="28" t="inlineStr">
         <is>
           <t>SAD</t>
         </is>
@@ -14504,31 +14504,31 @@
         <v>93</v>
       </c>
       <c r="Z120" s="21" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="AA120" s="24" t="inlineStr">
         <is>
-          <t>UNDECIDED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB120" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:24(22.43%) | INC:35(32.71%) | BJP:2 | SAD:9</t>
         </is>
       </c>
       <c r="AC120" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD120" s="20" t="inlineStr">
         <is>
-          <t>SAD → AAP → UNDECIDED</t>
+          <t>SAD → AAP → INC</t>
         </is>
       </c>
       <c r="AE120" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (SAD → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (SAD → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B121" s="26" t="inlineStr">
         <is>
-          <t>Booth 118 - Amritsar South</t>
+          <t>Govt. Elementary School (Boys), Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C121" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 118 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ (ਲੜਕੇ), ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D121" s="27" t="n">
@@ -14570,7 +14570,7 @@
       <c r="K121" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L121" s="28" t="inlineStr">
+      <c r="L121" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -14621,7 +14621,7 @@
         <v>35</v>
       </c>
       <c r="Z121" s="27" t="n">
-        <v>5</v>
+        <v>143</v>
       </c>
       <c r="AA121" s="22" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="AB121" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(20.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:50(34.97%) | INC:34(23.78%) | BJP:5 | SAD:3</t>
         </is>
       </c>
       <c r="AC121" s="26" t="inlineStr">
@@ -14655,12 +14655,12 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>Booth 119 - Amritsar South</t>
+          <t>Harman Public High School, Link Road, Sultanwind Road, Amritsar - Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C122" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 119 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਹਰਮਨ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਲਿੰਕ ਰੋਡ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D122" s="21" t="n">
@@ -14687,7 +14687,7 @@
       <c r="K122" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="L122" s="28" t="inlineStr">
+      <c r="L122" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -14724,7 +14724,7 @@
       <c r="V122" s="21" t="n">
         <v>74</v>
       </c>
-      <c r="W122" s="28" t="inlineStr">
+      <c r="W122" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -14738,31 +14738,31 @@
         <v>92</v>
       </c>
       <c r="Z122" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA122" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>130</v>
+      </c>
+      <c r="AA122" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB122" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:9(6.92%) | INC:61(46.92%) | BJP:3 | SAD:10</t>
         </is>
       </c>
       <c r="AC122" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD122" s="20" t="inlineStr">
         <is>
-          <t>INC → INC → AAP</t>
+          <t>INC → INC → INC</t>
         </is>
       </c>
       <c r="AE122" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (INC → INC → AAP)</t>
+          <t>INC Leading Survey (INC → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -14772,12 +14772,12 @@
       </c>
       <c r="B123" s="26" t="inlineStr">
         <is>
-          <t>Booth 120 - Amritsar South</t>
+          <t>Harman Public High School, Link Road, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C123" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 120 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਹਰਮਨ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਲਿੰਕ ਰੋਡ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D123" s="27" t="n">
@@ -14855,31 +14855,31 @@
         <v>146</v>
       </c>
       <c r="Z123" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA123" s="29" t="inlineStr">
-        <is>
-          <t>TIED</t>
+        <v>114</v>
+      </c>
+      <c r="AA123" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB123" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:1(33.33%) | BJP:0 | SAD:0</t>
+          <t>AAP:22(19.3%) | INC:43(37.72%) | BJP:5 | SAD:3</t>
         </is>
       </c>
       <c r="AC123" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD123" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → TIED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE123" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → TIED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -14889,12 +14889,12 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>Booth 121 - Amritsar South</t>
+          <t>Harman Public High School - Link Road, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C124" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 121 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਹਰਮਨ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ - ਲਿੰਕ ਰੋਡ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D124" s="21" t="n">
@@ -14972,31 +14972,31 @@
         <v>156</v>
       </c>
       <c r="Z124" s="21" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="AA124" s="24" t="inlineStr">
         <is>
-          <t>UNDECIDED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB124" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:30(26.55%) | INC:36(31.86%) | BJP:2 | SAD:4</t>
         </is>
       </c>
       <c r="AC124" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD124" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE124" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -15006,12 +15006,12 @@
       </c>
       <c r="B125" s="26" t="inlineStr">
         <is>
-          <t>Booth 122 - Amritsar South</t>
+          <t>Harman Public High School, Amritsar - Link Road, Sultanwind Road, Amritsar</t>
         </is>
       </c>
       <c r="C125" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 122 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਹਰਮਨ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਅੰਮ੍ਰਿਤਸਰ - ਲਿੰਕ ਰੋਡ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D125" s="27" t="n">
@@ -15089,31 +15089,31 @@
         <v>122</v>
       </c>
       <c r="Z125" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA125" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>137</v>
+      </c>
+      <c r="AA125" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB125" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:26(18.98%) | INC:44(32.12%) | BJP:4 | SAD:13</t>
         </is>
       </c>
       <c r="AC125" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD125" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE125" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -15123,12 +15123,12 @@
       </c>
       <c r="B126" s="20" t="inlineStr">
         <is>
-          <t>Booth 123 - Amritsar South</t>
+          <t>Govt. High School (Boys), Patti Mansoor, Amritsar - Sultanwind</t>
         </is>
       </c>
       <c r="C126" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 123 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ (ਲੜਕੇ), ਪੱਤੀ মনਸੂਰ, ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ</t>
         </is>
       </c>
       <c r="D126" s="21" t="n">
@@ -15206,31 +15206,31 @@
         <v>171</v>
       </c>
       <c r="Z126" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" s="24" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>140</v>
+      </c>
+      <c r="AA126" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB126" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:52(37.14%) | INC:21(15.0%) | BJP:3 | SAD:14</t>
         </is>
       </c>
       <c r="AC126" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD126" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE126" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -15240,12 +15240,12 @@
       </c>
       <c r="B127" s="26" t="inlineStr">
         <is>
-          <t>Booth 124 - Amritsar South</t>
+          <t>Govt. High School (Boys), Patti Mansur, Amritsar - Sultanwind</t>
         </is>
       </c>
       <c r="C127" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 124 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ (ਲੜਕੇ), ਪੱਤੀ ਮਨਸੂਰ, ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ</t>
         </is>
       </c>
       <c r="D127" s="27" t="n">
@@ -15309,7 +15309,7 @@
       <c r="V127" s="27" t="n">
         <v>93</v>
       </c>
-      <c r="W127" s="28" t="inlineStr">
+      <c r="W127" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -15323,31 +15323,31 @@
         <v>56</v>
       </c>
       <c r="Z127" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA127" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>137</v>
+      </c>
+      <c r="AA127" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB127" s="26" t="inlineStr">
         <is>
-          <t>AAP:2(66.67%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:14(10.22%) | INC:55(40.15%) | BJP:7 | SAD:12</t>
         </is>
       </c>
       <c r="AC127" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD127" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → AAP</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE127" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (AAP → INC → AAP)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -15357,12 +15357,12 @@
       </c>
       <c r="B128" s="20" t="inlineStr">
         <is>
-          <t>Booth 125 - Amritsar South</t>
+          <t>Govt. High School (Boys), Patti Mansur, Amritsar</t>
         </is>
       </c>
       <c r="C128" s="20" t="inlineStr">
         <is>
-          <t>ਬੂਥ 125 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ (ਲੜਕੇ), ਪੱਤੀ মনਸੁਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D128" s="21" t="n">
@@ -15440,31 +15440,31 @@
         <v>144</v>
       </c>
       <c r="Z128" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA128" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>100</v>
+      </c>
+      <c r="AA128" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB128" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(25.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:29(29.0%) | INC:28(28.0%) | BJP:3 | SAD:5</t>
         </is>
       </c>
       <c r="AC128" s="20" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD128" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE128" s="20" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -15474,12 +15474,12 @@
       </c>
       <c r="B129" s="26" t="inlineStr">
         <is>
-          <t>Daburji G.T. Road Right Side Chungi Sahib, Municipal Corporation Amritsar, Ward No. 36</t>
+          <t>Govt. Elementary School, Lubana Daburji Road, Amritsar - Sultanwind</t>
         </is>
       </c>
       <c r="C129" s="26" t="inlineStr">
         <is>
-          <t>ਦਬੁਰਜੀ ਜੀ.ਟੀ.ਰੋਡ ਸੱਜਾ ਪਾਸਾ ਚੁੰਗੀ ਸਾਹਿਬ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 36</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਲੁਬਾਣਾ ਦਬੁਰਜੀ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ</t>
         </is>
       </c>
       <c r="D129" s="27" t="n">
@@ -15543,7 +15543,7 @@
       <c r="V129" s="27" t="n">
         <v>143</v>
       </c>
-      <c r="W129" s="28" t="inlineStr">
+      <c r="W129" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -15557,31 +15557,31 @@
         <v>62</v>
       </c>
       <c r="Z129" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA129" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>147</v>
+      </c>
+      <c r="AA129" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB129" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:18(12.24%) | INC:59(40.14%) | BJP:5 | SAD:13</t>
         </is>
       </c>
       <c r="AC129" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD129" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → UNDECIDED</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE129" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → INC → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -15591,12 +15591,12 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Gali No 1, Nahre Paar, Daburji Road, Nagar Nigam, Amritsar, Ward No 36 + Alpha International City, G.T. Road, Daburji, Nagar Nigam Amritsar Ward No 36, Amritsar + Abadi Kanwar Farm Near OTC Corporate Foyer Field, Nagar Nigam Amritsar, Ward No. 36 + Kanwar Avenue, Nagar Nigam Amritsar Ward No 36, Amritsar</t>
+          <t>Govt. Elementary School, Lubana Daburji Road, Amritsar</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਨੰ 1, ਨਹਿਰੇ ਪਾਰ, ਦਬੁਰਜੀ ਰੋਡ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 36 + ਅਲਫ਼ਾ ਇੰਟਰਨੈਸ਼ਨਲ ਸਿਟੀ, ਜੀ.ਟੀ. ਰੋਡ, ਦਬੁਰਜੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 36, ਅੰਮ੍ਰਿਤਸਰ + ਅਬਾਦੀ ਕੰਵਰ ਫਾਰਮ ਨੇੜੇ ਓ.ਟੀ.ਸੀ. ਕਾਰਪੋਟ ਫੋਅਰ ਫੀਲਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 36 + ਕਨਵਰ ਐਵੀਨਿਊ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 36, ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਲੁਬਾਣਾ ਦਬੁਰਜੀ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D130" s="21" t="n">
@@ -15660,7 +15660,7 @@
       <c r="V130" s="21" t="n">
         <v>55</v>
       </c>
-      <c r="W130" s="28" t="inlineStr">
+      <c r="W130" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -15674,31 +15674,31 @@
         <v>82</v>
       </c>
       <c r="Z130" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA130" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>120</v>
+      </c>
+      <c r="AA130" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB130" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:29(24.17%) | INC:40(33.33%) | BJP:2 | SAD:6</t>
         </is>
       </c>
       <c r="AC130" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD130" s="20" t="inlineStr">
         <is>
-          <t>AAP → INC → AAP</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE130" s="20" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (AAP → INC → AAP)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -15708,12 +15708,12 @@
       </c>
       <c r="B131" s="26" t="inlineStr">
         <is>
-          <t>Pyramid City, Municipal Corporation Amritsar, Ward No. 25 + Baba Budha Ji Avenue Municipal Corporation Amritsar, Ward No. 36 + Surya Vihar, Municipal Corporation Ward No. 36 Amritsar + Nimbu Baba Budha Ji Avenue, Municipal Corporation Ward No. 36 Amritsar</t>
+          <t>Government High School, Lubana Daburji - Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C131" s="26" t="inlineStr">
         <is>
-          <t>ਪੀਰਾਮਿੰਡ ਸਿਟੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 25 + ਬਾਬਾ ਬੁੱਢਾ ਜੀ ਐਵੇਨਿਊ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 36 + ਸੁਰਿਆਆ ਵਿਹਾਰ, ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ.36 ਅੰਮ੍ਰਿਤਸਰ + ਨਿੰਭੂ ਬਾਬਾ ਬੁੱਢਾ ਜੀ ਐਵੇਨਿਊ, ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ.36 ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ, ਲੁਬਾਣਾ ਦਬੁਰਜੀ - ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D131" s="27" t="n">
@@ -15740,7 +15740,7 @@
       <c r="K131" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="L131" s="28" t="inlineStr">
+      <c r="L131" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -15777,7 +15777,7 @@
       <c r="V131" s="27" t="n">
         <v>116</v>
       </c>
-      <c r="W131" s="28" t="inlineStr">
+      <c r="W131" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -15791,31 +15791,31 @@
         <v>19</v>
       </c>
       <c r="Z131" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA131" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>142</v>
+      </c>
+      <c r="AA131" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB131" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:14(9.86%) | INC:61(42.96%) | BJP:5 | SAD:9</t>
         </is>
       </c>
       <c r="AC131" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD131" s="26" t="inlineStr">
         <is>
-          <t>INC → INC → PENDING</t>
+          <t>INC → INC → INC</t>
         </is>
       </c>
       <c r="AE131" s="26" t="inlineStr">
         <is>
-          <t>INC → INC → Survey Pending</t>
+          <t>INC Leading Survey (INC → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -15825,12 +15825,12 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>Abadi Mandir Wale Plot, Subhash Colony, Gali No. 4, Nagar Nigam Amritsar, Ward No. 39 + Abadi Darshan Avenue, Nagar Nigam, Amritsar Ward No. 36, Amritsar + Darshan Avenue, B-Block, Sultanwind Road, Nagar Nigam, Amritsar, Ward No. 36, Amritsar + Abadi Bazigar G.T. Road, Nagar Nigam Amritsar, Ward No. 36</t>
+          <t>Govt High School, Lubana Daburji Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C132" s="20" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਮੰਦਰ ਵਾਲੇ ਪਲਾਟ, ਸੁਭਾਸ਼ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39 + ਅਬਾਦੀ ਦਰਸ਼ਨ ਐਵੇਨਿਊ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 36, ਅੰਮ੍ਰਿਤਸਰ + ਦਰਸ਼ਨ ਐਵੇਨਿਊ, ਬੀ-ਬਲੌਕ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 36, ਅੰਮ੍ਰਿਤਸਰ + ਅਬਾਦੀ ਬਾਜੀਗਰ ਜੀ.ਟੀ. ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 36</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ, ਲੁਬਾਣਾ ਦਬੁਰਜੀ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D132" s="21" t="n">
@@ -15908,31 +15908,31 @@
         <v>131</v>
       </c>
       <c r="Z132" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA132" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>94</v>
+      </c>
+      <c r="AA132" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB132" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:30(31.91%) | INC:25(26.6%) | BJP:4 | SAD:2</t>
         </is>
       </c>
       <c r="AC132" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD132" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE132" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -15942,12 +15942,12 @@
       </c>
       <c r="B133" s="26" t="inlineStr">
         <is>
-          <t>Sultanwind Abadi Lakha Singh, Municipal Corporation Amritsar, Ward No. 36 + Abadi Subhash Colony, Street No. 1, Municipal Corporation Amritsar, Ward No. 38 + Jasbir Nagar Daburji Road, Municipal Corporation Amritsar, Ward No. 36 + Abadi G.T. Road Field Amritsar, Municipal Corporation Amritsar, Ward No. 25 + New Darshan Avenue Municipal Corporation Ward No. 36 Amritsar</t>
+          <t>Govt. High School, Lubana Daburji Sultanwind Road Amritsar</t>
         </is>
       </c>
       <c r="C133" s="26" t="inlineStr">
         <is>
-          <t>ਸੁਲਤਾਨਵਿੰਡ ਅਬਾਦੀ ਲੱਖਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 36 + ਅਬਾਦੀ ਸੁਭਾਸ਼ ਕਲੋਨੀ, ਗਲੀ ਨੰ.1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38 + ਜਸਬੀਰ ਨਗਰ ਦਬੁਰਜੀ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 36 + ਅਬਾਦੀ ਜੀ.ਟੀ. ਰੋਡ ਫੀਲਡ ਅੰਮ੍ਰਿਤਸਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 25 + ਨਿਊ ਦਰਸ਼ਨ ਐਵੇਨਿਊ ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ.36 ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਸਰਕਾਰੀ ਹਾਈ ਸਕੂਲ, ਲੁਬਾਣਾ ਦਬੁਰਜੀ ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D133" s="27" t="n">
@@ -16025,31 +16025,31 @@
         <v>41</v>
       </c>
       <c r="Z133" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA133" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>61</v>
+      </c>
+      <c r="AA133" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB133" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:14(22.95%) | INC:20(32.79%) | BJP:0 | SAD:4</t>
         </is>
       </c>
       <c r="AC133" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD133" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE133" s="26" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -16059,12 +16059,12 @@
       </c>
       <c r="B134" s="20" t="inlineStr">
         <is>
-          <t>Abadi Subhash Colony, Mandir Wali Side, Nagar Nigam Amritsar, Ward No. 39 + Gate Enclave, Near Taran Wala Pull, Nagar Nigam Amritsar, Ward No. 39 + Ujagar Nagar, Sultanwind Road Nagar Nigam, Amritsar, Ward No. 39 + Harkrishan Avenue, Nagar Nigam Amritsar, Ward No. 39 + Abadi Dasmesh Engineering Works, Nagar Nigam Amritsar, Ward No. 25</t>
+          <t>Sri Harkrishan Public School - G.T. Road, Sultanwind Link Road, Amritsar</t>
         </is>
       </c>
       <c r="C134" s="20" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਸੁਭਾਸ਼ ਕਲੋਨੀ,, ਮੰਦਿਰ ਵਾਲੀ ਸਾਈਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39 + ਗੇਟ ਇਨਕਲੇਵ, ਨਜਦੀਕ ਤਾਰਾਂ ਵਾਲਾ ਪੁੱਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39 + ਉਜਾਗਰ ਨਗਰ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 39 + ਹਰਕ੍ਰਿਸ਼ਨ ਐਵੀਨਿਊ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 39 + ਅਬਾਦੀ ਦਸਮੇਸ਼ ਇੰਜੀਨਿਰਿੰਗ ਵਰਕਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 25</t>
+          <t>ਸ੍ਰੀ ਹਰਕ੍ਰਿਸ਼ਨ ਪਬਲਿਕ ਸਕੂਲ - ਜੀ.ਟੀ. ਰੋਡ, ਸੁਲਤਾਨਵਿੰਡ ਲਿੰਕ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D134" s="21" t="n">
@@ -16142,16 +16142,16 @@
         <v>211</v>
       </c>
       <c r="Z134" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA134" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>156</v>
+      </c>
+      <c r="AA134" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB134" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:38(24.36%) | INC:40(25.64%) | BJP:10 | SAD:13</t>
         </is>
       </c>
       <c r="AC134" s="20" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="AD134" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE134" s="20" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -16176,12 +16176,12 @@
       </c>
       <c r="B135" s="26" t="inlineStr">
         <is>
-          <t>Mandar Colony, G.T. Road Side, Municipal Corporation Amritsar, Ward No. 39 + Ram Avenue, Municipal Corporation Amritsar, Ward No. 39 + Abadi Mandir Wale Plat, Subhash Colony, Street No. 4, Municipal Corporation Amritsar, Ward No. 39</t>
+          <t>Sri Harkrishan Public School, Chowk Baba Sahib, Prag Das Chowk, Amritsar - Sultanwind</t>
         </is>
       </c>
       <c r="C135" s="26" t="inlineStr">
         <is>
-          <t>ਮੰਦਰ ਕਾਲੋਨੀ, ਜੀ.ਟੀ. ਰੋਡ ਵਾਲਾ ਪਾਸਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39 + ਰਾਮ ਐਵੇਨਿਊ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 39 + ਅਬਾਦੀ ਮੰਦਰ ਵਾਲੇ ਪਲਾਟ, ਸੁਭਾਸ਼ ਕਾਲੋਨੀ, ਗਲੀ ਨੰ. 4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39</t>
+          <t>ਸ੍ਰੀ ਹਰਕ੍ਰਿਸ਼ਨ ਪਬਲਿਕ ਸਕੂਲ, ਚੌਂਕ ਬਾਬਾ ਸਾਹਿਬ, ਪਰਾਗ ਦਾਸ ਚੌਂਕ, ਅੰਮ੍ਰਿਤਸਰ - ਸੁਲਤਾਨਵਿੰਡ</t>
         </is>
       </c>
       <c r="D135" s="27" t="n">
@@ -16259,7 +16259,7 @@
         <v>189</v>
       </c>
       <c r="Z135" s="27" t="n">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="AA135" s="22" t="inlineStr">
         <is>
@@ -16268,12 +16268,12 @@
       </c>
       <c r="AB135" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:56(38.89%) | INC:21(14.58%) | BJP:3 | SAD:13</t>
         </is>
       </c>
       <c r="AC135" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD135" s="26" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>Abadi Kot Mit Singh, Nagar Nigam Amritsar, Ward No. 38</t>
+          <t>Taran Taran Road Amritsar - Amanjyoti Modern School, Kot Mit Singh, Taran Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਕੋਟ ਮିਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਅਮਨਜੋਤੀ ਮਾਡਰਨ ਸਕੂਲ, ਕੋਟ ਮিত ਸਿੰਘ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D136" s="21" t="n">
@@ -16376,31 +16376,31 @@
         <v>138</v>
       </c>
       <c r="Z136" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA136" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>126</v>
+      </c>
+      <c r="AA136" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB136" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:41(32.54%) | INC:30(23.81%) | BJP:0 | SAD:11</t>
         </is>
       </c>
       <c r="AC136" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD136" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE136" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -16410,12 +16410,12 @@
       </c>
       <c r="B137" s="26" t="inlineStr">
         <is>
-          <t>Abadi Kot Mit Singh, Nagar Nigam Amritsar, Ward No. 38</t>
+          <t>Tarn Taran Road Amritsar - Amanjyoti Modern School, Kot Mit Singh, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C137" s="26" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਕੋਟ ਮਿੱਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਅਮਨਜੋਤੀ ਮਾਡਰਨ ਸਕੂਲ, ਕੋਟ ਮਿਤ ਸਿੰਘ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D137" s="27" t="n">
@@ -16493,31 +16493,31 @@
         <v>168</v>
       </c>
       <c r="Z137" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA137" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>130</v>
+      </c>
+      <c r="AA137" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB137" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:49(37.69%) | INC:15(11.54%) | BJP:1 | SAD:19</t>
         </is>
       </c>
       <c r="AC137" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD137" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE137" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -16527,12 +16527,12 @@
       </c>
       <c r="B138" s="20" t="inlineStr">
         <is>
-          <t>Abadi Davinder Nagar, Nagar Nigam Amritsar, Ward No. 38 + Kot Vadhava Singh, Near Kecher Rice Mill, Nagar Nigam Amritsar, Ward No. 38 + Abadi Mata Ganga Ji Nagar, Nagar Nigam Amritsar, Ward No. 38 + Abadi Bagichi Bhagta Kot Mitt Singh, Nagar Nigam Amritsar, Ward No. 37 + Punjabi Bagh Colony, Nagar Nigam Ward No. 37 Amritsar</t>
+          <t>Amanjyoti Modern School - Kot Mit Singh, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C138" s="20" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਦਵਿੰਦਰ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38 + ਕੋਟ ਵਧਾਵਾ ਸਿੰਘ, ਨੇੜੇ ਕੇਚਰ ਰਾਇਸ ਮਿੱਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38 + ਅਬਾਦੀ ਮਾਤਾ ਗੰਗਾ ਜੀ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38 + ਅਬਾਦੀ ਬਗੀਚੀ ਭਗਤਾ ਕੋਟ ਮਿੱਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 37 + ਪੰਜਾਬੀ ਬਾਗ਼ ਕਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ.37 ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਅਮਨਜੋਤੀ ਮਾਡਰਨ ਸਕੂਲ - ਕੋਟ ਮਿੱਤ ਸਿੰਘ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D138" s="21" t="n">
@@ -16610,31 +16610,31 @@
         <v>52</v>
       </c>
       <c r="Z138" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA138" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>99</v>
+      </c>
+      <c r="AA138" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB138" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:2(66.67%) | BJP:0 | SAD:0</t>
+          <t>AAP:33(33.33%) | INC:23(23.23%) | BJP:1 | SAD:6</t>
         </is>
       </c>
       <c r="AC138" s="20" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD138" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE138" s="20" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -16644,12 +16644,12 @@
       </c>
       <c r="B139" s="26" t="inlineStr">
         <is>
-          <t>Sultanwind, Abadi Kot Mint Singh, Nagar Nigam Amritsar, Ward No. 38 + Abadi Kot Mint Singh Nagar Nigam Ward No. 38</t>
+          <t>Govt Elementary School, Tarn Taran Road, Main Building No. 2 - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C139" s="26" t="inlineStr">
         <is>
-          <t>ਸੁਲਤਾਨਵਿੰਡ,ਅਬਾਦੀ ਕੋਟ ਮਿੰਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38 + ਅਬਾਦੀ ਕੋਟ ਮਿੰਤ ਸਿੰਘ ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ 38</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਮੇਨ ਬਿਲਡਿੰਗ ਨੰ. 2 - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D139" s="27" t="n">
@@ -16727,31 +16727,31 @@
         <v>91</v>
       </c>
       <c r="Z139" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA139" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>124</v>
+      </c>
+      <c r="AA139" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB139" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(20.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:38(30.65%) | INC:31(25.0%) | BJP:6 | SAD:5</t>
         </is>
       </c>
       <c r="AC139" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD139" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE139" s="26" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -16761,12 +16761,12 @@
       </c>
       <c r="B140" s="20" t="inlineStr">
         <is>
-          <t>Abadi Kot Mitt Singh, Nagar Nigam Amritsar, Ward No. 38</t>
+          <t>Govt Elementary School, Taran Taran Road, Main Building No. 2 - Taran Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C140" s="20" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਕੋਟ ਮਿੱਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਮੇਨ ਬਿਲਡਿੰਗ ਨੰ. 2 - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D140" s="21" t="n">
@@ -16844,31 +16844,31 @@
         <v>94</v>
       </c>
       <c r="Z140" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA140" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>90</v>
+      </c>
+      <c r="AA140" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB140" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(66.67%) | INC:1(33.33%) | BJP:0 | SAD:0</t>
+          <t>AAP:24(26.67%) | INC:26(28.89%) | BJP:5 | SAD:3</t>
         </is>
       </c>
       <c r="AC140" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD140" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → AAP</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE140" s="20" t="inlineStr">
         <is>
-          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -16878,12 +16878,12 @@
       </c>
       <c r="B141" s="26" t="inlineStr">
         <is>
-          <t>Abadi Gurduare Wali Gali Khalsa Nagar, Nagar Nigam Amritsar, Ward No. 38 + Abadi Gurduare To Agge Wali Gali Khalsa Nagar, Nagar Nigam Amritsar, Ward No. 38 + Abadi Kot Mitt Singh, Nagar Nigam Amritsar, Ward No. 38 + Kot Mitt Singh, Gali No. 1,2,3,4,5, Nagar Nigam Amritsar, Ward No. 38</t>
+          <t>Taran Taran Road Amritsar - Govt. Elementary Smart School, Kot Mitt Singh Amritsar</t>
         </is>
       </c>
       <c r="C141" s="26" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਗੁਰਦੁਆਰੇ ਵਾਲੀ ਗਲੀ ਖਾਲਸਾ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38 + ਅਬਾਦੀ ਗੁਰਦੁਆਰੇ ਤੋ ਅੱਗੇ ਵਾਲੀ ਗਲੀ ਖਾਲਸਾ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38 + ਅਬਾਦੀ ਕੋਟ ਮਿੱਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38 + ਕੋਟ ਮਿੱਤ ਸਿੰਘ, ਗਲੀ ਨੰ. 1,2,3,4,5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਮਾਰਟ ਸਕੂਲ, ਕੋਟ ਮਿੱਤ ਸਿੰਘ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D141" s="27" t="n">
@@ -16961,31 +16961,31 @@
         <v>110</v>
       </c>
       <c r="Z141" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA141" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>114</v>
+      </c>
+      <c r="AA141" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB141" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:33(28.95%) | INC:31(27.19%) | BJP:0 | SAD:10</t>
         </is>
       </c>
       <c r="AC141" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD141" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE141" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -16995,12 +16995,12 @@
       </c>
       <c r="B142" s="20" t="inlineStr">
         <is>
-          <t>Sultanwind, Abadi Khalsa Nagar, Nagar Nigam Amritsar, O.G. 85 Ward No. 38</t>
+          <t>Tarn Taran Road Amritsar - Govt. Elementary School, Khalsa Nagar, Bhai Makh Singh Road, Amritsar</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
         <is>
-          <t>ਸੁਲਤਾਨਵਿੰਡ, ਅਬਾਦੀ ਖਾਲਸਾ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ੳ.ਜੀ. 85 ਵਾਰਡ ਨੰ 38</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਖਾਲਸਾ ਨਗਰ, ਭਾਈ ਮੱਖ ਸਿੰਘ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D142" s="21" t="n">
@@ -17078,16 +17078,16 @@
         <v>81</v>
       </c>
       <c r="Z142" s="21" t="n">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="AA142" s="24" t="inlineStr">
         <is>
-          <t>TIED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB142" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(50.0%) | INC:1(50.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:18(20.22%) | INC:33(37.08%) | BJP:2 | SAD:5</t>
         </is>
       </c>
       <c r="AC142" s="20" t="inlineStr">
@@ -17097,12 +17097,12 @@
       </c>
       <c r="AD142" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → TIED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE142" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → TIED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -17112,12 +17112,12 @@
       </c>
       <c r="B143" s="26" t="inlineStr">
         <is>
-          <t>Abadi Khalsa Colony, Kot Mint Singh, Nagar Nigam Amritsar Ward No 38 + Abadi Gurduware Wali Gali Khalsa Nagar, Nagar Nigam Amritsar, Ward No. 38</t>
+          <t>Paragon Pardect Public School, Khalsa Nagar, Bhai Mukh Singh Road, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C143" s="26" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਖਾਲਸਾ ਕਲੋਨੀ, ਕੋਟ ਮਿੰਤ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 38 + ਅਬਾਦੀ ਗੁਰਦੁਆਰੇ ਵਾਲੀ ਗਲੀ ਖਾਲਸਾ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38</t>
+          <t>ਪੈਰਾਗਾਨ ਪਰਡੈਕਟ ਪਬਲਿਕ ਸਕੂਲ, ਖਾਲਸਾ ਨਗਰ, ਭਾਈ ਮੱਖ ਸਿੰਘ ਰੋਡ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D143" s="27" t="n">
@@ -17195,31 +17195,31 @@
         <v>91</v>
       </c>
       <c r="Z143" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA143" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>77</v>
+      </c>
+      <c r="AA143" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB143" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:27(35.06%) | INC:19(24.68%) | BJP:2 | SAD:2</t>
         </is>
       </c>
       <c r="AC143" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD143" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE143" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="B144" s="20" t="inlineStr">
         <is>
-          <t>Abadi Main Bazar, Bhai Manjh Road, Mata Ganga Ji Nagar, Nagar Nigam, Amritsar Ward No. 38, Amritsar. + Abadi Mata Ganga Ji Nagar, Nagar Nigam Amritsar, Ward No. 38</t>
+          <t>Taran Taran Road Amritsar - Paragon Product Public School, Khalsa Nagar, Bhai Mukh Singh Road, Taran Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C144" s="20" t="inlineStr">
         <is>
-          <t>ਆਬਾਦੀ ਮੇਨ ਬਜਾਰ, ਭਾਈ ਮਾਂਝ ਰੋਡ, ਮਾਤਾ ਗੰਗਾ ਜੀ ਨਗਰ, ਨਗਰ ਨਿਗਮ,ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 38, ਅੰਮ੍ਰਿਤਸਰ. + ਆਬਾਦੀ ਮਾਤਾ ਗੰਗਾ ਜੀ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38</t>
+          <t>ਤৰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਪੈਰਾਗਾਨ ਪਰਡੈਕਟ ਪਬਲਿਕ ਸਕੂਲ, ਖਾਲਸਾ ਨਗਰ, ਭਾਈ ਮੱਖ ਸਿੰਘ ਰੋਡ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D144" s="21" t="n">
@@ -17312,31 +17312,31 @@
         <v>213</v>
       </c>
       <c r="Z144" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA144" s="24" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>106</v>
+      </c>
+      <c r="AA144" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB144" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:38(35.85%) | INC:22(20.75%) | BJP:2 | SAD:7</t>
         </is>
       </c>
       <c r="AC144" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD144" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE144" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -17346,12 +17346,12 @@
       </c>
       <c r="B145" s="26" t="inlineStr">
         <is>
-          <t>Bhai Kanaiya Ji Birdh Ashram, Nagar Nigam, Amritsar, Ward No. 38 + Abadi Main Bazaar, Bhai Manjh Road, Mata Ganga Ji Nagar, Nagar Nigam, Amritsar Ward No 38, Amritsar. + Abadi Guruduware te Agge Vali Gali Khalsa Nagar, Nagar Nigam Amritsar, Ward No. 38</t>
+          <t>Paragon Pardect Public School - Khalsa Nagar, Bhai Mukh Singh Road, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C145" s="26" t="inlineStr">
         <is>
-          <t>ਭਾਈ ਕਨਈਆ ਜੀ ਬਿਰਧ ਆਸ਼ਰਮ, ਨਗਰ ਨਿਗਮ, ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38 + ਆਬਾਦੀ ਮੇਨ ਬਾਜ਼ਾਰ, ਭਾਈ ਮਾਂਝ ਰੋਡ, ਮਾਤਾ ਗੰਗਾ ਜੀ ਨਗਰ, ਨਗਰ ਨਿਗਮ,ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 38, ਅੰਮ੍ਰਿਤਸਰ. + ਆਬਾਦੀ ਗੁਰਦੁਆਰੇ ਤੇ ਅੱਗੇ ਵਾਲੀ ਗਲੀ ਖਾਲਸਾ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38</t>
+          <t>ਪੈਰਾਗਾਨ ਪਰਡੈਕਟ ਪਬਲਿਕ ਸਕੂਲ - ਖਾਲਸਾ ਨਗਰ, ਭਾਈ ਮੱਖ ਸਿੰਘ ਰੋਡ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D145" s="27" t="n">
@@ -17378,7 +17378,7 @@
       <c r="K145" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="L145" s="28" t="inlineStr">
+      <c r="L145" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -17429,31 +17429,31 @@
         <v>37</v>
       </c>
       <c r="Z145" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA145" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>150</v>
+      </c>
+      <c r="AA145" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB145" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:51(34.0%) | INC:41(27.33%) | BJP:1 | SAD:5</t>
         </is>
       </c>
       <c r="AC145" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD145" s="26" t="inlineStr">
         <is>
-          <t>INC → AAP → UNDECIDED</t>
+          <t>INC → AAP → AAP</t>
         </is>
       </c>
       <c r="AE145" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (INC → AAP → UNDECIDED)</t>
+          <t>INC → AAP → AAP</t>
         </is>
       </c>
     </row>
@@ -17463,12 +17463,12 @@
       </c>
       <c r="B146" s="20" t="inlineStr">
         <is>
-          <t>Abadi Behiniwal, Nagar Nigam Amritsar, Ward No. 37</t>
+          <t>Shaheed Gurmeet Singh Government Secondary School (Girls), Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C146" s="20" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਬਹਿਣੀਵਾਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 37</t>
+          <t>ਸ਼ਹੀਦ ਗੁਰਮੀਤ ਸਿੰਘ ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ), ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D146" s="21" t="n">
@@ -17546,31 +17546,31 @@
         <v>153</v>
       </c>
       <c r="Z146" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA146" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>141</v>
+      </c>
+      <c r="AA146" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB146" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:52(36.88%) | INC:28(19.86%) | BJP:2 | SAD:10</t>
         </is>
       </c>
       <c r="AC146" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD146" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE146" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -17580,12 +17580,12 @@
       </c>
       <c r="B147" s="26" t="inlineStr">
         <is>
-          <t>Abadi Taraf Behnival, Nagar Nigam Amritsar, Ward No. 39</t>
+          <t>Shaheed Gurmeet Singh Government Secondary School (Girls), Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C147" s="26" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਤਰਫ ਬਹਿਨੀਵਾਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39</t>
+          <t>ਸ਼ਹੀਦ ਗੁਰਮੀਤ ਸਿੰਘ ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ), ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D147" s="27" t="n">
@@ -17663,31 +17663,31 @@
         <v>193</v>
       </c>
       <c r="Z147" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA147" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>120</v>
+      </c>
+      <c r="AA147" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB147" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:57(47.5%) | INC:16(13.33%) | BJP:5 | SAD:0</t>
         </is>
       </c>
       <c r="AC147" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD147" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE147" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -17697,12 +17697,12 @@
       </c>
       <c r="B148" s="20" t="inlineStr">
         <is>
-          <t>Abadi Patti Sultan, Nagar Nigam Amritsar, Ward No. 37 + Abadi Khalsa Colony, Opposite Petrol Pump, Nagar Nigam Amritsar, Ward No. 38</t>
+          <t>Shaheed Gurmeet Singh Government Secondary School (Girls), Sultanwind - Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C148" s="20" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਪੱਤੀ ਸੁਲਤਾਨ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 37 + ਅਬਾਦੀ ਖਾਲਸਾ ਕਲੋਨੀ, ਪੈਟਰੋਲ ਪੰਪ ਸਾਹਮਣੇ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 38</t>
+          <t>ਸ਼ਹੀਦ ਗੁਰਮੀਤ ਸਿੰਘ ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ), ਸੁਲਤਾਨਵਿੰਡ - ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D148" s="21" t="n">
@@ -17729,7 +17729,7 @@
       <c r="K148" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="L148" s="30" t="inlineStr">
+      <c r="L148" s="28" t="inlineStr">
         <is>
           <t>SAD</t>
         </is>
@@ -17766,7 +17766,7 @@
       <c r="V148" s="21" t="n">
         <v>76</v>
       </c>
-      <c r="W148" s="28" t="inlineStr">
+      <c r="W148" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -17780,31 +17780,31 @@
         <v>30</v>
       </c>
       <c r="Z148" s="21" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AA148" s="24" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB148" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:20(24.1%) | INC:28(33.73%) | BJP:1 | SAD:5</t>
         </is>
       </c>
       <c r="AC148" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD148" s="20" t="inlineStr">
         <is>
-          <t>SAD → INC → PENDING</t>
+          <t>SAD → INC → INC</t>
         </is>
       </c>
       <c r="AE148" s="20" t="inlineStr">
         <is>
-          <t>SAD → INC → Survey Pending</t>
+          <t>INC Leading Survey (SAD → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -17814,12 +17814,12 @@
       </c>
       <c r="B149" s="26" t="inlineStr">
         <is>
-          <t>Abadi Taraf Bahinival, Nagar Nigam Amritsar, Ward No. 39 + Gulmarg Avenue, Nagar Nigam Amritsar, Ward No 39, Amritsar. + Diamond Estate, Sultanwind Road, Nagar Nigam Ward No.39 Amritsar + Silver City, Sultanwind Road Ward No.39 Amritsar</t>
+          <t>Shaheed Gurmeet Singh Govt. Secondary School (Girls), Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C149" s="26" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਤਰਫ ਬਹਿਨੀਵਾਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39 + ਗੁਲਮਰਗ ਐਵੀਨਿਊ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ 39, ਅੰਮ੍ਰਿਤਸਰ. + ਡਾਇਮੰਡ ਅਸਟੇਟ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ.39 ਅੰਮ੍ਰਿਤਸਰ + ਸਿਲਵਰ ਸਿਟੀ, ਸੁਲਤਾਨਵਿੰਡ ਰੋਡ ਵਾਰਡ ਨੰ.39 ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਸ਼ਹੀਦ ਗੁਰਮੀਤ ਸਿੰਘ ਸਰਕਾਰੀ ਸੈਕੰਡਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ), ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D149" s="27" t="n">
@@ -17846,7 +17846,7 @@
       <c r="K149" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="L149" s="28" t="inlineStr">
+      <c r="L149" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -17883,7 +17883,7 @@
       <c r="V149" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="W149" s="28" t="inlineStr">
+      <c r="W149" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -17897,31 +17897,31 @@
         <v>65</v>
       </c>
       <c r="Z149" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA149" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>72</v>
+      </c>
+      <c r="AA149" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB149" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:6(8.33%) | INC:34(47.22%) | BJP:2 | SAD:5</t>
         </is>
       </c>
       <c r="AC149" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD149" s="26" t="inlineStr">
         <is>
-          <t>INC → INC → AAP</t>
+          <t>INC → INC → INC</t>
         </is>
       </c>
       <c r="AE149" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (INC → INC → AAP)</t>
+          <t>INC Leading Survey (INC → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -17931,12 +17931,12 @@
       </c>
       <c r="B150" s="20" t="inlineStr">
         <is>
-          <t>Sultanwind (Taraf Behniwal), Nagar Nigam Amritsar, Ward No. 39 + Abadi Behniwal, Nagar Nigam Amritsar, Ward No. 39 + Temple Avenue, Nagar Nigam Ward No.39 Amritsar</t>
+          <t>Govt. Elementary School (Girls), Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C150" s="20" t="inlineStr">
         <is>
-          <t>ਸੁਲਤਾਨਵਿੰਡ (ਤਰਫ ਬਹਿਣੀਵਾਲ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39 + ਅਬਾਦੀ ਬਹਿਣੀਵਾਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39 + ਟੈਪਲ ਐਵੀਨਿਊ, ਨਗਰ ਨਿਗਮ ਵਾਰਡ ਨੰ.39 ਅੰਮ੍ਰਿਤਸਰ</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ), ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D150" s="21" t="n">
@@ -18014,31 +18014,31 @@
         <v>53</v>
       </c>
       <c r="Z150" s="21" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="AA150" s="24" t="inlineStr">
         <is>
-          <t>UNDECIDED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB150" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:30(28.3%) | INC:36(33.96%) | BJP:1 | SAD:1</t>
         </is>
       </c>
       <c r="AC150" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD150" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE150" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -18048,12 +18048,12 @@
       </c>
       <c r="B151" s="26" t="inlineStr">
         <is>
-          <t>Abadi Taraf Behniwal, Nagar Nigam Amritsar, Ward No. 39</t>
+          <t>Govt. Elementary School (Girls), Sultanwind, Amritsar</t>
         </is>
       </c>
       <c r="C151" s="26" t="inlineStr">
         <is>
-          <t>ਅਬਾਦੀ ਤਰਫ ਬਹਿਣੀਵਾਲ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 39</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ (ਲੜਕੀਆਂ), ਸੁਲਤਾਨਵਿੰਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D151" s="27" t="n">
@@ -18131,31 +18131,31 @@
         <v>62</v>
       </c>
       <c r="Z151" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA151" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>69</v>
+      </c>
+      <c r="AA151" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB151" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:30(43.48%) | INC:5(7.25%) | BJP:0 | SAD:10</t>
         </is>
       </c>
       <c r="AC151" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD151" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE151" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -18165,12 +18165,12 @@
       </c>
       <c r="B152" s="20" t="inlineStr">
         <is>
-          <t>Randa Singh Nagar Taran Taran Road, Nagar Nigam Amritsar, Ward No. 44 + Baba Deep Singh Nagar Taran Taran Road (Sarabjit Nagar), Nagar Nigam Amritsar, Ward No. 44</t>
+          <t>Bibi Kaulan Ji Public School - Tarn Taran Road, Amritsar (Building No. 1)</t>
         </is>
       </c>
       <c r="C152" s="20" t="inlineStr">
         <is>
-          <t>ਰਾਂਡਾ ਸਿੰਘ ਨਗਰ ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44 + ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਨਗਰ ਤਰਨ ਤਾਰਨ ਰੋਡ (ਸਰਬਜੀਤ ਨਗਰ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44</t>
+          <t>ਬੀਬੀ ਕੌਲਾਂ ਜੀ ਪਬਲਿਕ ਸਕੂਲ - ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ (ਬਿਲਡਿੰਗ ਨੰ. 1)</t>
         </is>
       </c>
       <c r="D152" s="21" t="n">
@@ -18248,31 +18248,31 @@
         <v>33</v>
       </c>
       <c r="Z152" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA152" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>132</v>
+      </c>
+      <c r="AA152" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB152" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:50(37.88%) | INC:23(17.42%) | BJP:6 | SAD:4</t>
         </is>
       </c>
       <c r="AC152" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD152" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE152" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -18282,12 +18282,12 @@
       </c>
       <c r="B153" s="26" t="inlineStr">
         <is>
-          <t>Baba Deep Singh Avenue, Taran Taran Road, Near Bharat Palace, Municipal Corporation Amritsar Ward No 44, Amritsar. + Utam Nagar, Taran Taran Road, Municipal Corporation. Amritsar. Ward No 44, Amritsar. + Bagichi Lakha Singh Taran Taran Road, Municipal Corporation Amritsar. Ward No 45, Amritsar. + Mata Kaulan Ji Nagar, Amritsar Ward No 44</t>
+          <t>Bibi Kaulan Ji Public School - Taran Taran Road, Amritsar (Building No. 1)</t>
         </is>
       </c>
       <c r="C153" s="26" t="inlineStr">
         <is>
-          <t>ਬਾਬਾ ਦੀਪ ਸਿੰਘ ਐਵੀਨਿਊ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨੇੜੇ ਭਾਰਤ ਪੈਲੇਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 44, ਅੰਮ੍ਰਿਤਸਰ. + ਉਤਮ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ. ਅੰਮ੍ਰਿਤਸਰ. ਵਾਰਡ ਨੰ 44, ਅੰਮ੍ਰਿਤਸਰ. + ਬਗੀਚੀ ਲੱਖਾ ਸਿੰਘ ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ. ਵਾਰਡ ਨੰ 45, ਅੰਮ੍ਰਿਤਸਰ. + ਮਾਤਾ ਕੌਲਾਂ ਜੀ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 44</t>
+          <t>ਬੀਬੀ ਕੌਲਾਂ ਜੀ ਪਬਲਿਕ ਸਕੂਲ - ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ (ਬਿਲਡਿੰਗ ਨੰ. 1)</t>
         </is>
       </c>
       <c r="D153" s="27" t="n">
@@ -18351,7 +18351,7 @@
       <c r="V153" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="W153" s="28" t="inlineStr">
+      <c r="W153" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -18365,16 +18365,16 @@
         <v>6</v>
       </c>
       <c r="Z153" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA153" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>111</v>
+      </c>
+      <c r="AA153" s="30" t="inlineStr">
+        <is>
+          <t>TIED</t>
         </is>
       </c>
       <c r="AB153" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:30(27.03%) | INC:30(27.03%) | BJP:5 | SAD:7</t>
         </is>
       </c>
       <c r="AC153" s="26" t="inlineStr">
@@ -18384,12 +18384,12 @@
       </c>
       <c r="AD153" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → AAP</t>
+          <t>AAP → INC → TIED</t>
         </is>
       </c>
       <c r="AE153" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from INC (AAP → INC → AAP)</t>
+          <t>Close / Undecided (AAP → INC → TIED)</t>
         </is>
       </c>
     </row>
@@ -18399,12 +18399,12 @@
       </c>
       <c r="B154" s="20" t="inlineStr">
         <is>
-          <t>Hari Singh Avenue, Opposite Dera Sant Baba Bhuri Wala, Municipal Corporation Amritsar, Ward No. 44 + Ganda Singh Colony, Tarn Taran Road, Municipal Corporation Amritsar, Ward No. 44</t>
+          <t>Bibi Kaulan Ji Public School - Tarn Taran Road, Amritsar (Building No. 1)</t>
         </is>
       </c>
       <c r="C154" s="20" t="inlineStr">
         <is>
-          <t>ਹਰੀ ਸਿੰਘ ਐਵੇਨਿਊ ਸਾਹਮਣੇ ਡੇਰਾ ਸੰਤ ਬਾਬਾ ਭੂਰੀ ਵਾਲਾ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 44 + ਗੰਡਾ ਸਿੰਘ ਕਲੌਨੀ, ਤਰਨਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44</t>
+          <t>ਬੀਬੀ ਕੌਲਾਂ ਜੀ ਪਬਲਿਕ ਸਕੂਲ - ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ (ਬਿਲਡिंग ਨੰ. 1)</t>
         </is>
       </c>
       <c r="D154" s="21" t="n">
@@ -18482,31 +18482,31 @@
         <v>27</v>
       </c>
       <c r="Z154" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA154" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>89</v>
+      </c>
+      <c r="AA154" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB154" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:31(34.83%) | INC:16(17.98%) | BJP:2 | SAD:8</t>
         </is>
       </c>
       <c r="AC154" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD154" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE154" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -18516,12 +18516,12 @@
       </c>
       <c r="B155" s="26" t="inlineStr">
         <is>
-          <t>Booth 152 - Amritsar South</t>
+          <t>Bibi Kaulan Ji Public School, Tarn Taran Road, Amritsar (Building-1) - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C155" s="26" t="inlineStr">
         <is>
-          <t>ਬੂਥ 152 - ਅੰਮ੍ਰਿਤਸਰ ਦੱਖਣੀ</t>
+          <t>ਬੀਬੀ ਕੌਲਾਂ ਜੀ ਪਬਲਿਕ ਸਕੂਲ, ਤਰਨਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ (ਬਿਲਡਿੰਗ-1) - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D155" s="27" t="n">
@@ -18585,7 +18585,7 @@
       <c r="V155" s="27" t="n">
         <v>71</v>
       </c>
-      <c r="W155" s="28" t="inlineStr">
+      <c r="W155" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -18599,31 +18599,31 @@
         <v>29</v>
       </c>
       <c r="Z155" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA155" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>125</v>
+      </c>
+      <c r="AA155" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB155" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:38(30.4%) | INC:28(22.4%) | BJP:11 | SAD:4</t>
         </is>
       </c>
       <c r="AC155" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD155" s="26" t="inlineStr">
         <is>
-          <t>AAP → INC → UNDECIDED</t>
+          <t>AAP → INC → AAP</t>
         </is>
       </c>
       <c r="AE155" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → INC → UNDECIDED)</t>
+          <t>AAP Regained from INC (AAP → INC → AAP)</t>
         </is>
       </c>
     </row>
@@ -18633,12 +18633,12 @@
       </c>
       <c r="B156" s="20" t="inlineStr">
         <is>
-          <t>Guru Amardas Nagar, Taran Taran Road Nagar Nigam Amritsar, Ward No. 42 + Kot Maida Singh Bagihi Mathwali, Nagar Nigam Amritsar, Ward No. 45 + Gali Murbe Wali New Krishna Nagar Taran Taran Road, Nagar Nigam Amritsar, Ward No. 44</t>
+          <t>Govt Elementary School, Kot Khalsa - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C156" s="20" t="inlineStr">
         <is>
-          <t>ਗੁਰੂ ਅਮਰਦਾਸ ਨਗਰ, ਤਰਨ ਤਾਰਨ ਰੋਡ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕੋਟ ਮਾਇਦਾ ਸਿੰਘ ਬਗੀਚੀ ਮਠਵਾਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਗਾਲੀ ਮੁਰਬੇ ਵਾਲੀ ਨਿਉ ਕ੍ਰਿਸ਼ਨਾ ਨਗਰ ਤਰਨ ਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਕੋਟ ਖਾਲਸਾ - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D156" s="21" t="n">
@@ -18716,31 +18716,31 @@
         <v>46</v>
       </c>
       <c r="Z156" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA156" s="24" t="inlineStr">
-        <is>
-          <t>TIED</t>
+        <v>69</v>
+      </c>
+      <c r="AA156" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB156" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(25.0%) | BJP:0 | SAD:1</t>
+          <t>AAP:32(46.38%) | INC:9(13.04%) | BJP:3 | SAD:0</t>
         </is>
       </c>
       <c r="AC156" s="20" t="inlineStr">
         <is>
-          <t>Gurpratap Singh Tikka</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD156" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → TIED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE156" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → TIED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -18750,12 +18750,12 @@
       </c>
       <c r="B157" s="26" t="inlineStr">
         <is>
-          <t>Krishna Nagar Gali No. 1,2 Dera Kale Shah, Municipal Corporation Amritsar, Ward No. 42 + Krishna Nagar Gali Murabbe Vali, Tarn Taran Road, Municipal Corporation Amritsar, Ward No. 44 + Gali Bardana Tarn Taran Road, Municipal Corporation Amritsar, Ward No. 44</t>
+          <t>Govt. Elementary School, Kot Madha Singh, Amritsar. - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C157" s="26" t="inlineStr">
         <is>
-          <t>ਕ੍ਰਿਸ਼ਨਾ ਨਗਰ ਗਲੀ ਨੰ. 1,2 ਡੇਰਾ ਕਾਲੇ ਸ਼ਾਹ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕ੍ਰਿਸ਼ਨਾ ਨਗਰ ਗਲੀ ਮੁਰੱਬੇ ਵਾਲੀ, ਤਰਨਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44 + ਗਲੀ ਬਰਦਾਨਾ ਤਰਨਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਕੋਟ ਮਾਧਾ ਸਿੰਘ, ਅੰਮ੍ਰਿਤਸਰ. - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D157" s="27" t="n">
@@ -18833,31 +18833,31 @@
         <v>68</v>
       </c>
       <c r="Z157" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA157" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>127</v>
+      </c>
+      <c r="AA157" s="30" t="inlineStr">
+        <is>
+          <t>TIED</t>
         </is>
       </c>
       <c r="AB157" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:32(25.2%) | INC:32(25.2%) | BJP:9 | SAD:10</t>
         </is>
       </c>
       <c r="AC157" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD157" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → TIED</t>
         </is>
       </c>
       <c r="AE157" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>Close / Undecided (AAP → AAP → TIED)</t>
         </is>
       </c>
     </row>
@@ -18867,12 +18867,12 @@
       </c>
       <c r="B158" s="20" t="inlineStr">
         <is>
-          <t>Kot Mahana Singh Taran Taran Road, Nagar Nigam Amritsar, Ward No. 45 + Akali Quarter Kot Mahana Singh Taran Taran Road, Nagar Nigam Amritsar, Ward No. 45 + Kot Mahana Singh, Nagar Nigam Amritsar, Ward No. 45 + Dilbag Nagar Gali No. 1 Dera, Nagar Nigam Amritsar, Ward No. 45 + Dilbag Nagar, Nagar Nigam Amritsar, Ward No. 45 + Guru Amar Das Nagar Gali No. 5 Taran Taran Road, Nagar Nigam Amritsar, Ward No. 42 + Murabbe Wali Gali (Navi Abadi) Taran Taran Road, Nagar Nigam Amritsar, Ward No. 44</t>
+          <t>Govt. Elementary School, Kot Madhana Singh, Amritsar - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C158" s="20" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਮਾਹਣਾ ਸਿੰਘ ਤਰਨਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਅਕਾਲੀ ਕ੍ਵਾਟਰ ਕੋਟ ਮਾਹਣਾ ਸਿੰਘ ਤਰਨਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਕੋਟ ਮਾਹਣਾ ਸਿੰਘ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਦਿਲਬਾਗ ਨਗਰ ਗਲੀ ਨੰ. 1 ਡੇਰਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਦਿਲਬਾਗ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਗੁਰੂ ਅਮਰ ਦਾਸ ਨਗਰ ਗਲੀ ਨੰ. 5 ਤਾਰਨ ਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਮੁਰੱਬੇ ਵਾਲੀ ਗਲੀ (ਨਵੀ ਅਬਾਦੀ) ਤਰਨਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44</t>
+          <t>ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਕੂਲ, ਕੋਟ ਮਾਧਣਾ ਸਿੰਘ, ਅੰਮ੍ਰਿਤਸਰ - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D158" s="21" t="n">
@@ -18950,7 +18950,7 @@
         <v>146</v>
       </c>
       <c r="Z158" s="21" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="AA158" s="22" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="AB158" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:49(42.98%) | INC:21(18.42%) | BJP:1 | SAD:2</t>
         </is>
       </c>
       <c r="AC158" s="20" t="inlineStr">
@@ -18984,12 +18984,12 @@
       </c>
       <c r="B159" s="26" t="inlineStr">
         <is>
-          <t>Kot Manda Singh Taran Taran Road, Municipal Corporation Amritsar, Ward No. 45 + Krishna Nagar Taran Taran Road Gali No. 3 Municipal Corporation Amritsar, Ward No. 45 + Gurdev Nagar, Municipal Corporation Amritsar, Ward No. 45</t>
+          <t>156 - Taran Taran Road Amritsar - The Yatshala Public High School, Gurdev Nagar Amritsar</t>
         </is>
       </c>
       <c r="C159" s="26" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਮਾਂਦਾ ਸਿੰਘ ਤਰਨਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਕ੍ਰਿਸ਼ਨਾ ਨਗਰ ਤਰਨਤਾਰਨ ਰੋਡ ਗਲੀ ਨੰ. 3 ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਗੁਰਦੇਵ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45</t>
+          <t>156 - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਦ ਯਾਤਸ਼ਾਲਾ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਗੁਰਦੇਵ ਨਗਰ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D159" s="27" t="n">
@@ -19067,31 +19067,31 @@
         <v>117</v>
       </c>
       <c r="Z159" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA159" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>123</v>
+      </c>
+      <c r="AA159" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB159" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:50(40.65%) | INC:23(18.7%) | BJP:3 | SAD:4</t>
         </is>
       </c>
       <c r="AC159" s="26" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD159" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE159" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -19101,12 +19101,12 @@
       </c>
       <c r="B160" s="20" t="inlineStr">
         <is>
-          <t>Murabbe Wali Gali, Nagar Nigam Amritsar, Ward No. 45</t>
+          <t>157 - Tarn Taran Road Amritsar - Da Patshala Public High School, Gurdev Nagar Amritsar</t>
         </is>
       </c>
       <c r="C160" s="20" t="inlineStr">
         <is>
-          <t>ਮੁਰੱਬੇ ਵਾਲੀ ਗਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45</t>
+          <t>157 - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਦਾ ਪਾਠਸ਼ਾਲਾ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਗੁਰਦੇਵ ਨਗਰ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D160" s="21" t="n">
@@ -19184,31 +19184,31 @@
         <v>91</v>
       </c>
       <c r="Z160" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA160" s="28" t="inlineStr">
-        <is>
-          <t>INC</t>
+        <v>86</v>
+      </c>
+      <c r="AA160" s="22" t="inlineStr">
+        <is>
+          <t>AAP</t>
         </is>
       </c>
       <c r="AB160" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:2(66.67%) | BJP:0 | SAD:0</t>
+          <t>AAP:39(45.35%) | INC:8(9.3%) | BJP:3 | SAD:4</t>
         </is>
       </c>
       <c r="AC160" s="20" t="inlineStr">
         <is>
-          <t>Inderbir Singh Bolaria</t>
+          <t>Dr. Inderbir Singh Nijjar</t>
         </is>
       </c>
       <c r="AD160" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → INC</t>
+          <t>AAP → AAP → AAP</t>
         </is>
       </c>
       <c r="AE160" s="20" t="inlineStr">
         <is>
-          <t>INC Leading Survey (AAP → AAP → INC)</t>
+          <t>AAP Triple Stronghold (22✓ 24✓ 26✓)</t>
         </is>
       </c>
     </row>
@@ -19218,12 +19218,12 @@
       </c>
       <c r="B161" s="26" t="inlineStr">
         <is>
-          <t>Krishna Nagar Taran Taran Road Street No. 4, Municipal Corporation Amritsar, Ward No. 42 + Krishna Nagar Taran Taran Road Street No. 5, Municipal Corporation Amritsar, Ward No. 44 + Krishna Nagar Taran Taran Road Street No. 6, Municipal Corporation Amritsar, Ward No. 44 + Muhabbe Wali Gali, Municipal Corporation Amritsar, Ward No. 45</t>
+          <t>The Pathshala Public High School, Gurdev Nagar Amritsar - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C161" s="26" t="inlineStr">
         <is>
-          <t>ਕ੍ਰਿਸ਼ਨਾ ਨਗਰ ਤਰਨਤਾਰਨ ਰੋਡ ਗਲੀ ਨੰ. 4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 42 + ਕ੍ਰਿਸ਼ਨਾ ਨਗਰ ਤਰਨਤਾਰਨ ਰੋਡ ਗਲੀ ਨੰ. 5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44 + ਕ੍ਰਿਸ਼ਨਾ ਨਗਰ ਤਰਨਤਾਰਨ ਰੋਡ ਗਲੀ ਨੰ. 6, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44 + ਮුਹੱਬੇ ਵਾਲੀ ਗਲੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45</t>
+          <t>ਦਾ ਪਾਠਸ਼ਾਲਾ ਪਬਲਿਕ ਹਾਈ ਸਕੂਲ, ਗੁਰਦੇਵ ਨਗਰ ਅੰਮ੍ਰਿਤਸਰ - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D161" s="27" t="n">
@@ -19301,31 +19301,31 @@
         <v>33</v>
       </c>
       <c r="Z161" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA161" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>65</v>
+      </c>
+      <c r="AA161" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB161" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:19(29.23%) | INC:21(32.31%) | BJP:2 | SAD:0</t>
         </is>
       </c>
       <c r="AC161" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD161" s="26" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE161" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -19335,12 +19335,12 @@
       </c>
       <c r="B162" s="20" t="inlineStr">
         <is>
-          <t>Dasmesh Nagar Gali No. 3, Nagar Nigam Amritsar, Ward No. 44 + Dasmesh Nagar Gali No. 2, Nagar Nigam Amritsar, Ward No. 44 + Ishwar Nagar, Gali No. 3, Nagar Nigam Amritsar, Ward No. 44 + Dasmesh Nagar Gali No. 1, Nagar Nigam Amritsar, Ward No. 50 + Atma Nagar, Gali No. 4, Nagar Nigam Amritsar, Ward No. 45</t>
+          <t>Bibi Kaulan Ji Public School (Building-2) - Taran Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C162" s="20" t="inlineStr">
         <is>
-          <t>ਦਸ਼ਮੇਸ਼ ਨਗਰ ਗਲੀ ਨੰ 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44 + ਦਸ਼ਮੇਸ਼ ਨਗਰ ਗਲੀ ਨੰ. 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44 + ਈਸ਼ਵਰ ਨਗਰ, ਗਲੀ ਨੰ.3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44 + ਦਸ਼ਮੇਸ਼ ਨਗਰ ਗਲੀ ਨੰ. 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਆਤਮਾ ਨਗਰ, ਗਲੀ ਨੰ.4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45</t>
+          <t>ਬੀਬੀ ਕੌਲਾਂ ਜੀ ਪਬਲਿਕ ਸਕੂਲ (ਬਿਲਡਿੰਗ-2) - ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D162" s="21" t="n">
@@ -19418,31 +19418,31 @@
         <v>83</v>
       </c>
       <c r="Z162" s="21" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="AA162" s="24" t="inlineStr">
         <is>
-          <t>UNDECIDED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB162" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:25(21.93%) | INC:38(33.33%) | BJP:7 | SAD:3</t>
         </is>
       </c>
       <c r="AC162" s="20" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD162" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → UNDECIDED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE162" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → UNDECIDED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -19452,12 +19452,12 @@
       </c>
       <c r="B163" s="26" t="inlineStr">
         <is>
-          <t>Guru Nanak Colony, Gali No. 1A Ward No. 44 + Dashmesh Nagar Gali No. 4, Nagar Nigam Amritsar, Ward No. 44 + Dashmesh Nagar Gali No. 5, Nagar Nigam Amritsar, Ward No. 45 + Guru Nanak Colony, Gali No. 6 Ward No. 45 + Baba Budha Ji Nagar, Nagar Nigam Amritsar, Ward No. 45</t>
+          <t>Bibi Kaulan Ji Public School, Tarn Taran Road, Amritsar (Building-2) - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C163" s="26" t="inlineStr">
         <is>
-          <t>ਗੁਰੂ ਨਾਨਕ ਕਲੋਨੀ, ਗਲੀ ਨੰ 1ਏ ਵਾਰਡ ਨੰ. 44 + ਦਸ਼ਮੇਸ਼ ਨਗਰ ਗਲੀ ਨੰ. 4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 44 + ਦਸ਼ਮੇਸ਼ ਨਗਰ ਗਲੀ ਨੰ. 5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਗੁਰੂ ਨਾਨਕ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 6 ਵਾਰਡ ਨੰ. 45 + ਬਾਬਾ ਬੁੱਢਾ ਜੀ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45</t>
+          <t>ਬੀਬੀ ਕੌਲਾਂ ਜੀ ਪਬਲਿਕ ਸਕੂਲ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ (ਬਿਲਡਿੰਗ-2) - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D163" s="27" t="n">
@@ -19535,31 +19535,31 @@
         <v>74</v>
       </c>
       <c r="Z163" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA163" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>150</v>
+      </c>
+      <c r="AA163" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB163" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:29(19.33%) | INC:48(32.0%) | BJP:14 | SAD:6</t>
         </is>
       </c>
       <c r="AC163" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD163" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → PENDING</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE163" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → Survey Pending</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -19569,12 +19569,12 @@
       </c>
       <c r="B164" s="20" t="inlineStr">
         <is>
-          <t>New Shaheed Udham Singh Nagar Street No. 5, Municipal Corporation Amritsar, Ward No. 43 + Bagichi Lakha Singh Taran Taran Road Before Canal, Municipal Corporation Amritsar, Ward No. 45 + New Shaheed Udham Singh Nagar Street No. 2, Municipal Corporation Amritsar, Ward No. 43 + Dev Singh Sham Singh Rice Mill Bank Side Rajput Dharm Kanda Nagar Nigam Amritsar Ward No. 42</t>
+          <t>Govt. Middle School, Kot Madha Singh, Tarn Taran Road, Amritsar</t>
         </is>
       </c>
       <c r="C164" s="20" t="inlineStr">
         <is>
-          <t>ਨਿਉ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.5, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਬਾਗੀਚੀ ਲੱਖਾ ਸਿੰਘ ਤਰਨਤਾਰਨ ਰੋਡ ਨਹਿਰ ਤੋਂ ਪਹਿਲਾਂ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਨਿਉ ਸ਼ਹੀਦ ਊਧਮ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ. 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 43 + ਦੇਵ ਸਿੰਘ ਸ਼ਾਮ ਸਿੰਘ ਰਾਇਸ ਮਿੱਲ ਬੈਂਕ ਸਾਈਡ ਰਾਜਪੂਤ ਧਰਮ ਕੰਡਾ ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ. 42</t>
+          <t>ਸਰਕਾਰੀ ਮਿਡਲ ਸਕੂਲ, ਕੋਟ ਮਾਧਾ ਸਿੰਘ, ਤਰਨ ਤਾਰਨ ਰੋਡ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D164" s="21" t="n">
@@ -19638,7 +19638,7 @@
       <c r="V164" s="21" t="n">
         <v>37</v>
       </c>
-      <c r="W164" s="28" t="inlineStr">
+      <c r="W164" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -19652,16 +19652,16 @@
         <v>19</v>
       </c>
       <c r="Z164" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA164" s="24" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>106</v>
+      </c>
+      <c r="AA164" s="29" t="inlineStr">
+        <is>
+          <t>TIED</t>
         </is>
       </c>
       <c r="AB164" s="20" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:30(28.3%) | INC:30(28.3%) | BJP:7 | SAD:1</t>
         </is>
       </c>
       <c r="AC164" s="20" t="inlineStr">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="AD164" s="20" t="inlineStr">
         <is>
-          <t>AAP → INC → UNDECIDED</t>
+          <t>AAP → INC → TIED</t>
         </is>
       </c>
       <c r="AE164" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → INC → UNDECIDED)</t>
+          <t>Close / Undecided (AAP → INC → TIED)</t>
         </is>
       </c>
     </row>
@@ -19686,12 +19686,12 @@
       </c>
       <c r="B165" s="26" t="inlineStr">
         <is>
-          <t>Shailer Wali Gali Sharma Colony, Nagar Nigam Amritsar, Ward No. 45 + Namak Wali Gali Sharma Colony, Nagar Nigam Amritsar, Ward No. 45 + New Guru Gobind Singh Nagar Gali No. 4, Nagar Nigam Amritsar, Ward No. 50 + New Guru Gobind Singh Nagar Gali No. 3, Nagar Nigam Amritsar, Ward No. 50 + Guru Nanak Colony, Gali No. 5 Ward No. 45 + Guru Nanak Colony, Gali No. 2, Nagar Nigam Amritsar, Ward No. 45</t>
+          <t>Taran Taran Road Amritsar - Shakti Modal School, Sharma Colony, Amritsar</t>
         </is>
       </c>
       <c r="C165" s="26" t="inlineStr">
         <is>
-          <t>ਸ਼ੈਲਰ ਵਾਲੀ ਗਲੀ ਸ਼ਰਮਾ ਕਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਨਮਕ ਵਾਲੀ ਗਲੀ ਸ਼ਰਮਾ ਕਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਨਿਊ ਗੁਰੂ ਗੋਬਿੰਦ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ 4, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਨਿਊ ਗੁਰੂ ਗੋਬਿੰਦ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਗੁਰੂ ਨਾਨਕ ਕਲੋਨੀ, ਗਲੀ ਨੰ.5 ਵਾਰਡ ਨੰ. 45 + ਗੁਰੂ ਨਾਨਕ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਸ਼ਕਤੀ ਮਾਡਲ ਸਕੂਲ, ਸ਼ਰਮਾ ਕਾਲੋਨੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D165" s="27" t="n">
@@ -19769,31 +19769,31 @@
         <v>93</v>
       </c>
       <c r="Z165" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA165" s="29" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+        <v>88</v>
+      </c>
+      <c r="AA165" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB165" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:19(21.59%) | INC:27(30.68%) | BJP:9 | SAD:1</t>
         </is>
       </c>
       <c r="AC165" s="26" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD165" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → PENDING</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE165" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → Survey Pending</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -19803,12 +19803,12 @@
       </c>
       <c r="B166" s="20" t="inlineStr">
         <is>
-          <t>Sharma Colony, Gali No. 1, Nagar Nigam Amritsar, Ward No. 45 + Main Bazar Guru Nanak Colony, Nagar Nigam Amritsar, Ward No. 45 + Chowk Chabutra, Nagar Nigam Amritsar, Ward No. 48 + Gali No. 1 Guru Gobind Singh Nagar, Nagar Nigam Amritsar, Ward No. 45 + Gali No. 1, Guru Gobind Singh Nagar, Nagar Nigam Amritsar, Ward No. 45</t>
+          <t>Shakti Model School - Sharma Colony, Amritsar</t>
         </is>
       </c>
       <c r="C166" s="20" t="inlineStr">
         <is>
-          <t>ਸ਼ਰਮਾ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਮੇਨ ਬਜ਼ਾਰ ਗੁਰੂ ਨਾਨਕ ਕਲੌਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਚੌਂਕ ਚਬੂਤਰਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 48 + ਗਲੀ ਨੰ.1 ਗੁਰੂ ਗੋਬਿੰਦ ਸਿੰਘ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਗਲੀ ਨੰ.1, ਗੁਰੂ ਗੋਬਿੰਦ ਸਿੰਘ ਨਗਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45</t>
+          <t>ਸ਼ਕਤੀ ਮਾਡਲ ਸਕੂਲ - ਸ਼ਰਮਾ ਕਲੋਨੀ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D166" s="21" t="n">
@@ -19886,31 +19886,31 @@
         <v>11</v>
       </c>
       <c r="Z166" s="21" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AA166" s="24" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB166" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey Sample</t>
+          <t>AAP:34(25.0%) | INC:40(29.41%) | BJP:3 | SAD:11</t>
         </is>
       </c>
       <c r="AC166" s="20" t="inlineStr">
         <is>
-          <t>Awaiting Survey</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD166" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → PENDING</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE166" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → Survey Pending</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
@@ -19920,12 +19920,12 @@
       </c>
       <c r="B167" s="26" t="inlineStr">
         <is>
-          <t>Sharma Colony, Gali No. 2, Nagar Nigam Amritsar, Ward No. 45 + Sharma Colony, Gali No. 3, Nagar Nigam Amritsar, Ward No. 45 + Main Road Guru Gobind Singh Palace, Nagar Nigam Amritsar, Ward No. 45 + Guru Gobind Singh Nagar Gali No. 2, Nagar Nigam Amritsar, Ward No. 50</t>
+          <t>Little Flower Public School, Ekta Colony, Guru Gobind Singh Nagar, Amritsar - Tarn Taran Road Amritsar</t>
         </is>
       </c>
       <c r="C167" s="26" t="inlineStr">
         <is>
-          <t>ਸ਼ਰਮਾ ਕਲੋਨੀ, ਗਲੀ ਨੰ 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਸ਼ਰਮਾ ਕਲੋਨੀ, ਗਲੀ ਨੰ 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਮੇਨ ਰੋਡ ਗੁਰੂ ਗੋਬਿੰਦ ਸਿੰਘ ਪੈਲੇਸ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਗੁਰੂ ਗੋਬਿੰਦ ਸਿੰਘ ਨਗਰ ਗਲੀ ਨੰ.2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਲਿਟਲ ਫਲਾਵਰ ਪਬਲਿਕ ਸਕੂਲ, ਏਕਤਾ ਕੈਲਨੀ, ਗੁਰੂ ਗੋਬਿੰਦ ਸਿੰਘ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ - ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D167" s="27" t="n">
@@ -19989,7 +19989,7 @@
       <c r="V167" s="27" t="n">
         <v>62</v>
       </c>
-      <c r="W167" s="28" t="inlineStr">
+      <c r="W167" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -20003,16 +20003,16 @@
         <v>3</v>
       </c>
       <c r="Z167" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA167" s="28" t="inlineStr">
+        <v>90</v>
+      </c>
+      <c r="AA167" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
       </c>
       <c r="AB167" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:1(33.33%) | BJP:0 | SAD:0</t>
+          <t>AAP:17(18.89%) | INC:29(32.22%) | BJP:4 | SAD:8</t>
         </is>
       </c>
       <c r="AC167" s="26" t="inlineStr">
@@ -20037,12 +20037,12 @@
       </c>
       <c r="B168" s="20" t="inlineStr">
         <is>
-          <t>Guru Nanak Colony, Street No. 3, Nagar Nigam Amritsar, Ward No. 45 + Guru Nanak Colony, Main Bazaar, Nagar Nigam Amritsar, Ward No. 45 + Guru Nanak Colony, Street No. 7, Nagar Nigam Amritsar, Ward No. 45</t>
+          <t>Taran Taran Road Amritsar - Little Flower Public School, Ekta Colony, Guru Gobind Singh Nagar, Amritsar</t>
         </is>
       </c>
       <c r="C168" s="20" t="inlineStr">
         <is>
-          <t>ਗੁਰੂ ਨਾਨਕ ਕਲੋਨੀ, ਗਲੀ ਨੰ 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਗੁਰੂ ਨਾਨਕ ਕਲੋਨੀ, ਮੇਨ ਬਾਜਾਰ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਗੁਰੂ ਨਾਨਕ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 7, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਲਿਟਲ ਫਲਾਵਰ ਪਬਲਿਕ ਸਕੂਲ, ਏਕਤਾ ਕੈਲਨੀ, ਗੁਰੂ ਗੋਬਿੰਦ ਸਿੰਘ ਨਗਰ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D168" s="21" t="n">
@@ -20106,7 +20106,7 @@
       <c r="V168" s="21" t="n">
         <v>31</v>
       </c>
-      <c r="W168" s="28" t="inlineStr">
+      <c r="W168" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -20120,7 +20120,7 @@
         <v>46</v>
       </c>
       <c r="Z168" s="21" t="n">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="AA168" s="22" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
       </c>
       <c r="AB168" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:34(30.09%) | INC:29(25.66%) | BJP:8 | SAD:1</t>
         </is>
       </c>
       <c r="AC168" s="20" t="inlineStr">
@@ -20154,12 +20154,12 @@
       </c>
       <c r="B169" s="26" t="inlineStr">
         <is>
-          <t>Himmatpura Gali No. 2, Nagar Nigam Amritsar, Ward No. 50 + Himmatpura Gali No. 3, Nagar Nigam Amritsar, Ward No. 50</t>
+          <t>Tarn Taran Road Amritsar - Gyan Ashram School Nursery Wing, Outside Chatiwind Gate, Amritsar</t>
         </is>
       </c>
       <c r="C169" s="26" t="inlineStr">
         <is>
-          <t>ਹਿੰਮਤਪੁਰਾ ਗਾਲੀ ਨੰ 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਹਿੰਮਤਪੁਰਾ ਗਾਲੀ ਨੰ 3, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਗਿਆਨ ਆਸ਼ਰਮ ਸਕੂਲ ਨਰਸਰੀ ਵਿੰਗ, ਬਾਹਰਵਾਰ ਚਾਟੀਵਿੰਡ ਗੇਟ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D169" s="27" t="n">
@@ -20186,7 +20186,7 @@
       <c r="K169" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="L169" s="28" t="inlineStr">
+      <c r="L169" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -20223,7 +20223,7 @@
       <c r="V169" s="27" t="n">
         <v>63</v>
       </c>
-      <c r="W169" s="28" t="inlineStr">
+      <c r="W169" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -20237,31 +20237,31 @@
         <v>109</v>
       </c>
       <c r="Z169" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA169" s="29" t="inlineStr">
-        <is>
-          <t>UNDECIDED</t>
+        <v>119</v>
+      </c>
+      <c r="AA169" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB169" s="26" t="inlineStr">
         <is>
-          <t>AAP:0(0.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:11(9.24%) | INC:57(47.9%) | BJP:3 | SAD:5</t>
         </is>
       </c>
       <c r="AC169" s="26" t="inlineStr">
         <is>
-          <t>None / Undecided</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD169" s="26" t="inlineStr">
         <is>
-          <t>INC → INC → UNDECIDED</t>
+          <t>INC → INC → INC</t>
         </is>
       </c>
       <c r="AE169" s="26" t="inlineStr">
         <is>
-          <t>Close / Undecided (INC → INC → UNDECIDED)</t>
+          <t>INC Leading Survey (INC → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="B170" s="20" t="inlineStr">
         <is>
-          <t>Guru Nanak Colony, Street No. 1A (Right Side), Nagar Nigam Amritsar, Ward No. 45 + Guru Gobind Singh Colony, Nagar Nigam Amritsar, Ward No. 50 + Chattha Rice Mills, Nagar Nigam Amritsar, Ward No. 45</t>
+          <t>Taran Taran Road Amritsar - Gyan Ashram School Nursery Wing, Outside Chatiwind Gate, Amritsar</t>
         </is>
       </c>
       <c r="C170" s="20" t="inlineStr">
         <is>
-          <t>ਗੁਰੂ ਨਾਨਕ ਕਲੋਨੀ, ਗਲੀ ਨੰ. 1ਏ ( ਸੱਜਾ ਪਾਸਾ ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਗੁਰੂ ਗੋਬਿੰਦ ਸਿੰਘ ਕਲੋਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਚੱਠਾ ਰਾਇਸ ਮਿਲਜ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਗਿਆਨ ਆਸ਼ਰਮ ਸਕੂਲ ਨਰਸਰੀ ਵਿੰਗ, ਬਾਹਰਵਾਰ ਚਾਟੀਵਿੰਡ ਗੇਟ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D170" s="21" t="n">
@@ -20340,7 +20340,7 @@
       <c r="V170" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="W170" s="28" t="inlineStr">
+      <c r="W170" s="24" t="inlineStr">
         <is>
           <t>INC</t>
         </is>
@@ -20354,31 +20354,31 @@
         <v>69</v>
       </c>
       <c r="Z170" s="21" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="AA170" s="24" t="inlineStr">
         <is>
-          <t>TIED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB170" s="20" t="inlineStr">
         <is>
-          <t>AAP:1(33.33%) | INC:0(0.0%) | BJP:1 | SAD:0</t>
+          <t>AAP:2(3.92%) | INC:23(45.1%) | BJP:2 | SAD:6</t>
         </is>
       </c>
       <c r="AC170" s="20" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD170" s="20" t="inlineStr">
         <is>
-          <t>AAP → INC → TIED</t>
+          <t>AAP → INC → INC</t>
         </is>
       </c>
       <c r="AE170" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → INC → TIED)</t>
+          <t>INC Leading Survey (AAP → INC → INC)</t>
         </is>
       </c>
     </row>
@@ -20388,12 +20388,12 @@
       </c>
       <c r="B171" s="26" t="inlineStr">
         <is>
-          <t>Gali No. 1, Nagar Nigam Colony, Nagar Nigam Amritsar, Ward No. 45 + Main Road Himmatpura, Nagar Nigam Amritsar, Ward No. 50 + Sher Singh Tarantaran Road, Nagar Nigam Amritsar, Ward No. 45 + Himmatpura, Gali No. 2, Nagar Nigam Amritsar, Ward No. 50 + Himmatpura Gali No. 1, Nagar Nigam Amritsar, Ward No. 50</t>
+          <t>Taran Taran Road Amritsar - Gyan Ashram School Nursery Wing, Outside Chatiwind Gate, Amritsar</t>
         </is>
       </c>
       <c r="C171" s="26" t="inlineStr">
         <is>
-          <t>ਗਲੀ ਨੰ.1, ਨਗਰ ਨਿਗਮ ਕਲੌਨੀ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ ਵਾਰਡ ਨੰ 45 + ਮੇਨ ਰੋਡ ਹਿੰਮਤਪੁਰਾ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਸ਼ੇਰ ਸਿੰਘ ਤਰਨਤਾਰਨ ਰੋਡ, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 45 + ਹਿੰਮਤਪੁਰਾ, ਗਲੀ ਨੰ. 2, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਹਿੰਮਤਪੁਰਾ ਗਲੀ ਨੰ. 1, ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਗਿਆਨ ਆਸ਼ਰਮ ਸਕੂਲ ਨਰਸਰੀ ਵਿੰਗ, ਬਾਹਰਵਾਰ ਚਾਟੀਵਿੰਡ ਗੇਟ, ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D171" s="27" t="n">
@@ -20471,31 +20471,31 @@
         <v>26</v>
       </c>
       <c r="Z171" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA171" s="22" t="inlineStr">
-        <is>
-          <t>AAP</t>
+        <v>94</v>
+      </c>
+      <c r="AA171" s="24" t="inlineStr">
+        <is>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB171" s="26" t="inlineStr">
         <is>
-          <t>AAP:1(100.0%) | INC:0(0.0%) | BJP:0 | SAD:0</t>
+          <t>AAP:15(15.96%) | INC:33(35.11%) | BJP:9 | SAD:4</t>
         </is>
       </c>
       <c r="AC171" s="26" t="inlineStr">
         <is>
-          <t>Dr. Inderbir Singh Nijjar</t>
+          <t>Inderbir Singh Bolaria</t>
         </is>
       </c>
       <c r="AD171" s="26" t="inlineStr">
         <is>
-          <t>AAP → BJP → AAP</t>
+          <t>AAP → BJP → INC</t>
         </is>
       </c>
       <c r="AE171" s="26" t="inlineStr">
         <is>
-          <t>AAP Regained from BJP (AAP → BJP → AAP)</t>
+          <t>INC Leading Survey (AAP → BJP → INC)</t>
         </is>
       </c>
     </row>
@@ -20505,12 +20505,12 @@
       </c>
       <c r="B172" s="20" t="inlineStr">
         <is>
-          <t>Gujarpura - 1 (Left Side), Nagar Nigam Amritsar, Ward No. 50 + Gujarpura - 2 (Right Side), Nagar Nigam Amritsar, Ward No. 50 + Gujarpura - 3 (Left Side), Nagar Nigam Amritsar, Ward No. 50</t>
+          <t>Tarn Taran Road Amritsar - Govt. Elementary Smart School, Gujjarpura Amritsar</t>
         </is>
       </c>
       <c r="C172" s="20" t="inlineStr">
         <is>
-          <t>ਗੁੱਜਰਪੁਰਾ -1 (ਖੱਬਾ ਪਾਸਾ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਗੁੱਜਰਪੁਰਾ - 2 (ਸੱਜਾ ਪਾਸਾ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50 + ਗੁੱਜਰਪੁਰਾ -3 (ਖੱਬਾ ਪਾਸਾ), ਨਗਰ ਨਿਗਮ ਅੰਮ੍ਰਿਤਸਰ, ਵਾਰਡ ਨੰ. 50</t>
+          <t>ਤਰਨ ਤਾਰਨ ਰੋਡ ਅੰਮ੍ਰਿਤਸਰ - ਸਰਕਾਰੀ ਐਲੀਮੈਂਟਰੀ ਸਮਾਰਟ ਸਕੂਲ, ਗੁੱਜਰਪੁਰਾ ਅੰਮ੍ਰਿਤਸਰ</t>
         </is>
       </c>
       <c r="D172" s="21" t="n">
@@ -20588,16 +20588,16 @@
         <v>9</v>
       </c>
       <c r="Z172" s="21" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="AA172" s="24" t="inlineStr">
         <is>
-          <t>TIED</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="AB172" s="20" t="inlineStr">
         <is>
-          <t>AAP:2(10.53%) | INC:2(10.53%) | BJP:0 | SAD:0</t>
+          <t>AAP:23(23.47%) | INC:29(29.59%) | BJP:9 | SAD:0</t>
         </is>
       </c>
       <c r="AC172" s="20" t="inlineStr">
@@ -20607,12 +20607,12 @@
       </c>
       <c r="AD172" s="20" t="inlineStr">
         <is>
-          <t>AAP → AAP → TIED</t>
+          <t>AAP → AAP → INC</t>
         </is>
       </c>
       <c r="AE172" s="20" t="inlineStr">
         <is>
-          <t>Close / Undecided (AAP → AAP → TIED)</t>
+          <t>INC Leading Survey (AAP → AAP → INC)</t>
         </is>
       </c>
     </row>
